--- a/marketing-ownership-map.xlsx
+++ b/marketing-ownership-map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LRUSIN~1\AppData\Local\Temp\claude\c--Users-lrusinova-OneDrive---QuickBase-Documents-Project-Management-MCP\abf0f386-0ae7-411b-800d-e81e7586b212\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B66F7592-3596-4883-B9B8-8254B28DD6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EA43AA72-5732-48C6-ABC7-8FB3A181BA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{840B5537-3834-4E38-8A1A-8FEB33A66693}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{ADBF567C-1F4C-4A6D-87E4-148EBC33D2C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Ownership Matrix" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <author>Rusinova, Luiza</author>
   </authors>
   <commentList>
-    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{537CC844-9E50-46D8-9FF4-CC6B05AFF905}">
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{7DE34742-5DEC-4463-8B60-85207869E3E0}">
       <text>
         <r>
           <rPr>
@@ -59,7 +59,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{6F212F61-0CA5-408D-B0FA-B3DFE2F37743}">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{1F55DDC0-4776-414A-A47D-5D622508EEEC}">
       <text>
         <r>
           <rPr>
@@ -73,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{82D430CA-3774-44D6-90F6-08E87B2078DC}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{A17C0921-6D73-4F93-A751-6AAF90B505F6}">
       <text>
         <r>
           <rPr>
@@ -88,7 +88,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{331E90AF-3F7F-4F30-9B12-9651A48A50A6}">
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{1A2D261A-EBA8-438C-8232-F51E06F29A66}">
       <text>
         <r>
           <rPr>
@@ -102,7 +102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G6" authorId="0" shapeId="0" xr:uid="{E89D89C4-CBEF-4E89-A579-717992B71D85}">
+    <comment ref="G6" authorId="0" shapeId="0" xr:uid="{3758F9D8-E94E-4AE7-86AE-885C3DC16F1B}">
       <text>
         <r>
           <rPr>
@@ -117,7 +117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{B176D216-DA64-419E-B317-56E04C1731BA}">
+    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{9889D2A3-424B-498F-B837-B1FF5785345D}">
       <text>
         <r>
           <rPr>
@@ -131,7 +131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{9690C19F-DC72-488B-B312-0CE82DE04F91}">
+    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{38401944-6320-46B0-A577-662AEB74C926}">
       <text>
         <r>
           <rPr>
@@ -145,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="0" shapeId="0" xr:uid="{99AF020B-A93B-4045-B5A2-96148BB6DAC8}">
+    <comment ref="J6" authorId="0" shapeId="0" xr:uid="{11F5E611-549F-4380-BD99-05759C49E531}">
       <text>
         <r>
           <rPr>
@@ -159,7 +159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{244C2EEC-A1F4-48C8-99A3-875101732B02}">
+    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{85E94519-B74F-4BAD-9CCC-686FAC71D5E5}">
       <text>
         <r>
           <rPr>
@@ -173,7 +173,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{C0E7F949-4263-4A32-9214-1C95163C2014}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{317B8EA8-E95C-446F-A385-C91E9BD8DC0A}">
       <text>
         <r>
           <rPr>
@@ -188,7 +188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{AB3F0F02-5BF1-401A-8FB8-A0BC41A63489}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{40398932-E92F-4AD3-BF07-B7F8483B47A2}">
       <text>
         <r>
           <rPr>
@@ -202,7 +202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{0149602F-6E3C-4D8D-A3EF-E63F2BE5E422}">
+    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{0164D3B8-C066-4343-886C-A4FBAAE01567}">
       <text>
         <r>
           <rPr>
@@ -216,7 +216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{E5A73CA3-DCC7-4F3D-852C-FDC3868330C1}">
+    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{2C4A446B-9C95-4066-A05A-A653C3E5117E}">
       <text>
         <r>
           <rPr>
@@ -230,21 +230,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{F7127242-7E7C-4130-AFD0-D5F86FD8FF8E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Joins the pre-kickoff strategy call (per Jenny Louis, Director of Brand &amp; Creative) to weigh in on positioning before deliverables are scoped.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{3EB93470-340A-47E9-AD0D-FCAC2F41142A}">
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{43CB05E5-599B-4245-9EBE-3FCE78B2C63A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Joins the pre-kickoff strategy call (per Jenny Lui, Director of Brand &amp; Creative) to weigh in on positioning before deliverables are scoped.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{7166393F-9E9F-47A3-B599-7ED99CAC399F}">
       <text>
         <r>
           <rPr>
@@ -258,7 +258,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{CE84555B-30AB-48DF-A6CF-00EA38AB0549}">
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{DE347DE8-8893-4B4C-9F30-D50F999594AA}">
       <text>
         <r>
           <rPr>
@@ -272,7 +272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{21D46017-1BEA-4A11-8AA7-2738F6765058}">
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{13319A90-455A-4F49-B5CF-A96F866D93F8}">
       <text>
         <r>
           <rPr>
@@ -286,7 +286,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{84964482-1CBE-449E-AF32-80250D4E07AD}">
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{5B2EC2F8-1356-478A-B068-56FD7855840C}">
       <text>
         <r>
           <rPr>
@@ -301,7 +301,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{008E22CB-94FE-4C4D-A874-7C07EBCD9AA0}">
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{999108B7-4DCB-40D9-A3B5-840139F8924C}">
       <text>
         <r>
           <rPr>
@@ -315,7 +315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{B0703DB3-E497-4F73-9B0C-77CF973B15CD}">
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{33F75203-D8BE-4B40-BC0C-32B9DD0123DC}">
       <text>
         <r>
           <rPr>
@@ -329,7 +329,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{1D75D182-DA89-47F5-8CF1-762D86E9F9F1}">
+    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{8110718A-FD8C-4F26-962A-FB3B981A72A9}">
       <text>
         <r>
           <rPr>
@@ -343,7 +343,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="0" shapeId="0" xr:uid="{0B8F9D5C-C28A-4E81-9381-97D26D7CBAC0}">
+    <comment ref="J9" authorId="0" shapeId="0" xr:uid="{95B0933E-BBB8-4D96-8076-098036954215}">
       <text>
         <r>
           <rPr>
@@ -357,7 +357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{64264F1A-725F-40EE-B1C8-C8E6B7EA42FF}">
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{EADC331C-416C-4F17-9B9C-BA34CDDFBCBD}">
       <text>
         <r>
           <rPr>
@@ -371,7 +371,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{1C7814D0-32F1-47D5-9A77-7EA9AAEE056D}">
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{8E55F199-3381-439E-A1A3-A454146A0859}">
       <text>
         <r>
           <rPr>
@@ -385,7 +385,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{247902C4-5B4C-4574-89B7-3650BC2F171F}">
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{D9989B45-4139-449F-820A-9ECD262FD437}">
       <text>
         <r>
           <rPr>
@@ -400,7 +400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{044DB200-6145-48E2-8F2B-5EC4AB9375F8}">
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{99762019-B8B0-43BA-AD02-477CA4AAD5A7}">
       <text>
         <r>
           <rPr>
@@ -414,21 +414,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{E4632C3C-DD0D-4C49-8389-3C5B6C3C0663}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Joins the pre-kickoff strategy call (per Jenny Louis, Director of Brand &amp; Creative) to flag creative/asset approach before deliverables are scoped.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{F65B690C-4B2F-47FD-923F-83C1A39A3283}">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{9DF2B69C-6BF4-4509-B8E3-3AA88B4F5737}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Joins the pre-kickoff strategy call (per Jenny Lui, Director of Brand &amp; Creative) to flag creative/asset approach before deliverables are scoped.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{F8168D89-53B4-42D3-963F-78054D64C69C}">
       <text>
         <r>
           <rPr>
@@ -442,7 +442,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{D652496D-D9FD-4804-864C-342320ECC95D}">
+    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{515B47C5-1264-44C3-AA6D-C15829525771}">
       <text>
         <r>
           <rPr>
@@ -456,7 +456,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{7B7E1958-0AC8-414F-9013-744F6B31E672}">
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{DFE3D0E9-B88A-4605-92C2-37F667297B04}">
       <text>
         <r>
           <rPr>
@@ -470,7 +470,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{D0D14E1E-F28F-4F30-B7E8-4481051AE8CE}">
+    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{ED87AD16-284E-4850-8D5D-949A48C6C6D5}">
       <text>
         <r>
           <rPr>
@@ -484,7 +484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{02558303-BFC1-4338-841E-6554164BA0D1}">
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{469F0668-0830-4B7C-9281-30F265F7934C}">
       <text>
         <r>
           <rPr>
@@ -498,7 +498,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{69E31930-E18F-4B94-90AF-3D8D8FB2A33B}">
+    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{741E7FFE-A857-4230-BD12-64AC5A853284}">
       <text>
         <r>
           <rPr>
@@ -512,7 +512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="0" shapeId="0" xr:uid="{745FA499-7B64-40B2-AFE2-E2B9B444A59E}">
+    <comment ref="H13" authorId="0" shapeId="0" xr:uid="{506A5A7F-1B18-4F39-B012-2FECC80679F8}">
       <text>
         <r>
           <rPr>
@@ -526,7 +526,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J13" authorId="0" shapeId="0" xr:uid="{CF5A20AA-A4D0-42A2-B968-C704C4FF399B}">
+    <comment ref="J13" authorId="0" shapeId="0" xr:uid="{F60BB9C5-FEBB-4D7B-AAEF-FB3E28C8CF30}">
       <text>
         <r>
           <rPr>
@@ -540,7 +540,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{78AE6D5A-B632-4758-9715-8CCB2F4545BE}">
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{71AF8E85-4AC1-4041-B5BD-D4AF2909CB10}">
       <text>
         <r>
           <rPr>
@@ -554,7 +554,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{32B96530-C76B-4F33-A4C8-97006B46F8C4}">
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{39BBF026-D7E0-4BFE-9AF3-13F4FBAD97B7}">
       <text>
         <r>
           <rPr>
@@ -568,7 +568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{2F270CF0-A03A-4965-8E41-2AB8FE7CB995}">
+    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{16951E65-2C5C-4D7E-B44A-8E5481B7CE66}">
       <text>
         <r>
           <rPr>
@@ -582,7 +582,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{C2A08AE6-E0A3-443F-93AE-CDC84C4995CA}">
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{71724FF0-A5FB-4610-A97D-C1F31AC656B9}">
       <text>
         <r>
           <rPr>
@@ -596,7 +596,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{4CB40028-B8FE-4558-98EE-3E69DBCCC631}">
+    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{EC2A2EAE-9C6F-4027-B167-9F5EF9CD131C}">
       <text>
         <r>
           <rPr>
@@ -610,7 +610,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0" shapeId="0" xr:uid="{96A94C7D-46EC-4BF2-8F2C-74ED96260B02}">
+    <comment ref="E16" authorId="0" shapeId="0" xr:uid="{F7EA35BF-567D-49FB-A636-5609FDBA4BF7}">
       <text>
         <r>
           <rPr>
@@ -624,7 +624,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{16254745-3B74-4D44-8AB3-6FD6BBDCE3B5}">
+    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{E1C0B952-D615-4D28-AC53-2239E64B266D}">
       <text>
         <r>
           <rPr>
@@ -638,7 +638,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{46B7FE16-165B-426E-8998-55B1E16A5959}">
+    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{A1CF2403-1105-4A6F-ADFE-6B6F8EBD6E8F}">
       <text>
         <r>
           <rPr>
@@ -652,7 +652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J16" authorId="0" shapeId="0" xr:uid="{7C409EAF-234B-4921-A64D-FEA7C4BDFAF7}">
+    <comment ref="J16" authorId="0" shapeId="0" xr:uid="{01B3E2F4-70CA-4151-8C8F-F874997D91B8}">
       <text>
         <r>
           <rPr>
@@ -666,7 +666,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{B6129FD6-7E70-44D0-B703-1D8BA2DAD6A5}">
+    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{CB4F56AF-9363-4631-A8CC-0F36B848F7F9}">
       <text>
         <r>
           <rPr>
@@ -680,7 +680,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G17" authorId="0" shapeId="0" xr:uid="{73570073-FB44-4785-9E15-C238AFD19454}">
+    <comment ref="G17" authorId="0" shapeId="0" xr:uid="{21EC90F2-E20F-490E-924D-0DE554DBA751}">
       <text>
         <r>
           <rPr>
@@ -694,7 +694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{A0565A38-78F0-4AFF-8A04-45F01D315FB6}">
+    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{B0C8AF5A-A765-43F4-92C9-1171DDC9C0FE}">
       <text>
         <r>
           <rPr>
@@ -708,7 +708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J17" authorId="0" shapeId="0" xr:uid="{28330EC4-62B5-4198-A0C5-4E764F74ED65}">
+    <comment ref="J17" authorId="0" shapeId="0" xr:uid="{44891C13-D6E9-4CD1-83BF-52E9DE82BBFA}">
       <text>
         <r>
           <rPr>
@@ -722,7 +722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{39CB1A88-85BE-4DB6-94C5-2B2089DE28D9}">
+    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{2A6B3B22-F263-4E2F-845C-6FAC90DE278C}">
       <text>
         <r>
           <rPr>
@@ -736,7 +736,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{5FBBD009-1C3B-4654-97A0-CC9D7EE3CEE1}">
+    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{87576241-A281-419B-8CA3-4AD2806EB415}">
       <text>
         <r>
           <rPr>
@@ -750,7 +750,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{D051E8E3-2846-4589-8F9E-CFE4380E61E1}">
+    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{8E972169-81C7-4529-8EEB-B09EFDA72875}">
       <text>
         <r>
           <rPr>
@@ -764,7 +764,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{42AE314B-8207-49F3-A1A3-313B0CBAE351}">
+    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{686ACD90-4B53-4D53-85B8-5BDF1EE87A1D}">
       <text>
         <r>
           <rPr>
@@ -778,7 +778,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{99BD5D43-E37F-47CA-833E-F63213850D81}">
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{F9439D3B-B7DF-448E-B36C-2BA287AD8F4E}">
       <text>
         <r>
           <rPr>
@@ -792,7 +792,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{0BCCF6FD-1D9D-4F15-BCD2-0DE513F17FA0}">
+    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{2A5EA72C-09E9-4636-9174-F5102C14789A}">
       <text>
         <r>
           <rPr>
@@ -806,7 +806,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{8F5A6F63-F3BB-4F0F-8F41-09295BD3FBF5}">
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{3E07ED08-D6D5-4BE1-A5FB-45E52B54EF3C}">
       <text>
         <r>
           <rPr>
@@ -820,7 +820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G19" authorId="0" shapeId="0" xr:uid="{C085B643-144C-45A2-9A79-5159E7E0EF6E}">
+    <comment ref="G19" authorId="0" shapeId="0" xr:uid="{02F9447F-CF33-4050-9CAF-C832B8E2B20E}">
       <text>
         <r>
           <rPr>
@@ -834,7 +834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{159395E5-59E0-45CD-908F-D672660178F4}">
+    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{B798E47C-E88D-4FBC-9C59-AEC09262D02E}">
       <text>
         <r>
           <rPr>
@@ -848,7 +848,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J19" authorId="0" shapeId="0" xr:uid="{D3FA42B5-9709-4AA7-AB7D-E20D8FBECFD9}">
+    <comment ref="J19" authorId="0" shapeId="0" xr:uid="{F25D2C4E-ECFA-4243-B17E-A03791258CC9}">
       <text>
         <r>
           <rPr>
@@ -862,7 +862,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{E2A77803-2CCA-4C42-BDE9-A1D792EC649D}">
+    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{0ADAE55F-8485-416C-A564-C5990FFCCC24}">
       <text>
         <r>
           <rPr>
@@ -877,7 +877,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{E1FDDC36-F902-47D7-8525-B9BDF666DA77}">
+    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{23ACAD03-0F8C-47F8-97F1-69B908AE1E3C}">
       <text>
         <r>
           <rPr>
@@ -891,7 +891,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{20A8D9BA-7FDA-4B5D-AA36-8BCD988D9862}">
+    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{38F4B2A0-45DC-4C3E-B16B-B241CEA0FD9A}">
       <text>
         <r>
           <rPr>
@@ -905,7 +905,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{EEAEA712-3626-4BC7-9F87-A062314BB8B1}">
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{E9A55A74-131D-4F52-A5B5-4FDA6CE86108}">
       <text>
         <r>
           <rPr>
@@ -919,7 +919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{63C85853-5B48-4395-AB24-28B65E8173B3}">
+    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{BC067597-70EE-4BB8-A26B-5E5FC3BAAEB1}">
       <text>
         <r>
           <rPr>
@@ -933,7 +933,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{AF6DDDBB-AECF-4960-86FE-262663ED9873}">
+    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{F08F3952-3542-4117-8485-830BE8FCA06D}">
       <text>
         <r>
           <rPr>
@@ -947,7 +947,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{4CF74813-4053-4945-9EF8-B2D3A9A2491D}">
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{7C462FFB-73AE-4BE5-9FD1-EC67474F0DC5}">
       <text>
         <r>
           <rPr>
@@ -961,7 +961,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G21" authorId="0" shapeId="0" xr:uid="{E44A1D20-365F-4120-ACFE-7176579BC94F}">
+    <comment ref="G21" authorId="0" shapeId="0" xr:uid="{4A42E715-7CCB-44EA-954D-26109F86362C}">
       <text>
         <r>
           <rPr>
@@ -975,7 +975,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{632F8174-ADC9-4703-BAE4-43566DCA2C1C}">
+    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{DCEFA3CA-FB85-4216-B472-73AB3ED5F79E}">
       <text>
         <r>
           <rPr>
@@ -989,7 +989,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{4A864DCF-3D64-43F5-A4A9-AA9F933F697C}">
+    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{CE500F7A-CD50-457F-A93A-02798409260F}">
       <text>
         <r>
           <rPr>
@@ -1003,7 +1003,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J21" authorId="0" shapeId="0" xr:uid="{0213CCD2-6278-4D4A-A112-1BEB1C13F6EA}">
+    <comment ref="J21" authorId="0" shapeId="0" xr:uid="{51C3405B-7E23-4112-9180-B180A6054D9F}">
       <text>
         <r>
           <rPr>
@@ -1017,7 +1017,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E22" authorId="0" shapeId="0" xr:uid="{9B4E76DB-493B-453C-BE1D-A7513C517121}">
+    <comment ref="E22" authorId="0" shapeId="0" xr:uid="{C9B9B515-A8D1-403C-BC99-4E59D4C526ED}">
       <text>
         <r>
           <rPr>
@@ -1031,7 +1031,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G22" authorId="0" shapeId="0" xr:uid="{0AE9675D-176A-45A1-9436-F9F80163F466}">
+    <comment ref="G22" authorId="0" shapeId="0" xr:uid="{7C570F8B-0E99-4C9F-A396-BABE9CCFBD5D}">
       <text>
         <r>
           <rPr>
@@ -1045,7 +1045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H22" authorId="0" shapeId="0" xr:uid="{781EA18D-A7C1-43A8-B316-C04D41FF310B}">
+    <comment ref="H22" authorId="0" shapeId="0" xr:uid="{F228CBF0-7968-4EFD-A862-F297242FF5D7}">
       <text>
         <r>
           <rPr>
@@ -1059,7 +1059,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{CAACBFB2-E520-4EB9-B76B-D55F493177C5}">
+    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{460B977E-59AE-4C96-BD7F-8C80D0B84E89}">
       <text>
         <r>
           <rPr>
@@ -1073,7 +1073,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J22" authorId="0" shapeId="0" xr:uid="{CA260731-A31E-4733-8EA4-FB6069D0EE20}">
+    <comment ref="J22" authorId="0" shapeId="0" xr:uid="{A6F490CA-7473-4315-9BB0-C2D33732A957}">
       <text>
         <r>
           <rPr>
@@ -1087,7 +1087,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D23" authorId="0" shapeId="0" xr:uid="{66027402-F58C-4267-A7A5-F4BC145C98A6}">
+    <comment ref="D23" authorId="0" shapeId="0" xr:uid="{BA06F242-7739-4810-BE9B-5B53F952B6DC}">
       <text>
         <r>
           <rPr>
@@ -1101,7 +1101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E23" authorId="0" shapeId="0" xr:uid="{A6C2E588-4AD8-48A7-A44E-DCBB1CF961AB}">
+    <comment ref="E23" authorId="0" shapeId="0" xr:uid="{9C616769-CB89-4ABE-8833-49A09CC8AFE4}">
       <text>
         <r>
           <rPr>
@@ -1116,7 +1116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G23" authorId="0" shapeId="0" xr:uid="{61C975E0-12F2-4D3B-8CC7-A8441CACB557}">
+    <comment ref="G23" authorId="0" shapeId="0" xr:uid="{67D2B3D2-A257-4999-BF6A-73ADCC706A36}">
       <text>
         <r>
           <rPr>
@@ -1130,7 +1130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{FCBC009D-0370-432E-A966-5BB1A5FA4791}">
+    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{ED320130-4A68-4633-A508-DB772BBB91B6}">
       <text>
         <r>
           <rPr>
@@ -1144,7 +1144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{D08FB474-17BF-47E7-9395-5B36ECB3AF0D}">
+    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{AED8018E-1FC0-4A94-AEDB-1CBFBA4EBA0B}">
       <text>
         <r>
           <rPr>
@@ -1158,7 +1158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J23" authorId="0" shapeId="0" xr:uid="{153A8F0B-DD7D-4B6E-A124-CACDA936DC1B}">
+    <comment ref="J23" authorId="0" shapeId="0" xr:uid="{41A37461-2D61-452D-8041-573620C05AEB}">
       <text>
         <r>
           <rPr>
@@ -1173,7 +1173,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C25" authorId="0" shapeId="0" xr:uid="{DCEA9FC0-A711-4A28-BE24-E33F95C9A4AE}">
+    <comment ref="C25" authorId="0" shapeId="0" xr:uid="{92E9143E-8F37-4D34-9CF3-86BC1DA90459}">
       <text>
         <r>
           <rPr>
@@ -1187,7 +1187,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E25" authorId="0" shapeId="0" xr:uid="{4873C3D9-F2B2-4B2E-9464-9A0F2AA75777}">
+    <comment ref="E25" authorId="0" shapeId="0" xr:uid="{228EC8C7-FDAE-41E6-9109-8CA94006FF6E}">
       <text>
         <r>
           <rPr>
@@ -1201,7 +1201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0" xr:uid="{182926B4-4A8F-4282-8471-D979DD21E028}">
+    <comment ref="F25" authorId="0" shapeId="0" xr:uid="{FD18C5BF-CDBA-4A3F-9116-32A11663FD00}">
       <text>
         <r>
           <rPr>
@@ -1215,7 +1215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G25" authorId="0" shapeId="0" xr:uid="{9E2B77B5-F838-4460-AF4B-F7B915421F54}">
+    <comment ref="G25" authorId="0" shapeId="0" xr:uid="{B3B912FB-C979-44DE-BBF0-100A50BDA736}">
       <text>
         <r>
           <rPr>
@@ -1229,7 +1229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{68F72275-02B1-43FF-9F0D-95D59EC8A714}">
+    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{BBD7E4AF-8E9B-42A5-B5E8-7A66CD2840B1}">
       <text>
         <r>
           <rPr>
@@ -1243,7 +1243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0" xr:uid="{196F64AB-7159-4E64-A576-3F1E19EC3BBD}">
+    <comment ref="J25" authorId="0" shapeId="0" xr:uid="{3E38B2B0-0B6F-41AB-97F9-E3F267B3AB8B}">
       <text>
         <r>
           <rPr>
@@ -1477,7 +1477,7 @@
     <t>Reports channel performance against targets.</t>
   </si>
   <si>
-    <t>Joins the pre-kickoff strategy call (per Jenny Louis, Director of Brand &amp; Creative) to weigh in on positioning before deliverables are scoped.</t>
+    <t>Joins the pre-kickoff strategy call (per Jenny Lui, Director of Brand &amp; Creative) to weigh in on positioning before deliverables are scoped.</t>
   </si>
   <si>
     <t>Owns narrative, positioning, and messaging architecture.</t>
@@ -1522,7 +1522,7 @@
     <t>Incorporates review feedback.</t>
   </si>
   <si>
-    <t>Joins the pre-kickoff strategy call (per Jenny Louis, Director of Brand &amp; Creative) to flag creative/asset approach before deliverables are scoped.</t>
+    <t>Joins the pre-kickoff strategy call (per Jenny Lui, Director of Brand &amp; Creative) to flag creative/asset approach before deliverables are scoped.</t>
   </si>
   <si>
     <t>Produces visual/design assets.</t>
@@ -1916,16 +1916,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C61C7A6C-7615-431F-B40C-EDA7291A25D3}" name="OwnershipData" displayName="OwnershipData" ref="A1:G137" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:G137" xr:uid="{C61C7A6C-7615-431F-B40C-EDA7291A25D3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8C8C3D2D-8A01-48A6-BE8E-E2D22875FC43}" name="OwnershipData" displayName="OwnershipData" ref="A1:G137" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:G137" xr:uid="{8C8C3D2D-8A01-48A6-BE8E-E2D22875FC43}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{9C50D4B1-563D-49A8-A88E-CDDF693E3B01}" name="Team"/>
-    <tableColumn id="2" xr3:uid="{8AA70762-6D6D-44A2-AD93-6E4537C4880A}" name="Team Group"/>
-    <tableColumn id="3" xr3:uid="{BD8E6D9B-D254-4795-A30D-637C62BC3A3C}" name="Stage"/>
-    <tableColumn id="4" xr3:uid="{5F14F368-29C6-4407-8F4F-7C407AABB0D3}" name="RACI"/>
-    <tableColumn id="5" xr3:uid="{E0C6DE87-E8CB-467E-AD12-9038663D1CC8}" name="Note"/>
-    <tableColumn id="6" xr3:uid="{41640DA7-CA11-4CF9-A788-DDCE1BFD765F}" name="Conflict"/>
-    <tableColumn id="7" xr3:uid="{E5231930-1FAF-43DC-8BD2-D868EE2FBF1C}" name="Conflict Note"/>
+    <tableColumn id="1" xr3:uid="{2E2C7524-55A1-4FC6-8475-026F4FF2919B}" name="Team"/>
+    <tableColumn id="2" xr3:uid="{95AA5A62-A822-47CE-94BC-92103EFA0850}" name="Team Group"/>
+    <tableColumn id="3" xr3:uid="{8E405F79-F8FD-482B-9EAB-EAD9BB0CC229}" name="Stage"/>
+    <tableColumn id="4" xr3:uid="{DF47C2C1-74BF-4907-B0CD-D8730D8A44AB}" name="RACI"/>
+    <tableColumn id="5" xr3:uid="{2FA533DE-65FC-4A8B-85F8-91E049006FFE}" name="Note"/>
+    <tableColumn id="6" xr3:uid="{A38E4250-D730-45A0-80E7-5CF20C7791C7}" name="Conflict"/>
+    <tableColumn id="7" xr3:uid="{11D74464-C59C-44BC-8DBB-C0A0B1B97466}" name="Conflict Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2247,7 +2247,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{907F1F04-6417-4FE3-8644-27B0B8304B53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01CE1FA-930D-4760-AC02-5FF3A6A920DD}">
   <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -2877,7 +2877,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A676F9BA-A5F2-43F6-86CD-E44727B2CB39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E7F510-9BA2-404C-9032-21C8FA09436C}">
   <dimension ref="A1:G137"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/marketing-ownership-map.xlsx
+++ b/marketing-ownership-map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LRUSIN~1\AppData\Local\Temp\claude\c--Users-lrusinova-OneDrive---QuickBase-Documents-Project-Management-MCP\abf0f386-0ae7-411b-800d-e81e7586b212\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3519A7-ECD0-4741-946A-20CE196E1246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804F8EB9-DE6B-45CF-9EC8-13B68BADB024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{F2D5D3C6-8892-4EB4-A380-5A7790109366}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{6BE01299-3AA2-44C9-B560-36F384A9188D}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
     <author>Rusinova, Luiza</author>
   </authors>
   <commentList>
-    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{80A03AEF-5D39-46A4-9E62-502FAE7436C2}">
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{BAB04E11-E01F-4118-84D7-5F13012659D1}">
       <text>
         <r>
           <rPr>
@@ -60,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{2D1D2EF3-1E7F-47DE-BE89-4500FE944ED0}">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{D3F167C3-553D-4F51-B41A-3774D0F2097E}">
       <text>
         <r>
           <rPr>
@@ -74,7 +74,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{CFA41A8D-8A32-4A72-9B1A-C48BB9BE7667}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{D1C72457-2918-49DA-B32D-328B621ECDA1}">
       <text>
         <r>
           <rPr>
@@ -89,7 +89,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{CAD831B4-AEC4-4330-B217-465DEFEEB1FF}">
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{A18B08CA-E4B8-4F2B-9481-F871476B38C9}">
       <text>
         <r>
           <rPr>
@@ -103,7 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G6" authorId="0" shapeId="0" xr:uid="{4B38E8A0-D57E-4442-B5AF-E008F6B90AA1}">
+    <comment ref="G6" authorId="0" shapeId="0" xr:uid="{5C0144C2-A9B0-4B6E-9BD9-4B1621C476E2}">
       <text>
         <r>
           <rPr>
@@ -118,7 +118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{2C7A71BB-3674-46FD-8597-9E774E175F78}">
+    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{469E6ABC-E10B-411B-9542-2B8DA935CABF}">
       <text>
         <r>
           <rPr>
@@ -132,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{4566ABEC-0646-4806-9234-F928F8E137C3}">
+    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{DB7B26AE-03F3-4C85-A806-20AB014279A1}">
       <text>
         <r>
           <rPr>
@@ -146,7 +146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="0" shapeId="0" xr:uid="{F2E25358-F85F-4F0D-B27B-B5BB07D44D10}">
+    <comment ref="J6" authorId="0" shapeId="0" xr:uid="{C60F9F14-A735-4807-9321-5ECB348502FE}">
       <text>
         <r>
           <rPr>
@@ -160,7 +160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{3464AB2F-6547-4136-8321-3F2A7ECB1785}">
+    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{1FD10B2F-6D27-4426-B98C-EA76901E1365}">
       <text>
         <r>
           <rPr>
@@ -174,7 +174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{2E290DE8-6A1D-4FEA-94A6-4987F45C5436}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{8090B464-0FF5-4C53-A54C-273AEA6FC384}">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{B31B330A-7330-4011-9107-7B415C6DBB77}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{64C3D2BB-B6C1-40A1-8324-FC0A37D160A8}">
       <text>
         <r>
           <rPr>
@@ -203,7 +203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{ED1CC432-30F0-46CD-AB6B-5038C71BF711}">
+    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{3FBDE4D7-3442-4B00-AF5D-2CD67B161FC9}">
       <text>
         <r>
           <rPr>
@@ -217,7 +217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{19ACF89A-8DDC-4485-AAB5-E950C97990D6}">
+    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{2BDC43F2-0940-489C-B32A-D2D08AB7BED7}">
       <text>
         <r>
           <rPr>
@@ -231,7 +231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{476A78A4-6DCD-4C89-9D90-F27A997C0085}">
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{C609FCB9-EEC5-4C6E-8E0C-F1E8A2BFC828}">
       <text>
         <r>
           <rPr>
@@ -245,7 +245,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{1F245D74-6D7C-4EA4-A375-D159A89D6183}">
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{CB2734AF-0CEA-428E-94F5-CFF09597CC8E}">
       <text>
         <r>
           <rPr>
@@ -259,7 +259,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{3E7A3C47-6A1D-4A2A-A083-5FB360D10023}">
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{4D8ED339-95D6-434E-B24F-787333C1EE7B}">
       <text>
         <r>
           <rPr>
@@ -273,7 +273,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{B2F87FEB-4011-4549-9FE7-59F6F9F2BA1A}">
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{FB406B22-1174-408F-BD67-CE9D0EF3601C}">
       <text>
         <r>
           <rPr>
@@ -287,7 +287,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{C634B8C5-CB00-4F4C-B39F-4BD2BB107442}">
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{F7D7397A-0BCB-4A53-AF77-F157AE764E31}">
       <text>
         <r>
           <rPr>
@@ -302,7 +302,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{0CC110E5-AC28-4C21-8F55-2A60D44EEF22}">
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{82D527DE-C892-4004-A20F-0E22C35CB7DD}">
       <text>
         <r>
           <rPr>
@@ -316,7 +316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{8AA60B7C-6D96-4D8D-B929-545B2571ABF2}">
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{1B7F7F27-5C2A-471F-A774-BDDFD099AA7E}">
       <text>
         <r>
           <rPr>
@@ -330,7 +330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{355E88C1-C59A-4EE7-9418-4880B5B44BF9}">
+    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{2999E64B-6FE6-43B0-B9AF-5453C2C733FE}">
       <text>
         <r>
           <rPr>
@@ -344,7 +344,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="0" shapeId="0" xr:uid="{531894A1-156D-41C4-833F-FC8C76D4DE3D}">
+    <comment ref="J9" authorId="0" shapeId="0" xr:uid="{64EA06BF-A8C7-4C32-B3C2-B446820B1183}">
       <text>
         <r>
           <rPr>
@@ -358,7 +358,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{3FB118A0-EB77-451B-81B1-E13EB67557FC}">
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{351CE4CB-5539-4C96-BCAD-CF1430ADADEB}">
       <text>
         <r>
           <rPr>
@@ -372,7 +372,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{D6434A65-42BB-4D95-9DE0-23BBA3FFD902}">
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{A1980C4C-A314-40ED-8D5B-A783F93CD60B}">
       <text>
         <r>
           <rPr>
@@ -386,7 +386,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{CA5CADDF-52CD-4495-B727-D054D839B6A1}">
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{860D7150-E2A5-46E1-95C5-16712C27A4F1}">
       <text>
         <r>
           <rPr>
@@ -401,7 +401,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{FC06E4B0-E675-4BB6-96ED-8A50B9042EBA}">
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{09572632-D062-4673-9D61-1CE15F6E768F}">
       <text>
         <r>
           <rPr>
@@ -415,7 +415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{3A49C1E4-036D-448A-8CBB-EFBE91BC33FB}">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{D29097A2-A8F1-4846-AF57-54D1CD695227}">
       <text>
         <r>
           <rPr>
@@ -429,7 +429,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{4E26D842-5AE6-4B75-80F0-240F958C2CE2}">
+    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{8A6A7456-A543-4A63-A452-06BB33A214C9}">
       <text>
         <r>
           <rPr>
@@ -443,7 +443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{783C9663-C210-42CA-B73F-BF1024E0D559}">
+    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{2F353211-B85B-4140-8355-A58127BD373E}">
       <text>
         <r>
           <rPr>
@@ -457,7 +457,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{EA14FC5A-7C09-4ABB-9C22-B1F09FE156FC}">
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{3F963966-445B-404A-8D20-091E2DC8E888}">
       <text>
         <r>
           <rPr>
@@ -471,7 +471,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{7CB6BC80-32DE-40D9-B1CA-09D5597C2ABE}">
+    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{A900AE41-2839-4C08-A8AA-EBC7FCD5AE27}">
       <text>
         <r>
           <rPr>
@@ -485,7 +485,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{34538757-2BB3-4E4B-BD63-24A62B6864D8}">
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{579E7184-2533-4115-83E6-78B9DEE61FFD}">
       <text>
         <r>
           <rPr>
@@ -499,7 +499,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{1767F5BA-18DD-4EAE-B0F6-88990C16EEC0}">
+    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{5F1D4EF9-CAC2-4D94-83AE-CCD28A91135A}">
       <text>
         <r>
           <rPr>
@@ -513,7 +513,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="0" shapeId="0" xr:uid="{ECB7298A-6D83-4EF6-AD13-6EB22602F857}">
+    <comment ref="H13" authorId="0" shapeId="0" xr:uid="{8FB00AF5-0D62-4E79-A02F-18CE5849E43A}">
       <text>
         <r>
           <rPr>
@@ -527,7 +527,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J13" authorId="0" shapeId="0" xr:uid="{12ABBEB5-42C9-455B-BB1D-13B5C0A02518}">
+    <comment ref="J13" authorId="0" shapeId="0" xr:uid="{6D43A919-0D72-4AAA-BDA0-08D868574998}">
       <text>
         <r>
           <rPr>
@@ -541,7 +541,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{1987E295-DD64-4B1E-8E29-97356031FB70}">
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{BBBD1169-C60E-4E5B-BEA4-92849CE0A736}">
       <text>
         <r>
           <rPr>
@@ -555,7 +555,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{B600620F-8787-4925-B03C-F1F04D8FBAFB}">
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{19D31EF5-A25A-4411-B00A-9028B89941A3}">
       <text>
         <r>
           <rPr>
@@ -569,7 +569,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{3D1CA42D-0A83-49CB-9688-7A08B22ECFA8}">
+    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{CC1883E9-B48E-4B90-B843-0A6D2E67320D}">
       <text>
         <r>
           <rPr>
@@ -583,7 +583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{10E00851-BAE3-4E6E-946F-F7A77DD891C1}">
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{AD51A3FF-3DEB-48D7-9C05-C576DB2B8A31}">
       <text>
         <r>
           <rPr>
@@ -597,7 +597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{0A3CBBA5-7E2A-4E0C-A35C-3A1B2BCAF08F}">
+    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{D9F5B064-F1DD-41E7-B76D-7E6DCA41A63D}">
       <text>
         <r>
           <rPr>
@@ -611,7 +611,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0" shapeId="0" xr:uid="{A174F1A2-79A2-480D-9770-8F8A28F466C8}">
+    <comment ref="E16" authorId="0" shapeId="0" xr:uid="{7C14BC21-B56C-44A1-8A8F-2B10F3C32F91}">
       <text>
         <r>
           <rPr>
@@ -625,7 +625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{BFE9CAAE-2474-40D5-863F-AE8EF5A6D0D0}">
+    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{9E6DFAFE-D66E-4BD2-8BE7-6618171629D1}">
       <text>
         <r>
           <rPr>
@@ -639,7 +639,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{633930CD-E900-4082-9AB3-B0761F422E5D}">
+    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{F57F7327-8223-409F-8E68-7D9220AE4782}">
       <text>
         <r>
           <rPr>
@@ -653,7 +653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J16" authorId="0" shapeId="0" xr:uid="{782D297E-637B-4A3F-96C9-E21D18530BC6}">
+    <comment ref="J16" authorId="0" shapeId="0" xr:uid="{61C6CD16-2477-46AB-89FE-81C2C9FC4519}">
       <text>
         <r>
           <rPr>
@@ -667,7 +667,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{185891CB-9711-420C-BEFE-7072451D90B8}">
+    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{1CCBA09D-2496-480B-BA6E-CB030F3F6707}">
       <text>
         <r>
           <rPr>
@@ -681,7 +681,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G17" authorId="0" shapeId="0" xr:uid="{46C39410-22BB-4D1D-9C5D-99536270121F}">
+    <comment ref="G17" authorId="0" shapeId="0" xr:uid="{255398D5-80A5-4CEF-9234-BF7FAE79E30B}">
       <text>
         <r>
           <rPr>
@@ -695,7 +695,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{A3B106FF-4415-4DE6-86AE-D1A15714E2BA}">
+    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{ADA45EB7-5789-41C2-A097-0F9D2224831D}">
       <text>
         <r>
           <rPr>
@@ -709,7 +709,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J17" authorId="0" shapeId="0" xr:uid="{0DC74181-AF2A-476C-8C6A-35ED4CD52CDD}">
+    <comment ref="J17" authorId="0" shapeId="0" xr:uid="{AACA4D19-2F7C-47EB-AB52-950570862342}">
       <text>
         <r>
           <rPr>
@@ -723,7 +723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{8EDECB01-81F1-4513-87FE-64F1FB624FD8}">
+    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{D1CBDFBA-0E22-46B5-AACD-919680D6F8A0}">
       <text>
         <r>
           <rPr>
@@ -737,7 +737,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{8E9F62C5-8211-4EA2-AE9E-CC05B171997F}">
+    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{AEFA6057-EE90-4F1C-B17C-C4AB5990A220}">
       <text>
         <r>
           <rPr>
@@ -751,7 +751,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{F6A2837A-EE99-4A8D-B902-119FE0EAA080}">
+    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{CF27BA6F-8718-454C-A3C2-7B1F1B2D43D7}">
       <text>
         <r>
           <rPr>
@@ -765,7 +765,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{A202A2E9-092B-4C08-BC19-07D0A723AC49}">
+    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{F062BF64-FE28-4DCA-B2D9-9A9250541D82}">
       <text>
         <r>
           <rPr>
@@ -779,7 +779,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{123D6002-27B8-4DEF-AE78-DFB539814B74}">
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{33A5B5E1-C892-4D15-8586-6A1CA1527399}">
       <text>
         <r>
           <rPr>
@@ -793,7 +793,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{C9CA2838-1BFD-4D61-8D99-709F31BAD4BD}">
+    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{B74871B0-A20F-41D1-9FDF-098C2F10614D}">
       <text>
         <r>
           <rPr>
@@ -807,7 +807,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{41B551A7-3DBF-48DC-AA06-1E80FAEE9B79}">
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{6D18C7E2-A41A-46E0-847B-E5E331563F86}">
       <text>
         <r>
           <rPr>
@@ -821,7 +821,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G19" authorId="0" shapeId="0" xr:uid="{02FFF970-9DE9-419C-A25B-53037481A5AA}">
+    <comment ref="G19" authorId="0" shapeId="0" xr:uid="{9ED6303B-2CB6-471D-BD25-630B79E93A8D}">
       <text>
         <r>
           <rPr>
@@ -835,7 +835,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{758CB2FB-99B8-4D9D-97C3-5A06A1855D25}">
+    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{1BDAD591-E21C-4A70-BB11-B6EE5FFCF387}">
       <text>
         <r>
           <rPr>
@@ -849,7 +849,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J19" authorId="0" shapeId="0" xr:uid="{76083589-A1C2-4F65-969B-CDB157C738A7}">
+    <comment ref="J19" authorId="0" shapeId="0" xr:uid="{BE529E6C-1F99-4712-94AE-0B7F205766AA}">
       <text>
         <r>
           <rPr>
@@ -863,7 +863,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{A30E3EE8-17D0-4C4D-90FA-EA3F4FA9747E}">
+    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{CBE8EED1-8C06-4241-9438-C26F190B609A}">
       <text>
         <r>
           <rPr>
@@ -878,7 +878,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{7F9FD825-A5E9-4FA1-BA3C-B0C814E0CE62}">
+    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{0F52992C-6346-4AC9-AA55-80C5FE5803B4}">
       <text>
         <r>
           <rPr>
@@ -892,7 +892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{D0F0AFB1-6FD9-4D3E-ADE5-D767BF3D358F}">
+    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{2068A96C-0CD5-4947-B1E3-0A930466B02F}">
       <text>
         <r>
           <rPr>
@@ -906,7 +906,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{9CD0E417-B22B-497F-8FB5-1F5F9A5BE01C}">
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{E31432B3-3C37-4DCF-AE9A-B90F3F88A84B}">
       <text>
         <r>
           <rPr>
@@ -920,7 +920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{B23D66B0-7B5C-4844-A911-A347C30F415C}">
+    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{BC232B02-F26C-4E7F-8174-3D663B4DFBC8}">
       <text>
         <r>
           <rPr>
@@ -934,7 +934,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{648EAAE4-F3B1-4C9B-BB6B-51652232251F}">
+    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{B1EA46D5-3C3A-43BA-847E-3852A1A60C9C}">
       <text>
         <r>
           <rPr>
@@ -948,7 +948,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{9DF7D254-C8C9-4DA4-8346-12561AFFA8D8}">
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{868A23ED-530F-4B30-B610-31D544B8B0A2}">
       <text>
         <r>
           <rPr>
@@ -962,7 +962,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G21" authorId="0" shapeId="0" xr:uid="{1A258A2A-968F-4483-BD1A-1E0AC1569A21}">
+    <comment ref="G21" authorId="0" shapeId="0" xr:uid="{1314B8BB-57AB-495E-B039-077ED9ECC548}">
       <text>
         <r>
           <rPr>
@@ -976,7 +976,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{F9CB07D2-8320-4B8C-8028-142528D9E823}">
+    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{97076E4A-96E9-4192-B008-7609FF871335}">
       <text>
         <r>
           <rPr>
@@ -990,7 +990,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{33BD7127-6978-4828-8574-FAB6B4303869}">
+    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{138FBBD1-7C54-4BE5-B049-827CC041D5CE}">
       <text>
         <r>
           <rPr>
@@ -1004,7 +1004,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J21" authorId="0" shapeId="0" xr:uid="{CF88B95D-A913-4DFC-9365-E2278D8A3DB6}">
+    <comment ref="J21" authorId="0" shapeId="0" xr:uid="{6EED2700-CFD2-4D9E-B68C-E4240B0225EF}">
       <text>
         <r>
           <rPr>
@@ -1018,7 +1018,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E22" authorId="0" shapeId="0" xr:uid="{FEE82DD2-6BF4-45FC-846A-FD790F7AF1D7}">
+    <comment ref="E22" authorId="0" shapeId="0" xr:uid="{BCDE9ECF-EEC2-491C-B371-899E6E54D8F7}">
       <text>
         <r>
           <rPr>
@@ -1032,7 +1032,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G22" authorId="0" shapeId="0" xr:uid="{A4237826-262C-4E3B-AC49-C793FB3378BB}">
+    <comment ref="G22" authorId="0" shapeId="0" xr:uid="{529A996D-C0FB-495C-AF75-57108372A047}">
       <text>
         <r>
           <rPr>
@@ -1046,7 +1046,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H22" authorId="0" shapeId="0" xr:uid="{757BE362-3657-4242-BED6-D93D811FD40D}">
+    <comment ref="H22" authorId="0" shapeId="0" xr:uid="{1D8EC8B4-C9FA-4F50-A117-77F2D8BB4B9F}">
       <text>
         <r>
           <rPr>
@@ -1060,7 +1060,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{E6DB27C2-3C6A-45B1-BDD8-397A67C57F03}">
+    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{CC757A20-B0D2-4BDD-9EB5-58C5135156C6}">
       <text>
         <r>
           <rPr>
@@ -1074,7 +1074,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J22" authorId="0" shapeId="0" xr:uid="{733DBFAB-7943-48FD-880D-318DE4E594F3}">
+    <comment ref="J22" authorId="0" shapeId="0" xr:uid="{9A901DC6-8D69-4006-BE26-49D41A1D6EFB}">
       <text>
         <r>
           <rPr>
@@ -1088,7 +1088,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D23" authorId="0" shapeId="0" xr:uid="{ECE4520F-8C6F-4969-8C53-4A4F3C3741FE}">
+    <comment ref="D23" authorId="0" shapeId="0" xr:uid="{2B4B74E6-BDC8-49E3-AB6F-109BFED3DEBB}">
       <text>
         <r>
           <rPr>
@@ -1102,7 +1102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E23" authorId="0" shapeId="0" xr:uid="{098C9AF8-B868-4DF9-9351-5DE09413B905}">
+    <comment ref="E23" authorId="0" shapeId="0" xr:uid="{12B0AEB4-B882-436C-919C-43E1F6CA62C9}">
       <text>
         <r>
           <rPr>
@@ -1117,7 +1117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G23" authorId="0" shapeId="0" xr:uid="{7DECEEE8-32A8-4977-B091-32AAE401C6A3}">
+    <comment ref="G23" authorId="0" shapeId="0" xr:uid="{865B9357-FA6C-4974-8C90-DDD45639A287}">
       <text>
         <r>
           <rPr>
@@ -1131,7 +1131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{C339DD1B-8651-4BC6-BCF2-50A509EEBC4E}">
+    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{11079701-3CB7-424E-9224-25029338DD44}">
       <text>
         <r>
           <rPr>
@@ -1145,7 +1145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{C833E7A6-EB43-41A8-977C-FAE15475356F}">
+    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{319A6C11-4520-4732-8796-56CD60FDB2EA}">
       <text>
         <r>
           <rPr>
@@ -1159,7 +1159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J23" authorId="0" shapeId="0" xr:uid="{18254D99-888D-4D14-AFB0-9B8462444F69}">
+    <comment ref="J23" authorId="0" shapeId="0" xr:uid="{780BD32B-BFC5-441D-96E4-2E04CD6C7CBC}">
       <text>
         <r>
           <rPr>
@@ -1174,7 +1174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C25" authorId="0" shapeId="0" xr:uid="{7643AF0D-04A3-4117-AB92-0C8BA1EED955}">
+    <comment ref="C25" authorId="0" shapeId="0" xr:uid="{06BBBAC6-094A-4494-94ED-414566540E5D}">
       <text>
         <r>
           <rPr>
@@ -1188,7 +1188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E25" authorId="0" shapeId="0" xr:uid="{A61DC354-B155-4312-9F46-B250C29E4CCB}">
+    <comment ref="E25" authorId="0" shapeId="0" xr:uid="{6E6CD7EA-1C67-423A-8229-41ACE3CD4BB0}">
       <text>
         <r>
           <rPr>
@@ -1202,7 +1202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0" xr:uid="{94645F02-7DCA-49B2-B641-F687E0E8A8EB}">
+    <comment ref="F25" authorId="0" shapeId="0" xr:uid="{D33C6B88-F365-4389-85EF-E2F917A0BA17}">
       <text>
         <r>
           <rPr>
@@ -1216,7 +1216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G25" authorId="0" shapeId="0" xr:uid="{4E4FAD99-D00C-4779-A9E8-86E8768FF8F8}">
+    <comment ref="G25" authorId="0" shapeId="0" xr:uid="{CE9143E9-90E4-4987-87EF-F3E8FCEEFEAF}">
       <text>
         <r>
           <rPr>
@@ -1230,7 +1230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{D5E30882-C15B-42BA-A18D-2DD4A89E03FD}">
+    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{00B96307-8AC0-4215-963A-47CE280C941E}">
       <text>
         <r>
           <rPr>
@@ -1244,7 +1244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0" xr:uid="{D09A999A-2AAB-4E98-84AD-29D5AA37F61A}">
+    <comment ref="J25" authorId="0" shapeId="0" xr:uid="{D10A8545-BCE0-4479-A86E-3AAAB169072A}">
       <text>
         <r>
           <rPr>
@@ -1263,7 +1263,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="175">
   <si>
     <t>Marketing Ownership Map - RACI Matrix (Working Draft)</t>
   </si>
@@ -1307,7 +1307,7 @@
     <t>PMM</t>
   </si>
   <si>
-    <t>TBD</t>
+    <t>Heather Pepe, Michelle Hendley, Hira Saeed, Michael Decker</t>
   </si>
   <si>
     <t>R</t>
@@ -1322,6 +1322,9 @@
     <t>Demand Gen</t>
   </si>
   <si>
+    <t>Gar Smith, Stephanie McPhee, Charlie Kleiner</t>
+  </si>
+  <si>
     <t>I</t>
   </si>
   <si>
@@ -1334,7 +1337,7 @@
     <t>Analytics &amp; Ops</t>
   </si>
   <si>
-    <t>Tihomir Radev (web analytics), Joe Grabmeier (marketing ops)</t>
+    <t>Lynn Tan, Tihomir Radev</t>
   </si>
   <si>
     <t>PRODUCTION</t>
@@ -1343,18 +1346,21 @@
     <t>Content / Writers</t>
   </si>
   <si>
-    <t>Soumya Ghosh</t>
+    <t>Nathan Wahl</t>
   </si>
   <si>
     <t>Creative</t>
   </si>
   <si>
-    <t>Soumya Ghosh, Jasmin Mora</t>
+    <t>Jenny Lui</t>
   </si>
   <si>
     <t>SEO</t>
   </si>
   <si>
+    <t>Tom South</t>
+  </si>
+  <si>
     <t>Web</t>
   </si>
   <si>
@@ -1367,27 +1373,51 @@
     <t>Social</t>
   </si>
   <si>
+    <t>Tory Waldron, Sarah Rich, Colin Holgan</t>
+  </si>
+  <si>
     <t>Community</t>
   </si>
   <si>
+    <t>Caroline Eglert</t>
+  </si>
+  <si>
     <t>PR / Comms</t>
   </si>
   <si>
+    <t>Tory Waldron</t>
+  </si>
+  <si>
     <t>Email / Lifecycle</t>
   </si>
   <si>
+    <t>Lynn Tann</t>
+  </si>
+  <si>
     <t>Paid Media</t>
   </si>
   <si>
+    <t>Raul Martins</t>
+  </si>
+  <si>
     <t>Events</t>
   </si>
   <si>
+    <t>Lindsey Speidel</t>
+  </si>
+  <si>
     <t>Customer Marketing</t>
   </si>
   <si>
+    <t>Caroline Eglert, Meaghan Nichols</t>
+  </si>
+  <si>
     <t>Partner Marketing</t>
   </si>
   <si>
+    <t>Meaghan Nichols</t>
+  </si>
+  <si>
     <t>?</t>
   </si>
   <si>
@@ -1395,6 +1425,9 @@
   </si>
   <si>
     <t>Program Management</t>
+  </si>
+  <si>
+    <t>Luiza Rusinova, Soumya Ghosh</t>
   </si>
   <si>
     <t>OPEN CONFLICTS - NEEDS DISCUSSION</t>
@@ -1761,7 +1794,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1812,14 +1845,6 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF898781"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1977,7 +2002,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1986,26 +2011,25 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2013,24 +2037,24 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2296,7 +2320,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E115-48AA-845F-72CA8532EAD5}"/>
+              <c16:uniqueId val="{00000000-D468-41F5-BD81-2D150BADEADE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2309,11 +2333,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="1228154255"/>
-        <c:axId val="1228143215"/>
+        <c:axId val="1480255792"/>
+        <c:axId val="1480245712"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1228154255"/>
+        <c:axId val="1480255792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2356,7 +2380,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1228143215"/>
+        <c:crossAx val="1480245712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2364,7 +2388,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1228143215"/>
+        <c:axId val="1480245712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2415,7 +2439,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1228154255"/>
+        <c:crossAx val="1480255792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2638,7 +2662,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-11B7-4F08-A6B6-542BC157F652}"/>
+              <c16:uniqueId val="{00000000-AC4F-4A36-97C7-8B31F1AA5EDE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2652,11 +2676,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1228144175"/>
-        <c:axId val="1228155695"/>
+        <c:axId val="1480252912"/>
+        <c:axId val="1480247152"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1228144175"/>
+        <c:axId val="1480252912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2699,7 +2723,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1228155695"/>
+        <c:crossAx val="1480247152"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2707,7 +2731,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1228155695"/>
+        <c:axId val="1480247152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2758,7 +2782,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1228144175"/>
+        <c:crossAx val="1480252912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3922,7 +3946,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F195B0E6-E084-56D8-3499-A629DDA0D881}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{628E7048-07B3-D9A3-AC58-6E93E3F8B46A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3958,7 +3982,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C45A7353-E1E1-F1C0-BE37-85E98AE171E7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{398B62D7-F564-8594-BA55-71B7D9E88455}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3980,17 +4004,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8B795265-6F7F-45B4-856B-86B5D46961A2}" name="OwnershipData" displayName="OwnershipData" ref="A1:H137" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:H137" xr:uid="{8B795265-6F7F-45B4-856B-86B5D46961A2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B4DFD34F-77E3-407B-9ECB-4ED4255F30F0}" name="OwnershipData" displayName="OwnershipData" ref="A1:H137" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:H137" xr:uid="{B4DFD34F-77E3-407B-9ECB-4ED4255F30F0}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{CAC6BE6E-384D-4DB1-ABAF-8E69584BEB36}" name="Team"/>
-    <tableColumn id="2" xr3:uid="{842AE0D5-52C6-47E1-A5F7-DB498D201137}" name="Team Group"/>
-    <tableColumn id="3" xr3:uid="{86B0B20C-77BD-48B1-BDE2-432AEF0A1E0B}" name="Who"/>
-    <tableColumn id="4" xr3:uid="{F1882486-E4F5-439B-96F8-65BD40A4B0B2}" name="Stage"/>
-    <tableColumn id="5" xr3:uid="{327B85A8-4AA2-4805-9F09-D970019A98B9}" name="RACI"/>
-    <tableColumn id="6" xr3:uid="{1B54FCDD-5B34-43D5-9758-4B6815EEF858}" name="Note"/>
-    <tableColumn id="7" xr3:uid="{F248F9E9-35FF-42DD-B5CF-15C55D86AD05}" name="Conflict"/>
-    <tableColumn id="8" xr3:uid="{C21D8BDA-2C12-4B49-8C25-A49F76B41EF5}" name="Conflict Note"/>
+    <tableColumn id="1" xr3:uid="{B9EF1F69-65F4-493A-8A4B-0A54E83C314A}" name="Team"/>
+    <tableColumn id="2" xr3:uid="{858001F8-B347-4BF3-9238-20E299AEC610}" name="Team Group"/>
+    <tableColumn id="3" xr3:uid="{A31087B8-68FB-40CE-AC40-A75DF457DE9B}" name="Who"/>
+    <tableColumn id="4" xr3:uid="{0E457DD0-B46F-4420-8F1E-8870F259B53A}" name="Stage"/>
+    <tableColumn id="5" xr3:uid="{56FAA244-28BB-4FA3-BF57-8C08C2EBDE6A}" name="RACI"/>
+    <tableColumn id="6" xr3:uid="{85760AEF-C0C9-476A-BCBE-295A4B0B0866}" name="Note"/>
+    <tableColumn id="7" xr3:uid="{78AD7CF9-2EA3-4A3D-A0FA-9187FB47143C}" name="Conflict"/>
+    <tableColumn id="8" xr3:uid="{C4C8EFC9-FEB1-4E40-8BAF-4D8440704A6B}" name="Conflict Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4312,7 +4336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9F8B12F-EA7A-48EE-8726-EA0F1FA68FAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70A489AD-4DDD-4622-A71F-CC7D1D665555}">
   <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -4324,35 +4348,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.3" x14ac:dyDescent="0.85">
-      <c r="A1" s="19" t="s">
-        <v>157</v>
+      <c r="A1" s="18" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="20" t="s">
-        <v>158</v>
+      <c r="A2" s="19" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="1.4">
-      <c r="A4" s="21">
+      <c r="A4" s="20">
         <v>17</v>
       </c>
-      <c r="B4" s="23">
+      <c r="B4" s="22">
         <v>8</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="24">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>161</v>
+      <c r="A5" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -4360,13 +4384,13 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I8" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="J8" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -4399,7 +4423,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F11" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G11">
         <v>3</v>
@@ -4413,7 +4437,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -4427,7 +4451,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F13" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -4441,7 +4465,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -4455,7 +4479,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -4469,7 +4493,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -4483,7 +4507,7 @@
     </row>
     <row r="17" spans="6:7" x14ac:dyDescent="0.55000000000000004">
       <c r="F17" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -4491,7 +4515,7 @@
     </row>
     <row r="18" spans="6:7" x14ac:dyDescent="0.55000000000000004">
       <c r="F18" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -4499,7 +4523,7 @@
     </row>
     <row r="19" spans="6:7" x14ac:dyDescent="0.55000000000000004">
       <c r="F19" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -4507,7 +4531,7 @@
     </row>
     <row r="20" spans="6:7" x14ac:dyDescent="0.55000000000000004">
       <c r="F20" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -4515,7 +4539,7 @@
     </row>
     <row r="21" spans="6:7" x14ac:dyDescent="0.55000000000000004">
       <c r="F21" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -4523,7 +4547,7 @@
     </row>
     <row r="22" spans="6:7" x14ac:dyDescent="0.55000000000000004">
       <c r="F22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -4531,7 +4555,7 @@
     </row>
     <row r="23" spans="6:7" x14ac:dyDescent="0.55000000000000004">
       <c r="F23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -4539,7 +4563,7 @@
     </row>
     <row r="24" spans="6:7" x14ac:dyDescent="0.55000000000000004">
       <c r="F24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -4547,7 +4571,7 @@
     </row>
     <row r="25" spans="6:7" x14ac:dyDescent="0.55000000000000004">
       <c r="F25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -4560,7 +4584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA70993-4979-4865-9980-B48630E2EC0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{066AAA2B-C07C-4CB2-AB30-85AA3DD73DAB}">
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -4612,18 +4636,18 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
@@ -4662,13 +4686,13 @@
         <v>18</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>15</v>
@@ -4677,10 +4701,10 @@
         <v>16</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>15</v>
@@ -4691,10 +4715,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="12" t="s">
         <v>21</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>16</v>
@@ -4715,36 +4739,36 @@
         <v>17</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="12" t="s">
         <v>23</v>
       </c>
+      <c r="B9" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="C9" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>16</v>
@@ -4754,37 +4778,37 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
+      <c r="A10" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="12" t="s">
         <v>26</v>
       </c>
+      <c r="B11" s="6" t="s">
+        <v>27</v>
+      </c>
       <c r="C11" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>15</v>
@@ -4793,30 +4817,30 @@
         <v>16</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="12" t="s">
         <v>28</v>
       </c>
+      <c r="B12" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="C12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>15</v>
@@ -4825,21 +4849,21 @@
         <v>16</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>16</v>
@@ -4848,7 +4872,7 @@
         <v>16</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>15</v>
@@ -4857,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>16</v>
@@ -4865,22 +4889,22 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>15</v>
@@ -4896,37 +4920,37 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
+      <c r="A15" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>15</v>
@@ -4943,22 +4967,22 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>15</v>
@@ -4975,13 +4999,13 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>16</v>
@@ -4990,7 +5014,7 @@
         <v>16</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>15</v>
@@ -5007,22 +5031,22 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>15</v>
@@ -5039,22 +5063,22 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>16</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>15</v>
@@ -5071,22 +5095,22 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>15</v>
@@ -5103,22 +5127,22 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>15</v>
@@ -5135,22 +5159,22 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>15</v>
@@ -5162,35 +5186,35 @@
         <v>15</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
+      <c r="A24" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="5" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>16</v>
@@ -5212,65 +5236,65 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A28" s="13" t="s">
-        <v>44</v>
+      <c r="A28" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
+      <c r="A29" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
     </row>
     <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
+      <c r="A30" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
     </row>
     <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
+      <c r="A31" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
     </row>
     <row r="32" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
+      <c r="A32" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5289,13 +5313,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E361310-1D56-43AA-8C5A-02430011C8CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F8F183-0888-4E35-ACCC-4B4021D90D9F}">
   <dimension ref="A1:H137"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="17.9453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.62890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.68359375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.3125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.05078125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.7890625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="45.578125" customWidth="1"/>
@@ -5308,25 +5332,25 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5334,22 +5358,22 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5357,48 +5381,48 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="G3" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="14" t="s">
+      <c r="B4" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>65</v>
+      <c r="F4" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5406,48 +5430,48 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
       </c>
       <c r="F5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="G5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>70</v>
+      <c r="D6" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5455,22 +5479,22 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="G7" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5478,22 +5502,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="G8" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5501,22 +5525,22 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5524,22 +5548,22 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5547,45 +5571,45 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" s="14" t="s">
+      <c r="D12" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>79</v>
+      <c r="F12" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5593,22 +5617,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5616,19 +5640,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5636,19 +5660,19 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5656,22 +5680,22 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -5679,2656 +5703,2656 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="G19" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
         <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="G20" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="14" t="s">
+      <c r="B22" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>88</v>
+      <c r="F22" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G23" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E28" t="s">
         <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G28" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E32" t="s">
         <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="G32" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
       </c>
       <c r="F33" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G33" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" t="s">
         <v>68</v>
       </c>
-      <c r="C34" t="s">
-        <v>26</v>
-      </c>
-      <c r="D34" t="s">
-        <v>57</v>
-      </c>
       <c r="E34" t="s">
         <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="G34" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G36" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" t="s">
+        <v>105</v>
+      </c>
+      <c r="G37" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D37" t="s">
-        <v>66</v>
-      </c>
-      <c r="E37" t="s">
-        <v>19</v>
-      </c>
-      <c r="F37" t="s">
-        <v>94</v>
-      </c>
-      <c r="G37" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E38" s="14" t="s">
+      <c r="B38" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F38" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>96</v>
+      <c r="F38" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E39" t="s">
         <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G39" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G41" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" t="s">
         <v>68</v>
       </c>
-      <c r="C42" t="s">
-        <v>28</v>
-      </c>
-      <c r="D42" t="s">
-        <v>57</v>
-      </c>
       <c r="E42" t="s">
         <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="G42" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D43" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G44" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G45" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
       </c>
       <c r="F46" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G46" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D47" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E47" t="s">
         <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G47" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D48" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G48" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C49" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D49" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G49" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50" t="s">
         <v>68</v>
       </c>
-      <c r="C50" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50" t="s">
-        <v>57</v>
-      </c>
       <c r="E50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G50" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B51" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E51" t="s">
         <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G51" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D52" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E52" t="s">
         <v>16</v>
       </c>
       <c r="F52" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G52" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C53" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D53" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F53" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="G53" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C54" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D54" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
       </c>
       <c r="F54" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="G54" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E55" t="s">
         <v>16</v>
       </c>
       <c r="F55" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="G55" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C56" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D56" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C57" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E57" t="s">
         <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G57" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B58" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" t="s">
         <v>68</v>
       </c>
-      <c r="C58" t="s">
-        <v>31</v>
-      </c>
-      <c r="D58" t="s">
-        <v>57</v>
-      </c>
       <c r="E58" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D59" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E59" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D60" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E60" t="s">
         <v>16</v>
       </c>
       <c r="F60" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G60" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D61" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D62" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
       </c>
       <c r="F62" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="G62" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D63" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E63" t="s">
         <v>16</v>
       </c>
       <c r="F63" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G63" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D64" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
       </c>
       <c r="F64" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="G64" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D65" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E65" t="s">
         <v>16</v>
       </c>
       <c r="F65" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="G65" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B66" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D66" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B67" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D67" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E67" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G67" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B68" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D68" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E68" t="s">
         <v>16</v>
       </c>
       <c r="F68" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="G68" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B69" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D69" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G69" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B70" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D70" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
       </c>
       <c r="F70" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="G70" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B71" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D71" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E71" t="s">
         <v>16</v>
       </c>
       <c r="G71" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B72" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D72" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
       </c>
       <c r="F72" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="G72" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B73" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D73" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E73" t="s">
         <v>16</v>
       </c>
       <c r="F73" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="G73" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B74" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C74" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D74" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E74" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G74" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B75" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D75" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E75" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B76" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D76" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E76" t="s">
         <v>16</v>
       </c>
       <c r="F76" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="G76" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B77" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C77" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D77" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G77" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B78" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D78" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
       </c>
       <c r="F78" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="G78" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B79" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D79" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E79" t="s">
         <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B80" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D80" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E80" t="s">
         <v>15</v>
       </c>
       <c r="F80" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="G80" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B81" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D81" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E81" t="s">
         <v>16</v>
       </c>
       <c r="F81" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="G81" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B82" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D82" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G82" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B83" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C83" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D83" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E83" t="s">
         <v>16</v>
       </c>
       <c r="F83" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G83" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B84" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C84" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D84" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E84" t="s">
         <v>16</v>
       </c>
       <c r="F84" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="G84" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B85" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C85" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D85" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E85" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G85" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B86" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C86" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D86" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E86" t="s">
         <v>15</v>
       </c>
       <c r="F86" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G86" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B87" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C87" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D87" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E87" t="s">
         <v>17</v>
       </c>
       <c r="F87" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="G87" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B88" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C88" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D88" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
       </c>
       <c r="F88" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G88" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B89" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C89" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D89" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E89" t="s">
         <v>16</v>
       </c>
       <c r="F89" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G89" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D90" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E90" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G90" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B91" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C91" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D91" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E91" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G91" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B92" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C92" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D92" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E92" t="s">
         <v>16</v>
       </c>
       <c r="F92" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G92" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B93" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C93" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D93" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E93" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G93" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B94" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C94" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D94" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E94" t="s">
         <v>15</v>
       </c>
       <c r="F94" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="G94" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B95" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C95" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D95" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E95" t="s">
         <v>16</v>
       </c>
       <c r="G95" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B96" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C96" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D96" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E96" t="s">
         <v>15</v>
       </c>
       <c r="F96" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="G96" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B97" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C97" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D97" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E97" t="s">
         <v>16</v>
       </c>
       <c r="F97" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G97" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B98" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C98" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E98" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G98" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B99" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C99" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E99" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G99" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B100" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C100" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E100" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F100" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="G100" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H100" s="14" t="s">
-        <v>130</v>
+      <c r="A100" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G100" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H100" s="13" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B101" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C101" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D101" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E101" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G101" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B102" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C102" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D102" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E102" t="s">
         <v>15</v>
       </c>
       <c r="F102" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="G102" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B103" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C103" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D103" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E103" t="s">
         <v>16</v>
       </c>
       <c r="F103" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G103" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B104" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C104" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D104" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E104" t="s">
         <v>15</v>
       </c>
       <c r="F104" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G104" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B105" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C105" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D105" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E105" t="s">
         <v>15</v>
       </c>
       <c r="F105" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="G105" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B106" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C106" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D106" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E106" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F106" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="G106" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B107" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C107" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D107" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E107" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G107" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B108" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C108" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D108" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E108" t="s">
         <v>16</v>
       </c>
       <c r="F108" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="G108" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B109" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C109" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D109" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E109" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G109" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C110" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D110" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E110" t="s">
         <v>15</v>
       </c>
       <c r="F110" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="G110" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C111" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D111" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E111" t="s">
         <v>16</v>
       </c>
       <c r="F111" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G111" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B112" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C112" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D112" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E112" t="s">
         <v>15</v>
       </c>
       <c r="F112" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="G112" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B113" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C113" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D113" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E113" t="s">
         <v>15</v>
       </c>
       <c r="F113" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="G113" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B114" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C114" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D114" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E114" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G114" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B115" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C115" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D115" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E115" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G115" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B116" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C116" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D116" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E116" t="s">
         <v>16</v>
       </c>
       <c r="F116" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="G116" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B117" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D117" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E117" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G117" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B118" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C118" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D118" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E118" t="s">
         <v>15</v>
       </c>
       <c r="F118" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="G118" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B119" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C119" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D119" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E119" t="s">
         <v>16</v>
       </c>
       <c r="F119" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G119" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B120" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C120" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D120" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E120" t="s">
         <v>15</v>
       </c>
       <c r="F120" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G120" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B121" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C121" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D121" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E121" t="s">
         <v>15</v>
       </c>
       <c r="F121" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="G121" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B122" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C122" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D122" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E122" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G122" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B123" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C123" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D123" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E123" t="s">
         <v>16</v>
       </c>
       <c r="F123" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G123" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B124" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C124" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D124" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E124" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F124" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="G124" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H124" s="14" t="s">
-        <v>145</v>
+      <c r="A124" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D124" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F124" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G124" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H124" s="13" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B125" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C125" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D125" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E125" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G125" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B126" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C126" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D126" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E126" t="s">
         <v>15</v>
       </c>
       <c r="F126" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="G126" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B127" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C127" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D127" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E127" t="s">
         <v>16</v>
       </c>
       <c r="F127" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="G127" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B128" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="D128" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E128" t="s">
         <v>15</v>
       </c>
       <c r="F128" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="G128" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A129" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B129" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C129" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D129" s="14" t="s">
+      <c r="A129" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B129" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D129" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E129" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F129" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="G129" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E129" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="F129" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="G129" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H129" s="14" t="s">
-        <v>149</v>
+      <c r="H129" s="13" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B130" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C130" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D130" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E130" t="s">
         <v>17</v>
       </c>
       <c r="F130" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="G130" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B131" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C131" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D131" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E131" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G131" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B132" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C132" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D132" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E132" t="s">
         <v>16</v>
       </c>
       <c r="F132" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="G132" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B133" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C133" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D133" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E133" t="s">
         <v>15</v>
       </c>
       <c r="F133" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="G133" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B134" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C134" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D134" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E134" t="s">
         <v>16</v>
       </c>
       <c r="F134" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="G134" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B135" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C135" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D135" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E135" t="s">
         <v>16</v>
       </c>
       <c r="G135" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B136" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C136" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D136" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E136" t="s">
         <v>17</v>
       </c>
       <c r="F136" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="G136" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B137" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C137" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="D137" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E137" t="s">
         <v>15</v>
       </c>
       <c r="F137" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="G137" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/marketing-ownership-map.xlsx
+++ b/marketing-ownership-map.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LRUSIN~1\AppData\Local\Temp\claude\c--Users-lrusinova-OneDrive---QuickBase-Documents-Project-Management-MCP\abf0f386-0ae7-411b-800d-e81e7586b212\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804F8EB9-DE6B-45CF-9EC8-13B68BADB024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA708C2-042D-4FF9-B4C2-97C5AB71F5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{6BE01299-3AA2-44C9-B560-36F384A9188D}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{6BE01299-3AA2-44C9-B560-36F384A9188D}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="3" r:id="rId1"/>
-    <sheet name="Ownership Matrix" sheetId="1" r:id="rId2"/>
-    <sheet name="Data" sheetId="2" r:id="rId3"/>
+    <sheet name="Project Type Guide" sheetId="4" r:id="rId2"/>
+    <sheet name="Ownership Matrix" sheetId="1" r:id="rId3"/>
+    <sheet name="Data" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1263,7 +1264,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="210">
   <si>
     <t>Marketing Ownership Map - RACI Matrix (Working Draft)</t>
   </si>
@@ -1788,13 +1789,118 @@
   </si>
   <si>
     <t>Active Teams</t>
+  </si>
+  <si>
+    <t>Project Type Guide - How Much of the Process Applies</t>
+  </si>
+  <si>
+    <t>The Ownership Matrix's 8 stages are built around a full Launch. Most other project types only need some of them - this shows how much of each stage actually applies, so you're not running the full process for a one-off creative request or a blog post.</t>
+  </si>
+  <si>
+    <t>Project Type</t>
+  </si>
+  <si>
+    <t>What's different</t>
+  </si>
+  <si>
+    <t>Launch (Product/Feature)</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>The baseline - this is what the RACI's 8 stages are built around.</t>
+  </si>
+  <si>
+    <t>New Standalone Landing Page</t>
+  </si>
+  <si>
+    <t>Light</t>
+  </si>
+  <si>
+    <t>Skip</t>
+  </si>
+  <si>
+    <t>Skips Activation Planning entirely - this isn't a campaign, just a page.</t>
+  </si>
+  <si>
+    <t>Content-Only Piece</t>
+  </si>
+  <si>
+    <t>Lightest of all types - mostly just Content + SEO, skip most cross-team stages.</t>
+  </si>
+  <si>
+    <t>Existing Page Update</t>
+  </si>
+  <si>
+    <t>Smallest footprint - often just Web, no content pipeline unless copy changes.</t>
+  </si>
+  <si>
+    <t>Creative-Only Request</t>
+  </si>
+  <si>
+    <t>No campaign machinery - just Creative, with conditional Brand sign-off.</t>
+  </si>
+  <si>
+    <t>Campaign (non-launch)</t>
+  </si>
+  <si>
+    <t>Activation Planning and Post-Launch reporting are the heart of this one - Positioning is usually inherited, not created fresh.</t>
+  </si>
+  <si>
+    <t>Event / Webinar</t>
+  </si>
+  <si>
+    <t>Runs mostly independent of launch machinery unless explicitly tied to one.</t>
+  </si>
+  <si>
+    <t>PR / Thought Leadership</t>
+  </si>
+  <si>
+    <t>Positioning &amp; Narrative and Review &amp; Approval carry more weight here - Brand's involvement is central, not optional.</t>
+  </si>
+  <si>
+    <t>Community Platform Build</t>
+  </si>
+  <si>
+    <t>Mostly a Production-and-Launch exercise - no activation planning or centralized brief since it's usually one BU.</t>
+  </si>
+  <si>
+    <t>Partner Co-Marketing Asset</t>
+  </si>
+  <si>
+    <t>Activation Planning here is really the unresolved routing/attribution question, not classic channel planning.</t>
+  </si>
+  <si>
+    <t>SEO Technical Work</t>
+  </si>
+  <si>
+    <t>No content or creative involvement at all - purely SEO (+Web if it touches a live page).</t>
+  </si>
+  <si>
+    <t>Email / Lifecycle Campaign</t>
+  </si>
+  <si>
+    <t>Similar shape to Campaign but single-channel - no activation-planning decision since the channel is already fixed.</t>
+  </si>
+  <si>
+    <t>Legend:</t>
+  </si>
+  <si>
+    <t>full stage applies</t>
+  </si>
+  <si>
+    <t>lighter/partial involvement</t>
+  </si>
+  <si>
+    <t>does not apply for this project type</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1918,6 +2024,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF082521"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF363432"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF898781"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2002,7 +2137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2029,14 +2164,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2057,6 +2184,22 @@
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4348,34 +4491,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.3" x14ac:dyDescent="0.85">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="14" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="15" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="1.4">
-      <c r="A4" s="20">
+      <c r="A4" s="16">
         <v>17</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="18">
         <v>8</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="20">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="21" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4584,6 +4727,474 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77218B90-BED6-42B1-9427-0EA34C679710}">
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="26.578125" customWidth="1"/>
+    <col min="2" max="9" width="14.578125" customWidth="1"/>
+    <col min="10" max="10" width="55.578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="18.3" x14ac:dyDescent="0.7">
+      <c r="A1" s="27" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="J14" s="28" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" t="s">
+        <v>209</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{066AAA2B-C07C-4CB2-AB30-85AA3DD73DAB}">
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
@@ -4636,18 +5247,18 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
@@ -4778,18 +5389,18 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
@@ -4920,18 +5531,18 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
@@ -5190,18 +5801,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="5" t="s">
@@ -5241,60 +5852,60 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
     </row>
     <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
     </row>
     <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
     </row>
     <row r="32" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5312,7 +5923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F8F183-0888-4E35-ACCC-4B4021D90D9F}">
   <dimension ref="A1:H137"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>

--- a/marketing-ownership-map.xlsx
+++ b/marketing-ownership-map.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LRUSIN~1\AppData\Local\Temp\claude\c--Users-lrusinova-OneDrive---QuickBase-Documents-Project-Management-MCP\abf0f386-0ae7-411b-800d-e81e7586b212\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA708C2-042D-4FF9-B4C2-97C5AB71F5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F973499D-1305-4FED-922A-1E69E2EB9B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{6BE01299-3AA2-44C9-B560-36F384A9188D}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{6BE01299-3AA2-44C9-B560-36F384A9188D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Executive Summary" sheetId="3" r:id="rId1"/>
+    <sheet name="Executive Summary" sheetId="5" r:id="rId1"/>
     <sheet name="Project Type Guide" sheetId="4" r:id="rId2"/>
     <sheet name="Ownership Matrix" sheetId="1" r:id="rId3"/>
     <sheet name="Data" sheetId="2" r:id="rId4"/>
@@ -1264,7 +1264,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="217">
   <si>
     <t>Marketing Ownership Map - RACI Matrix (Working Draft)</t>
   </si>
@@ -1773,9 +1773,6 @@
     <t>Marketing Ownership Map - Executive Summary</t>
   </si>
   <si>
-    <t>For SLT review - see Ownership Matrix tab for full detail, Data tab for the filterable flat view</t>
-  </si>
-  <si>
     <t>Teams mapped across the launch process</t>
   </si>
   <si>
@@ -1894,13 +1891,37 @@
   </si>
   <si>
     <t>does not apply for this project type</t>
+  </si>
+  <si>
+    <t>For SLT review - see Project Type Guide for how this scales down for smaller work, Ownership Matrix for full detail, Data tab for the filterable flat view</t>
+  </si>
+  <si>
+    <t>Last updated: August 7, 2026</t>
+  </si>
+  <si>
+    <t>Project types mapped (see Project Type Guide)</t>
+  </si>
+  <si>
+    <t>1. Activation Planning: PMM vs. Demand Gen - both show R, no agreed Accountable.</t>
+  </si>
+  <si>
+    <t>2. Production: PMM vs. Brand/Positioning vs. Content - messaging/copy ownership unresolved. The single biggest open question on the board.</t>
+  </si>
+  <si>
+    <t>3. Paid Media vs. Demand Gen - unclear whether paid activation is a Demand Gen sub-decision or owned directly by Paid Media.</t>
+  </si>
+  <si>
+    <t>4. Partner Marketing - routing/attribution ownership open; Channel Leader role not yet filled.</t>
+  </si>
+  <si>
+    <t>Supporting detail</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2053,6 +2074,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF898781"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2137,7 +2166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2184,6 +2213,14 @@
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2192,14 +2229,14 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2323,7 +2360,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Executive Summary'!$G$8</c:f>
+              <c:f>'Executive Summary'!$G$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2344,7 +2381,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Executive Summary'!$F$9:$F$25</c:f>
+              <c:f>'Executive Summary'!$F$16:$F$32</c:f>
               <c:strCache>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
@@ -2403,7 +2440,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Executive Summary'!$G$9:$G$25</c:f>
+              <c:f>'Executive Summary'!$G$16:$G$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
@@ -2463,7 +2500,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D468-41F5-BD81-2D150BADEADE}"/>
+              <c16:uniqueId val="{00000000-2C28-4F63-B6FE-34DC79C9D6EF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2476,11 +2513,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="1480255792"/>
-        <c:axId val="1480245712"/>
+        <c:axId val="1927333471"/>
+        <c:axId val="1927334911"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1480255792"/>
+        <c:axId val="1927333471"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2523,7 +2560,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1480245712"/>
+        <c:crossAx val="1927334911"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2531,7 +2568,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1480245712"/>
+        <c:axId val="1927334911"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2582,7 +2619,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1480255792"/>
+        <c:crossAx val="1927333471"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2719,7 +2756,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Executive Summary'!$J$8</c:f>
+              <c:f>'Executive Summary'!$J$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2740,7 +2777,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Executive Summary'!$I$9:$I$16</c:f>
+              <c:f>'Executive Summary'!$I$16:$I$23</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -2772,7 +2809,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Executive Summary'!$J$9:$J$16</c:f>
+              <c:f>'Executive Summary'!$J$16:$J$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -2805,7 +2842,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AC4F-4A36-97C7-8B31F1AA5EDE}"/>
+              <c16:uniqueId val="{00000000-C445-44B9-9506-258870A7B0D5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2819,11 +2856,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1480252912"/>
-        <c:axId val="1480247152"/>
+        <c:axId val="1927329631"/>
+        <c:axId val="1927327711"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1480252912"/>
+        <c:axId val="1927329631"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2866,7 +2903,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1480247152"/>
+        <c:crossAx val="1927327711"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2874,7 +2911,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1480247152"/>
+        <c:axId val="1927327711"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2925,7 +2962,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1480252912"/>
+        <c:crossAx val="1927329631"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4071,17 +4108,17 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1267460</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:colOff>1557020</xdr:colOff>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>111760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4089,7 +4126,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{628E7048-07B3-D9A3-AC58-6E93E3F8B46A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{845C40EB-1E42-C301-DC15-FD3BE36BB47D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4107,17 +4144,17 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>176530</xdr:colOff>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>372110</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1356360</xdr:colOff>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>111760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4125,7 +4162,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{398B62D7-F564-8594-BA55-71B7D9E88455}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{159423BA-7770-BD58-022E-CAF199A7DB9D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4479,11 +4516,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70A489AD-4DDD-4622-A71F-CC7D1D665555}">
-  <dimension ref="A1:J25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A4A1782-B0F0-4A80-B5B0-6DF2F503376B}">
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="3" width="24.578125" customWidth="1"/>
+    <col min="1" max="4" width="22.578125" customWidth="1"/>
     <col min="6" max="6" width="20.578125" customWidth="1"/>
     <col min="7" max="7" width="10.578125" customWidth="1"/>
     <col min="9" max="9" width="26.578125" customWidth="1"/>
@@ -4497,230 +4534,289 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="32" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="1.4">
+      <c r="A5" s="16">
+        <v>17</v>
+      </c>
+      <c r="B5" s="18">
+        <v>8</v>
+      </c>
+      <c r="C5" s="33">
+        <v>12</v>
+      </c>
+      <c r="D5" s="20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="17" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="1.4">
-      <c r="A4" s="16">
-        <v>17</v>
-      </c>
-      <c r="B4" s="18">
-        <v>8</v>
-      </c>
-      <c r="C4" s="20">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="17" t="s">
+      <c r="B6" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="C6" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="C5" s="21" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="F8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I8" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-      <c r="I9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-      <c r="I10" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="F11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11">
-        <v>3</v>
-      </c>
-      <c r="I11" t="s">
-        <v>6</v>
-      </c>
-      <c r="J11">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="F12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12">
-        <v>3</v>
-      </c>
-      <c r="I12" t="s">
-        <v>7</v>
-      </c>
-      <c r="J12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="F13" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-      <c r="I13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13">
-        <v>15</v>
-      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A8" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+    </row>
+    <row r="10" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+    </row>
+    <row r="11" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+    </row>
+    <row r="12" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="F14" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-      <c r="I14" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14">
-        <v>15</v>
+      <c r="A14" s="35" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G15">
         <v>2</v>
       </c>
+      <c r="G15" t="s">
+        <v>172</v>
+      </c>
       <c r="I15" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15">
-        <v>13</v>
+        <v>62</v>
+      </c>
+      <c r="J15" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F16" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J16">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.55000000000000004">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="6:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F17" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="6:7" x14ac:dyDescent="0.55000000000000004">
+        <v>3</v>
+      </c>
+      <c r="I17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="6:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F18" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="6:7" x14ac:dyDescent="0.55000000000000004">
+        <v>3</v>
+      </c>
+      <c r="I18" t="s">
+        <v>6</v>
+      </c>
+      <c r="J18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="6:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="6:7" x14ac:dyDescent="0.55000000000000004">
+        <v>3</v>
+      </c>
+      <c r="I19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="6:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="6:7" x14ac:dyDescent="0.55000000000000004">
+        <v>3</v>
+      </c>
+      <c r="I20" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="6:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F21" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="G21">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="6:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="I21" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="6:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="I22" t="s">
+        <v>10</v>
+      </c>
+      <c r="J22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="6:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="F23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="I23" t="s">
+        <v>11</v>
+      </c>
+      <c r="J23">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="6:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="F24" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="6:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="F25" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="6:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="F26" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="6:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="F27" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="6:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="F28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="6:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="F29" t="s">
         <v>23</v>
       </c>
-      <c r="G22">
+      <c r="G29">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="6:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F23" t="s">
+    <row r="30" spans="6:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="F30" t="s">
         <v>26</v>
       </c>
-      <c r="G23">
+      <c r="G30">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="6:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F24" t="s">
+    <row r="31" spans="6:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="F31" t="s">
         <v>28</v>
       </c>
-      <c r="G24">
+      <c r="G31">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="6:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="F25" t="s">
+    <row r="32" spans="6:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="F32" t="s">
         <v>30</v>
       </c>
-      <c r="G25">
+      <c r="G32">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -4737,18 +4833,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A1" s="27" t="s">
-        <v>175</v>
+      <c r="A1" s="23" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>4</v>
@@ -4775,418 +4871,418 @@
         <v>11</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J5" s="24" t="s">
         <v>180</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="J5" s="28" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="J6" s="24" t="s">
         <v>184</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="J7" s="24" t="s">
         <v>186</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="J7" s="28" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="J8" s="24" t="s">
         <v>188</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="J8" s="28" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="J9" s="24" t="s">
         <v>190</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="J9" s="28" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J10" s="24" t="s">
         <v>192</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="J10" s="28" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J11" s="24" t="s">
         <v>194</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="J11" s="28" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="J12" s="24" t="s">
         <v>196</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="J12" s="28" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="J13" s="24" t="s">
         <v>198</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="J13" s="28" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="J14" s="24" t="s">
         <v>200</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="J14" s="28" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="J15" s="24" t="s">
         <v>202</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="J15" s="28" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J16" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="G16" s="8" t="s">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="C18" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="C19" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="J16" s="28" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="C18" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>208</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="C20" t="s">
-        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -5247,18 +5343,18 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
@@ -5389,18 +5485,18 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
@@ -5531,18 +5627,18 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
@@ -5801,18 +5897,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="5" t="s">
@@ -5852,60 +5948,60 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
     </row>
     <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
     </row>
     <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
     </row>
     <row r="32" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
-      <c r="J32" s="23"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/marketing-ownership-map.xlsx
+++ b/marketing-ownership-map.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LRUSIN~1\AppData\Local\Temp\claude\c--Users-lrusinova-OneDrive---QuickBase-Documents-Project-Management-MCP\abf0f386-0ae7-411b-800d-e81e7586b212\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F973499D-1305-4FED-922A-1E69E2EB9B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674B75B3-42B8-4763-AFB8-98EE3F4FD91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{6BE01299-3AA2-44C9-B560-36F384A9188D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Executive Summary" sheetId="5" r:id="rId1"/>
-    <sheet name="Project Type Guide" sheetId="4" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="7" r:id="rId1"/>
+    <sheet name="Project Type Guide" sheetId="6" r:id="rId2"/>
     <sheet name="Ownership Matrix" sheetId="1" r:id="rId3"/>
     <sheet name="Data" sheetId="2" r:id="rId4"/>
   </sheets>
@@ -1264,7 +1264,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="221">
   <si>
     <t>Marketing Ownership Map - RACI Matrix (Working Draft)</t>
   </si>
@@ -1915,6 +1915,18 @@
   </si>
   <si>
     <t>Supporting detail</t>
+  </si>
+  <si>
+    <t>Customer Story / Case Study</t>
+  </si>
+  <si>
+    <t>Unlike other content, needs the customer's own sign-off before it can publish - that approval loop is the real bottleneck, not internal review.</t>
+  </si>
+  <si>
+    <t>Sales Enablement Asset</t>
+  </si>
+  <si>
+    <t>Internal-facing, not customer-facing - no public launch execution; PMM usually owns it start to finish with light Content/Creative polish.</t>
   </si>
 </sst>
 </file>
@@ -2221,6 +2233,14 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2229,14 +2249,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2500,7 +2512,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2C28-4F63-B6FE-34DC79C9D6EF}"/>
+              <c16:uniqueId val="{00000000-3138-4869-849D-DFD151A334E8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2513,11 +2525,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="1927333471"/>
-        <c:axId val="1927334911"/>
+        <c:axId val="238520911"/>
+        <c:axId val="238529551"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1927333471"/>
+        <c:axId val="238520911"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2560,7 +2572,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1927334911"/>
+        <c:crossAx val="238529551"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2568,7 +2580,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1927334911"/>
+        <c:axId val="238529551"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2619,7 +2631,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1927333471"/>
+        <c:crossAx val="238520911"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2842,7 +2854,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C445-44B9-9506-258870A7B0D5}"/>
+              <c16:uniqueId val="{00000000-EB42-41D5-B9A3-28F8F7FCC5DC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2856,11 +2868,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="1927329631"/>
-        <c:axId val="1927327711"/>
+        <c:axId val="238530031"/>
+        <c:axId val="238518511"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1927329631"/>
+        <c:axId val="238530031"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2903,7 +2915,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1927327711"/>
+        <c:crossAx val="238518511"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2911,7 +2923,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1927327711"/>
+        <c:axId val="238518511"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2962,7 +2974,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1927329631"/>
+        <c:crossAx val="238530031"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4126,7 +4138,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{845C40EB-1E42-C301-DC15-FD3BE36BB47D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8478AF3D-B0EE-5D9F-96D8-E71C7A4B4CC9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4162,7 +4174,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{159423BA-7770-BD58-022E-CAF199A7DB9D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{818AF01E-6438-916D-1A02-191DF4C7D4E8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4516,7 +4528,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A4A1782-B0F0-4A80-B5B0-6DF2F503376B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC05E435-C543-472B-BA10-01E2880EEBEB}">
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -4538,7 +4550,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="28" t="s">
         <v>210</v>
       </c>
     </row>
@@ -4549,8 +4561,8 @@
       <c r="B5" s="18">
         <v>8</v>
       </c>
-      <c r="C5" s="33">
-        <v>12</v>
+      <c r="C5" s="29">
+        <v>14</v>
       </c>
       <c r="D5" s="20">
         <v>4</v>
@@ -4563,7 +4575,7 @@
       <c r="B6" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="30" t="s">
         <v>211</v>
       </c>
       <c r="D6" s="21" t="s">
@@ -4576,39 +4588,39 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
     </row>
     <row r="10" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
     </row>
     <row r="11" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
     </row>
     <row r="12" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="31" t="s">
         <v>216</v>
       </c>
     </row>
@@ -4823,8 +4835,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77218B90-BED6-42B1-9427-0EA34C679710}">
-  <dimension ref="A1:J20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A099D435-D650-43CE-A7D2-53BDD00EBC1E}">
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="26.578125" customWidth="1"/>
@@ -5258,30 +5270,94 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="22" t="s">
+    <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B20" s="25" t="s">
         <v>179</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C20" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="26" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C21" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="27" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C22" t="s">
         <v>208</v>
       </c>
     </row>
@@ -5343,18 +5419,18 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
@@ -5485,18 +5561,18 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
@@ -5627,18 +5703,18 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
@@ -5897,18 +5973,18 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="5" t="s">
@@ -5948,60 +6024,60 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
     </row>
     <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
     </row>
     <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="29"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
     </row>
     <row r="32" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/marketing-ownership-map.xlsx
+++ b/marketing-ownership-map.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LRUSIN~1\AppData\Local\Temp\claude\c--Users-lrusinova-OneDrive---QuickBase-Documents-Project-Management-MCP\abf0f386-0ae7-411b-800d-e81e7586b212\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674B75B3-42B8-4763-AFB8-98EE3F4FD91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B02C43F-0DD0-4BE7-85A2-444C4797CC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{6BE01299-3AA2-44C9-B560-36F384A9188D}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{D9A43224-3FE6-4782-BEE1-41A45989FA1C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Executive Summary" sheetId="7" r:id="rId1"/>
-    <sheet name="Project Type Guide" sheetId="6" r:id="rId2"/>
+    <sheet name="Executive Summary" sheetId="4" r:id="rId1"/>
+    <sheet name="Project Type Guide" sheetId="3" r:id="rId2"/>
     <sheet name="Ownership Matrix" sheetId="1" r:id="rId3"/>
     <sheet name="Data" sheetId="2" r:id="rId4"/>
   </sheets>
@@ -47,7 +47,7 @@
     <author>Rusinova, Luiza</author>
   </authors>
   <commentList>
-    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{BAB04E11-E01F-4118-84D7-5F13012659D1}">
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{0218A692-7723-44DB-A43C-CDF3807E48D4}">
       <text>
         <r>
           <rPr>
@@ -61,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{D3F167C3-553D-4F51-B41A-3774D0F2097E}">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{3836F39A-C352-4723-8659-9567689D56A8}">
       <text>
         <r>
           <rPr>
@@ -75,7 +75,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{D1C72457-2918-49DA-B32D-328B621ECDA1}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{B9D46037-A0AE-42EE-880C-2DEC6612E149}">
       <text>
         <r>
           <rPr>
@@ -90,7 +90,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{A18B08CA-E4B8-4F2B-9481-F871476B38C9}">
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{1AA1B79C-C884-47DB-8505-9B21DA06D4E4}">
       <text>
         <r>
           <rPr>
@@ -104,7 +104,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G6" authorId="0" shapeId="0" xr:uid="{5C0144C2-A9B0-4B6E-9BD9-4B1621C476E2}">
+    <comment ref="G6" authorId="0" shapeId="0" xr:uid="{87879CBE-8D30-437D-9BC4-C49F4FED17E1}">
       <text>
         <r>
           <rPr>
@@ -119,7 +119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{469E6ABC-E10B-411B-9542-2B8DA935CABF}">
+    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{780C00C2-7BE1-4D60-A508-12DF338194C7}">
       <text>
         <r>
           <rPr>
@@ -133,7 +133,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{DB7B26AE-03F3-4C85-A806-20AB014279A1}">
+    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{8B4A2CEF-BFE9-45FA-8CD1-ADF48DD5ABE4}">
       <text>
         <r>
           <rPr>
@@ -147,7 +147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="0" shapeId="0" xr:uid="{C60F9F14-A735-4807-9321-5ECB348502FE}">
+    <comment ref="J6" authorId="0" shapeId="0" xr:uid="{DC4D30ED-0D1F-4045-A3A9-C1A88818684B}">
       <text>
         <r>
           <rPr>
@@ -161,7 +161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{1FD10B2F-6D27-4426-B98C-EA76901E1365}">
+    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{3B927DDE-9AEE-44D9-9360-FEF96441284D}">
       <text>
         <r>
           <rPr>
@@ -175,7 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{8090B464-0FF5-4C53-A54C-273AEA6FC384}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{5B00C449-93FE-41FF-9C7E-2CC6BA04DD4B}">
       <text>
         <r>
           <rPr>
@@ -190,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{64C3D2BB-B6C1-40A1-8324-FC0A37D160A8}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{AA8D2F59-004E-4C70-BA25-71C0A83152A1}">
       <text>
         <r>
           <rPr>
@@ -204,7 +204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{3FBDE4D7-3442-4B00-AF5D-2CD67B161FC9}">
+    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{50BC8400-2346-4431-8350-F3ABB5FAB396}">
       <text>
         <r>
           <rPr>
@@ -218,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{2BDC43F2-0940-489C-B32A-D2D08AB7BED7}">
+    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{750FB0CD-279C-4805-9936-D80B780CAF55}">
       <text>
         <r>
           <rPr>
@@ -232,7 +232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{C609FCB9-EEC5-4C6E-8E0C-F1E8A2BFC828}">
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{7A544A3A-985A-46AC-A60F-5D826EED7D42}">
       <text>
         <r>
           <rPr>
@@ -246,7 +246,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{CB2734AF-0CEA-428E-94F5-CFF09597CC8E}">
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{A080AFFB-C17F-42CF-86EF-959C7E3F1459}">
       <text>
         <r>
           <rPr>
@@ -260,7 +260,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{4D8ED339-95D6-434E-B24F-787333C1EE7B}">
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{C4E9B6B1-AEE1-45C4-A7A9-94346A1B8309}">
       <text>
         <r>
           <rPr>
@@ -274,7 +274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{FB406B22-1174-408F-BD67-CE9D0EF3601C}">
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{F74A40CE-6DD3-4BCC-A679-027C8E22E5AE}">
       <text>
         <r>
           <rPr>
@@ -288,7 +288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{F7D7397A-0BCB-4A53-AF77-F157AE764E31}">
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{35791E69-B3A6-441C-82E9-FD327DE3C6C8}">
       <text>
         <r>
           <rPr>
@@ -303,7 +303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{82D527DE-C892-4004-A20F-0E22C35CB7DD}">
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{44E4CC0F-E3D8-4DB7-B8A8-B5FCC5EB28E7}">
       <text>
         <r>
           <rPr>
@@ -317,7 +317,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{1B7F7F27-5C2A-471F-A774-BDDFD099AA7E}">
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{2230C867-FD9F-4D7F-958D-17C8B5CCC50E}">
       <text>
         <r>
           <rPr>
@@ -331,7 +331,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{2999E64B-6FE6-43B0-B9AF-5453C2C733FE}">
+    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{6FFA8626-00BA-4582-991D-51B0AE5B924F}">
       <text>
         <r>
           <rPr>
@@ -345,7 +345,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="0" shapeId="0" xr:uid="{64EA06BF-A8C7-4C32-B3C2-B446820B1183}">
+    <comment ref="J9" authorId="0" shapeId="0" xr:uid="{8F727813-4E6D-4811-9D45-DE013953693B}">
       <text>
         <r>
           <rPr>
@@ -359,7 +359,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{351CE4CB-5539-4C96-BCAD-CF1430ADADEB}">
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{56ACFF81-BB15-4C8A-A2ED-79766F8CBDB7}">
       <text>
         <r>
           <rPr>
@@ -373,7 +373,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{A1980C4C-A314-40ED-8D5B-A783F93CD60B}">
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{99B1C7CD-8D7F-4EDB-83C2-1D06C6EA4BAE}">
       <text>
         <r>
           <rPr>
@@ -387,7 +387,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{860D7150-E2A5-46E1-95C5-16712C27A4F1}">
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{8DE5E960-C906-42A9-A525-3FFDF7367203}">
       <text>
         <r>
           <rPr>
@@ -402,7 +402,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{09572632-D062-4673-9D61-1CE15F6E768F}">
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{B00B3C29-D2D8-412C-982E-21AE870EDE84}">
       <text>
         <r>
           <rPr>
@@ -416,7 +416,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{D29097A2-A8F1-4846-AF57-54D1CD695227}">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{223BB65A-19C1-47EE-A508-57E3FACA1EBA}">
       <text>
         <r>
           <rPr>
@@ -430,7 +430,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{8A6A7456-A543-4A63-A452-06BB33A214C9}">
+    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{0DA7DD26-00E8-4958-8B2F-EDD5E42B5E26}">
       <text>
         <r>
           <rPr>
@@ -444,7 +444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{2F353211-B85B-4140-8355-A58127BD373E}">
+    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{05A21C5A-3325-4F79-B4BC-963463101F18}">
       <text>
         <r>
           <rPr>
@@ -458,7 +458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{3F963966-445B-404A-8D20-091E2DC8E888}">
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{39D59A9A-3461-4A12-865D-09EA4F1917E8}">
       <text>
         <r>
           <rPr>
@@ -472,7 +472,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{A900AE41-2839-4C08-A8AA-EBC7FCD5AE27}">
+    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{DD213551-BC5F-4500-80C4-A2FBF7755013}">
       <text>
         <r>
           <rPr>
@@ -486,7 +486,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{579E7184-2533-4115-83E6-78B9DEE61FFD}">
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{8F11CC63-5280-4893-8973-7E529B0F4E77}">
       <text>
         <r>
           <rPr>
@@ -500,7 +500,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{5F1D4EF9-CAC2-4D94-83AE-CCD28A91135A}">
+    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{170EDEE2-0C14-4BC6-9744-0A0E8146CBE3}">
       <text>
         <r>
           <rPr>
@@ -514,7 +514,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="0" shapeId="0" xr:uid="{8FB00AF5-0D62-4E79-A02F-18CE5849E43A}">
+    <comment ref="H13" authorId="0" shapeId="0" xr:uid="{E7B2D3A9-35E6-49F4-8A6C-A0C9BD89D197}">
       <text>
         <r>
           <rPr>
@@ -528,7 +528,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J13" authorId="0" shapeId="0" xr:uid="{6D43A919-0D72-4AAA-BDA0-08D868574998}">
+    <comment ref="J13" authorId="0" shapeId="0" xr:uid="{C45D489A-A369-468E-A36B-C7BDBD0A9B78}">
       <text>
         <r>
           <rPr>
@@ -542,7 +542,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{BBBD1169-C60E-4E5B-BEA4-92849CE0A736}">
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{46727065-FDA2-4C20-856E-8E9C52F116DB}">
       <text>
         <r>
           <rPr>
@@ -556,7 +556,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{19D31EF5-A25A-4411-B00A-9028B89941A3}">
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{FCD0B9F1-CCE5-414D-B082-6C85E59690C4}">
       <text>
         <r>
           <rPr>
@@ -570,7 +570,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{CC1883E9-B48E-4B90-B843-0A6D2E67320D}">
+    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{2401683D-2BBB-4BEE-8B7C-4C43A75627FF}">
       <text>
         <r>
           <rPr>
@@ -584,7 +584,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{AD51A3FF-3DEB-48D7-9C05-C576DB2B8A31}">
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{6E61ED2D-B219-4715-B353-654CC8FB9E49}">
       <text>
         <r>
           <rPr>
@@ -598,7 +598,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{D9F5B064-F1DD-41E7-B76D-7E6DCA41A63D}">
+    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{E7D30DBA-32B8-489B-BDBD-755B35AC43F3}">
       <text>
         <r>
           <rPr>
@@ -612,7 +612,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0" shapeId="0" xr:uid="{7C14BC21-B56C-44A1-8A8F-2B10F3C32F91}">
+    <comment ref="E16" authorId="0" shapeId="0" xr:uid="{74767246-8894-4E6A-BCC3-826D4429B486}">
       <text>
         <r>
           <rPr>
@@ -626,7 +626,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{9E6DFAFE-D66E-4BD2-8BE7-6618171629D1}">
+    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{480DEC5B-65AB-46D7-A658-A82E005851E3}">
       <text>
         <r>
           <rPr>
@@ -640,7 +640,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{F57F7327-8223-409F-8E68-7D9220AE4782}">
+    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{DB251BBC-33BE-4F18-BDA4-CB146A050BE7}">
       <text>
         <r>
           <rPr>
@@ -654,7 +654,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J16" authorId="0" shapeId="0" xr:uid="{61C6CD16-2477-46AB-89FE-81C2C9FC4519}">
+    <comment ref="J16" authorId="0" shapeId="0" xr:uid="{46D63E66-BBCB-4D51-AABA-CBE2962C3065}">
       <text>
         <r>
           <rPr>
@@ -668,7 +668,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{1CCBA09D-2496-480B-BA6E-CB030F3F6707}">
+    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{3D69D7A2-7592-4CBE-8F52-9B83C0542AB9}">
       <text>
         <r>
           <rPr>
@@ -682,7 +682,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G17" authorId="0" shapeId="0" xr:uid="{255398D5-80A5-4CEF-9234-BF7FAE79E30B}">
+    <comment ref="G17" authorId="0" shapeId="0" xr:uid="{0B367BC9-2772-4AF7-A048-F1F65939D8AB}">
       <text>
         <r>
           <rPr>
@@ -696,7 +696,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{ADA45EB7-5789-41C2-A097-0F9D2224831D}">
+    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{64E1ADFB-F86D-48A8-9223-35A54A9D789B}">
       <text>
         <r>
           <rPr>
@@ -710,7 +710,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J17" authorId="0" shapeId="0" xr:uid="{AACA4D19-2F7C-47EB-AB52-950570862342}">
+    <comment ref="J17" authorId="0" shapeId="0" xr:uid="{8AF74B2A-52C3-40E2-8938-88A769350570}">
       <text>
         <r>
           <rPr>
@@ -724,7 +724,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{D1CBDFBA-0E22-46B5-AACD-919680D6F8A0}">
+    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{34E718FD-3636-4D39-B2BB-4FF9C93A435D}">
       <text>
         <r>
           <rPr>
@@ -738,7 +738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{AEFA6057-EE90-4F1C-B17C-C4AB5990A220}">
+    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{D94CFAEF-FBB8-45E7-9BD5-0E939B6F8A26}">
       <text>
         <r>
           <rPr>
@@ -752,7 +752,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{CF27BA6F-8718-454C-A3C2-7B1F1B2D43D7}">
+    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{01C5D719-4052-4359-8D80-DEAA8D86A91C}">
       <text>
         <r>
           <rPr>
@@ -766,7 +766,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{F062BF64-FE28-4DCA-B2D9-9A9250541D82}">
+    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{2BF6BCB1-F11A-4935-B075-CE20A880DAF0}">
       <text>
         <r>
           <rPr>
@@ -780,7 +780,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{33A5B5E1-C892-4D15-8586-6A1CA1527399}">
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{69FEB52C-1FDB-40DC-8A5E-D491ED7BDD48}">
       <text>
         <r>
           <rPr>
@@ -794,7 +794,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{B74871B0-A20F-41D1-9FDF-098C2F10614D}">
+    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{54B8448D-4C95-4AFD-A067-DAD828C1E106}">
       <text>
         <r>
           <rPr>
@@ -808,7 +808,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{6D18C7E2-A41A-46E0-847B-E5E331563F86}">
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{8237C414-BA88-4A3E-B084-7FEE0DC409FE}">
       <text>
         <r>
           <rPr>
@@ -822,7 +822,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G19" authorId="0" shapeId="0" xr:uid="{9ED6303B-2CB6-471D-BD25-630B79E93A8D}">
+    <comment ref="G19" authorId="0" shapeId="0" xr:uid="{3804D5E6-675A-4107-8459-7442E5738D67}">
       <text>
         <r>
           <rPr>
@@ -836,7 +836,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{1BDAD591-E21C-4A70-BB11-B6EE5FFCF387}">
+    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{88D897F4-7C6F-46EE-9429-5CA9DE78306D}">
       <text>
         <r>
           <rPr>
@@ -850,7 +850,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J19" authorId="0" shapeId="0" xr:uid="{BE529E6C-1F99-4712-94AE-0B7F205766AA}">
+    <comment ref="J19" authorId="0" shapeId="0" xr:uid="{DAA171BE-DDB7-464B-8C40-EE97497800E6}">
       <text>
         <r>
           <rPr>
@@ -864,7 +864,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{CBE8EED1-8C06-4241-9438-C26F190B609A}">
+    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{E7C06D9E-5457-4CB7-97C1-BE95537FA8C7}">
       <text>
         <r>
           <rPr>
@@ -879,7 +879,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{0F52992C-6346-4AC9-AA55-80C5FE5803B4}">
+    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{C553C9C5-5397-4BF7-9863-7A1C97125592}">
       <text>
         <r>
           <rPr>
@@ -893,7 +893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{2068A96C-0CD5-4947-B1E3-0A930466B02F}">
+    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{9E7C1238-D37B-49DB-A544-27AD10BC5083}">
       <text>
         <r>
           <rPr>
@@ -907,7 +907,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{E31432B3-3C37-4DCF-AE9A-B90F3F88A84B}">
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{DC324683-05A9-4B88-B540-4DF6198C356E}">
       <text>
         <r>
           <rPr>
@@ -921,7 +921,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{BC232B02-F26C-4E7F-8174-3D663B4DFBC8}">
+    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{0826A0B4-5215-4E3D-B98C-8F53811ED608}">
       <text>
         <r>
           <rPr>
@@ -935,7 +935,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{B1EA46D5-3C3A-43BA-847E-3852A1A60C9C}">
+    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{7B5ABC6A-3779-424A-9CB9-7F1A676C631E}">
       <text>
         <r>
           <rPr>
@@ -949,7 +949,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{868A23ED-530F-4B30-B610-31D544B8B0A2}">
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{4F00724C-4073-480D-8D4C-589D8D30AD95}">
       <text>
         <r>
           <rPr>
@@ -963,7 +963,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G21" authorId="0" shapeId="0" xr:uid="{1314B8BB-57AB-495E-B039-077ED9ECC548}">
+    <comment ref="G21" authorId="0" shapeId="0" xr:uid="{6F00C78B-943C-4C48-B6B5-0B9714EE486D}">
       <text>
         <r>
           <rPr>
@@ -977,7 +977,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{97076E4A-96E9-4192-B008-7609FF871335}">
+    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{34D2CB87-B33E-48D1-90FE-6A0F0915F9A0}">
       <text>
         <r>
           <rPr>
@@ -991,7 +991,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{138FBBD1-7C54-4BE5-B049-827CC041D5CE}">
+    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{A046FF26-9D99-4CA5-862F-075B310706BC}">
       <text>
         <r>
           <rPr>
@@ -1005,7 +1005,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J21" authorId="0" shapeId="0" xr:uid="{6EED2700-CFD2-4D9E-B68C-E4240B0225EF}">
+    <comment ref="J21" authorId="0" shapeId="0" xr:uid="{281F1181-1283-4CFE-B7CF-6111713B23BF}">
       <text>
         <r>
           <rPr>
@@ -1019,7 +1019,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E22" authorId="0" shapeId="0" xr:uid="{BCDE9ECF-EEC2-491C-B371-899E6E54D8F7}">
+    <comment ref="E22" authorId="0" shapeId="0" xr:uid="{F2240319-5F83-4ADF-8798-B4EC55672A83}">
       <text>
         <r>
           <rPr>
@@ -1033,7 +1033,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G22" authorId="0" shapeId="0" xr:uid="{529A996D-C0FB-495C-AF75-57108372A047}">
+    <comment ref="G22" authorId="0" shapeId="0" xr:uid="{EDDCBAE8-BD42-42A8-BD1E-FC79EBC5EB6C}">
       <text>
         <r>
           <rPr>
@@ -1047,7 +1047,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H22" authorId="0" shapeId="0" xr:uid="{1D8EC8B4-C9FA-4F50-A117-77F2D8BB4B9F}">
+    <comment ref="H22" authorId="0" shapeId="0" xr:uid="{4D424160-EDE6-4AB1-BE28-7F49CB2B6795}">
       <text>
         <r>
           <rPr>
@@ -1061,7 +1061,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{CC757A20-B0D2-4BDD-9EB5-58C5135156C6}">
+    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{C2B85560-B000-4317-9470-97A57CD6EAF5}">
       <text>
         <r>
           <rPr>
@@ -1075,7 +1075,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J22" authorId="0" shapeId="0" xr:uid="{9A901DC6-8D69-4006-BE26-49D41A1D6EFB}">
+    <comment ref="J22" authorId="0" shapeId="0" xr:uid="{DC74CD8E-0050-4F57-97EF-2C293A907E2A}">
       <text>
         <r>
           <rPr>
@@ -1089,7 +1089,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D23" authorId="0" shapeId="0" xr:uid="{2B4B74E6-BDC8-49E3-AB6F-109BFED3DEBB}">
+    <comment ref="D23" authorId="0" shapeId="0" xr:uid="{89EB78B4-BC9B-4482-B64D-316D4352F4EB}">
       <text>
         <r>
           <rPr>
@@ -1103,7 +1103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E23" authorId="0" shapeId="0" xr:uid="{12B0AEB4-B882-436C-919C-43E1F6CA62C9}">
+    <comment ref="E23" authorId="0" shapeId="0" xr:uid="{9A193541-6375-4BDB-A428-0CD6D424D849}">
       <text>
         <r>
           <rPr>
@@ -1113,12 +1113,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Partner-routing/activation ownership is still open.
-CONFLICT: Channel Leader role not yet filled - see Website Context Window brief open question on partner-routing ownership.</t>
+          <t>Owns partner-routing and activation decisions as Channel Leader.</t>
         </r>
       </text>
     </comment>
-    <comment ref="G23" authorId="0" shapeId="0" xr:uid="{865B9357-FA6C-4974-8C90-DDD45639A287}">
+    <comment ref="G23" authorId="0" shapeId="0" xr:uid="{DA2AFE56-1EBE-42CF-9B08-FC373FEA9C21}">
       <text>
         <r>
           <rPr>
@@ -1132,7 +1131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{11079701-3CB7-424E-9224-25029338DD44}">
+    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{A32ED967-FDDF-467E-AD25-5D92A2676D15}">
       <text>
         <r>
           <rPr>
@@ -1146,7 +1145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{319A6C11-4520-4732-8796-56CD60FDB2EA}">
+    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{89EB2FD9-E0C2-4A0E-93EB-7CFA5216D35B}">
       <text>
         <r>
           <rPr>
@@ -1160,7 +1159,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J23" authorId="0" shapeId="0" xr:uid="{780BD32B-BFC5-441D-96E4-2E04CD6C7CBC}">
+    <comment ref="J23" authorId="0" shapeId="0" xr:uid="{8986EFBA-4585-4B7F-8516-83350C817D29}">
       <text>
         <r>
           <rPr>
@@ -1170,12 +1169,11 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Partner-lead attribution and reporting ownership is unresolved.
-CONFLICT: Open question: Lynn Tan/RevOps vs. Partner Marketing - see Website Context Window brief.</t>
+          <t>Owns partner-lead attribution and reporting as Channel Leader.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C25" authorId="0" shapeId="0" xr:uid="{06BBBAC6-094A-4494-94ED-414566540E5D}">
+    <comment ref="C25" authorId="0" shapeId="0" xr:uid="{0D11C398-271C-4F94-A710-DC3A7848AEAC}">
       <text>
         <r>
           <rPr>
@@ -1189,7 +1187,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E25" authorId="0" shapeId="0" xr:uid="{6E6CD7EA-1C67-423A-8229-41ACE3CD4BB0}">
+    <comment ref="E25" authorId="0" shapeId="0" xr:uid="{D770439C-3364-439D-B290-6F1FB21408A9}">
       <text>
         <r>
           <rPr>
@@ -1203,7 +1201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0" xr:uid="{D33C6B88-F365-4389-85EF-E2F917A0BA17}">
+    <comment ref="F25" authorId="0" shapeId="0" xr:uid="{5DE5EC7D-0891-4BEE-BE66-3641632A3E5E}">
       <text>
         <r>
           <rPr>
@@ -1217,7 +1215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G25" authorId="0" shapeId="0" xr:uid="{CE9143E9-90E4-4987-87EF-F3E8FCEEFEAF}">
+    <comment ref="G25" authorId="0" shapeId="0" xr:uid="{B0C245F1-229B-4F6F-A438-03EB30A1FA17}">
       <text>
         <r>
           <rPr>
@@ -1231,7 +1229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{00B96307-8AC0-4215-963A-47CE280C941E}">
+    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{9364AAFC-02FE-46BA-8D85-036A5933C1A5}">
       <text>
         <r>
           <rPr>
@@ -1245,7 +1243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0" xr:uid="{D10A8545-BCE0-4479-A86E-3AAAB169072A}">
+    <comment ref="J25" authorId="0" shapeId="0" xr:uid="{B1D109B2-64C8-447C-ACA6-59B6C0CF6B41}">
       <text>
         <r>
           <rPr>
@@ -1264,7 +1262,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="216">
   <si>
     <t>Marketing Ownership Map - RACI Matrix (Working Draft)</t>
   </si>
@@ -1419,9 +1417,6 @@
     <t>Meaghan Nichols</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>ORCHESTRATION</t>
   </si>
   <si>
@@ -1443,9 +1438,6 @@
     <t>3. Paid Media vs. Demand Gen: Unclear whether paid activation is a Demand Gen sub-decision or owned directly by Paid Media. Both show involvement without a clear boundary.</t>
   </si>
   <si>
-    <t>4. Partner Marketing - routing and attribution ownership: (a) Partner-routing/activation ownership is unresolved - Channel Leader role not yet filled. (b) Post-launch, partner-lead attribution and reporting ownership is unresolved between Lynn Tan/RevOps and Partner Marketing.</t>
-  </si>
-  <si>
     <t>Team Group</t>
   </si>
   <si>
@@ -1731,10 +1723,7 @@
     <t>Weighs in on how positioning lands with the partner ecosystem.</t>
   </si>
   <si>
-    <t>Partner-routing/activation ownership is still open.</t>
-  </si>
-  <si>
-    <t>Channel Leader role not yet filled - see Website Context Window brief open question on partner-routing ownership.</t>
+    <t>Owns partner-routing and activation decisions as Channel Leader.</t>
   </si>
   <si>
     <t>Builds partner co-marketing and enablement assets.</t>
@@ -1743,10 +1732,7 @@
     <t>Executes partner enablement/co-marketing at launch.</t>
   </si>
   <si>
-    <t>Partner-lead attribution and reporting ownership is unresolved.</t>
-  </si>
-  <si>
-    <t>Open question: Lynn Tan/RevOps vs. Partner Marketing - see Website Context Window brief.</t>
+    <t>Owns partner-lead attribution and reporting as Channel Leader.</t>
   </si>
   <si>
     <t>Orchestration</t>
@@ -1770,163 +1756,160 @@
     <t>Runs the retro and compiles results.</t>
   </si>
   <si>
+    <t>Project Type Guide - How Much of the Process Applies</t>
+  </si>
+  <si>
+    <t>The Ownership Matrix's 8 stages are built around a full Launch. Most other project types only need some of them - this shows how much of each stage actually applies, so you're not running the full process for a one-off creative request or a blog post.</t>
+  </si>
+  <si>
+    <t>Project Type</t>
+  </si>
+  <si>
+    <t>What's different</t>
+  </si>
+  <si>
+    <t>Launch (Product/Feature)</t>
+  </si>
+  <si>
+    <t>Full</t>
+  </si>
+  <si>
+    <t>The baseline - this is what the RACI's 8 stages are built around.</t>
+  </si>
+  <si>
+    <t>New Standalone Landing Page</t>
+  </si>
+  <si>
+    <t>Light</t>
+  </si>
+  <si>
+    <t>Skip</t>
+  </si>
+  <si>
+    <t>Skips Activation Planning entirely - this isn't a campaign, just a page.</t>
+  </si>
+  <si>
+    <t>Content-Only Piece</t>
+  </si>
+  <si>
+    <t>Lightest of all types - mostly just Content + SEO, skip most cross-team stages.</t>
+  </si>
+  <si>
+    <t>Existing Page Update</t>
+  </si>
+  <si>
+    <t>Smallest footprint - often just Web, no content pipeline unless copy changes.</t>
+  </si>
+  <si>
+    <t>Creative-Only Request</t>
+  </si>
+  <si>
+    <t>No campaign machinery - just Creative, with conditional Brand sign-off.</t>
+  </si>
+  <si>
+    <t>Campaign (non-launch)</t>
+  </si>
+  <si>
+    <t>Activation Planning and Post-Launch reporting are the heart of this one - Positioning is usually inherited, not created fresh.</t>
+  </si>
+  <si>
+    <t>Event / Webinar</t>
+  </si>
+  <si>
+    <t>Runs mostly independent of launch machinery unless explicitly tied to one.</t>
+  </si>
+  <si>
+    <t>PR / Thought Leadership</t>
+  </si>
+  <si>
+    <t>Positioning &amp; Narrative and Review &amp; Approval carry more weight here - Brand's involvement is central, not optional.</t>
+  </si>
+  <si>
+    <t>Community Platform Build</t>
+  </si>
+  <si>
+    <t>Mostly a Production-and-Launch exercise - no activation planning or centralized brief since it's usually one BU.</t>
+  </si>
+  <si>
+    <t>Partner Co-Marketing Asset</t>
+  </si>
+  <si>
+    <t>Activation Planning here is really the unresolved routing/attribution question, not classic channel planning.</t>
+  </si>
+  <si>
+    <t>SEO Technical Work</t>
+  </si>
+  <si>
+    <t>No content or creative involvement at all - purely SEO (+Web if it touches a live page).</t>
+  </si>
+  <si>
+    <t>Email / Lifecycle Campaign</t>
+  </si>
+  <si>
+    <t>Similar shape to Campaign but single-channel - no activation-planning decision since the channel is already fixed.</t>
+  </si>
+  <si>
+    <t>Customer Story / Case Study</t>
+  </si>
+  <si>
+    <t>Unlike other content, needs the customer's own sign-off before it can publish - that approval loop is the real bottleneck, not internal review.</t>
+  </si>
+  <si>
+    <t>Sales Enablement Asset</t>
+  </si>
+  <si>
+    <t>Internal-facing, not customer-facing - no public launch execution; PMM usually owns it start to finish with light Content/Creative polish.</t>
+  </si>
+  <si>
+    <t>Legend:</t>
+  </si>
+  <si>
+    <t>full stage applies</t>
+  </si>
+  <si>
+    <t>lighter/partial involvement</t>
+  </si>
+  <si>
+    <t>does not apply for this project type</t>
+  </si>
+  <si>
     <t>Marketing Ownership Map - Executive Summary</t>
   </si>
   <si>
+    <t>For SLT review - see Project Type Guide for how this scales down for smaller work, Ownership Matrix for full detail, Data tab for the filterable flat view</t>
+  </si>
+  <si>
+    <t>Last updated: August 7, 2026</t>
+  </si>
+  <si>
     <t>Teams mapped across the launch process</t>
   </si>
   <si>
     <t>Process stages, Intake through Post-Launch</t>
   </si>
   <si>
+    <t>Project types mapped (see Project Type Guide)</t>
+  </si>
+  <si>
     <t>Open conflicts needing discussion</t>
   </si>
   <si>
+    <t>1. Activation Planning: PMM vs. Demand Gen - both show R, no agreed Accountable.</t>
+  </si>
+  <si>
+    <t>2. Production: PMM vs. Brand/Positioning vs. Content - messaging/copy ownership unresolved. The single biggest open question on the board.</t>
+  </si>
+  <si>
+    <t>3. Paid Media vs. Demand Gen - unclear whether paid activation is a Demand Gen sub-decision or owned directly by Paid Media.</t>
+  </si>
+  <si>
+    <t>Supporting detail</t>
+  </si>
+  <si>
     <t>R Count</t>
   </si>
   <si>
     <t>Active Teams</t>
-  </si>
-  <si>
-    <t>Project Type Guide - How Much of the Process Applies</t>
-  </si>
-  <si>
-    <t>The Ownership Matrix's 8 stages are built around a full Launch. Most other project types only need some of them - this shows how much of each stage actually applies, so you're not running the full process for a one-off creative request or a blog post.</t>
-  </si>
-  <si>
-    <t>Project Type</t>
-  </si>
-  <si>
-    <t>What's different</t>
-  </si>
-  <si>
-    <t>Launch (Product/Feature)</t>
-  </si>
-  <si>
-    <t>Full</t>
-  </si>
-  <si>
-    <t>The baseline - this is what the RACI's 8 stages are built around.</t>
-  </si>
-  <si>
-    <t>New Standalone Landing Page</t>
-  </si>
-  <si>
-    <t>Light</t>
-  </si>
-  <si>
-    <t>Skip</t>
-  </si>
-  <si>
-    <t>Skips Activation Planning entirely - this isn't a campaign, just a page.</t>
-  </si>
-  <si>
-    <t>Content-Only Piece</t>
-  </si>
-  <si>
-    <t>Lightest of all types - mostly just Content + SEO, skip most cross-team stages.</t>
-  </si>
-  <si>
-    <t>Existing Page Update</t>
-  </si>
-  <si>
-    <t>Smallest footprint - often just Web, no content pipeline unless copy changes.</t>
-  </si>
-  <si>
-    <t>Creative-Only Request</t>
-  </si>
-  <si>
-    <t>No campaign machinery - just Creative, with conditional Brand sign-off.</t>
-  </si>
-  <si>
-    <t>Campaign (non-launch)</t>
-  </si>
-  <si>
-    <t>Activation Planning and Post-Launch reporting are the heart of this one - Positioning is usually inherited, not created fresh.</t>
-  </si>
-  <si>
-    <t>Event / Webinar</t>
-  </si>
-  <si>
-    <t>Runs mostly independent of launch machinery unless explicitly tied to one.</t>
-  </si>
-  <si>
-    <t>PR / Thought Leadership</t>
-  </si>
-  <si>
-    <t>Positioning &amp; Narrative and Review &amp; Approval carry more weight here - Brand's involvement is central, not optional.</t>
-  </si>
-  <si>
-    <t>Community Platform Build</t>
-  </si>
-  <si>
-    <t>Mostly a Production-and-Launch exercise - no activation planning or centralized brief since it's usually one BU.</t>
-  </si>
-  <si>
-    <t>Partner Co-Marketing Asset</t>
-  </si>
-  <si>
-    <t>Activation Planning here is really the unresolved routing/attribution question, not classic channel planning.</t>
-  </si>
-  <si>
-    <t>SEO Technical Work</t>
-  </si>
-  <si>
-    <t>No content or creative involvement at all - purely SEO (+Web if it touches a live page).</t>
-  </si>
-  <si>
-    <t>Email / Lifecycle Campaign</t>
-  </si>
-  <si>
-    <t>Similar shape to Campaign but single-channel - no activation-planning decision since the channel is already fixed.</t>
-  </si>
-  <si>
-    <t>Legend:</t>
-  </si>
-  <si>
-    <t>full stage applies</t>
-  </si>
-  <si>
-    <t>lighter/partial involvement</t>
-  </si>
-  <si>
-    <t>does not apply for this project type</t>
-  </si>
-  <si>
-    <t>For SLT review - see Project Type Guide for how this scales down for smaller work, Ownership Matrix for full detail, Data tab for the filterable flat view</t>
-  </si>
-  <si>
-    <t>Last updated: August 7, 2026</t>
-  </si>
-  <si>
-    <t>Project types mapped (see Project Type Guide)</t>
-  </si>
-  <si>
-    <t>1. Activation Planning: PMM vs. Demand Gen - both show R, no agreed Accountable.</t>
-  </si>
-  <si>
-    <t>2. Production: PMM vs. Brand/Positioning vs. Content - messaging/copy ownership unresolved. The single biggest open question on the board.</t>
-  </si>
-  <si>
-    <t>3. Paid Media vs. Demand Gen - unclear whether paid activation is a Demand Gen sub-decision or owned directly by Paid Media.</t>
-  </si>
-  <si>
-    <t>4. Partner Marketing - routing/attribution ownership open; Channel Leader role not yet filled.</t>
-  </si>
-  <si>
-    <t>Supporting detail</t>
-  </si>
-  <si>
-    <t>Customer Story / Case Study</t>
-  </si>
-  <si>
-    <t>Unlike other content, needs the customer's own sign-off before it can publish - that approval loop is the real bottleneck, not internal review.</t>
-  </si>
-  <si>
-    <t>Sales Enablement Asset</t>
-  </si>
-  <si>
-    <t>Internal-facing, not customer-facing - no public launch execution; PMM usually owns it start to finish with light Content/Creative polish.</t>
   </si>
 </sst>
 </file>
@@ -2028,7 +2011,7 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color rgb="FF082521"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -2038,29 +2021,6 @@
       <i/>
       <sz val="10"/>
       <color rgb="FF898781"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="28"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF082521"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2087,9 +2047,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF082521"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF898781"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2205,42 +2188,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2249,6 +2205,33 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2372,7 +2355,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Executive Summary'!$G$15</c:f>
+              <c:f>'Executive Summary'!$G$14</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2393,44 +2376,44 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Executive Summary'!$F$16:$F$32</c:f>
+              <c:f>'Executive Summary'!$F$15:$F$31</c:f>
               <c:strCache>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
+                  <c:v>Partner Marketing</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>PMM</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>Demand Gen</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>Paid Media</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>Events</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Customer Marketing</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>Brand / Positioning</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>Web</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>Social</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>Community</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>PR / Comms</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>Email / Lifecycle</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Partner Marketing</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>Program Management</c:v>
@@ -2452,12 +2435,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Executive Summary'!$G$16:$G$32</c:f>
+              <c:f>'Executive Summary'!$G$15:$G$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>3</c:v>
@@ -2472,7 +2455,7 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2</c:v>
@@ -2512,7 +2495,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3138-4869-849D-DFD151A334E8}"/>
+              <c16:uniqueId val="{00000000-5AC8-483E-9504-660C3078434A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2525,11 +2508,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="238520911"/>
-        <c:axId val="238529551"/>
+        <c:axId val="994759711"/>
+        <c:axId val="994755391"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="238520911"/>
+        <c:axId val="994759711"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2572,7 +2555,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="238529551"/>
+        <c:crossAx val="994755391"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2580,7 +2563,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="238529551"/>
+        <c:axId val="994755391"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2631,7 +2614,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="238520911"/>
+        <c:crossAx val="994759711"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2768,7 +2751,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Executive Summary'!$J$15</c:f>
+              <c:f>'Executive Summary'!$J$14</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2789,7 +2772,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Executive Summary'!$I$16:$I$23</c:f>
+              <c:f>'Executive Summary'!$I$15:$I$22</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -2821,7 +2804,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Executive Summary'!$J$16:$J$23</c:f>
+              <c:f>'Executive Summary'!$J$15:$J$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -2832,7 +2815,7 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4</c:v>
@@ -2847,14 +2830,14 @@
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EB42-41D5-B9A3-28F8F7FCC5DC}"/>
+              <c16:uniqueId val="{00000000-8BBF-4137-83EC-17146A3E138B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2868,11 +2851,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="238530031"/>
-        <c:axId val="238518511"/>
+        <c:axId val="1061321343"/>
+        <c:axId val="1061320863"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="238530031"/>
+        <c:axId val="1061321343"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2915,7 +2898,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="238518511"/>
+        <c:crossAx val="1061320863"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2923,7 +2906,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="238518511"/>
+        <c:axId val="1061320863"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2974,7 +2957,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="238530031"/>
+        <c:crossAx val="1061321343"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4124,13 +4107,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1557020</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>111760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4138,7 +4121,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8478AF3D-B0EE-5D9F-96D8-E71C7A4B4CC9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D6F56E9-F41B-4555-0EA4-462EBBE492B0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4160,13 +4143,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>176530</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>1356360</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>111760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4174,7 +4157,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{818AF01E-6438-916D-1A02-191DF4C7D4E8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3480DB83-500B-E208-5DA0-A644FD89AE7E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4196,17 +4179,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B4DFD34F-77E3-407B-9ECB-4ED4255F30F0}" name="OwnershipData" displayName="OwnershipData" ref="A1:H137" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:H137" xr:uid="{B4DFD34F-77E3-407B-9ECB-4ED4255F30F0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2607C8CC-A66C-48FA-AE73-5225724582B4}" name="OwnershipData" displayName="OwnershipData" ref="A1:H137" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:H137" xr:uid="{2607C8CC-A66C-48FA-AE73-5225724582B4}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{B9EF1F69-65F4-493A-8A4B-0A54E83C314A}" name="Team"/>
-    <tableColumn id="2" xr3:uid="{858001F8-B347-4BF3-9238-20E299AEC610}" name="Team Group"/>
-    <tableColumn id="3" xr3:uid="{A31087B8-68FB-40CE-AC40-A75DF457DE9B}" name="Who"/>
-    <tableColumn id="4" xr3:uid="{0E457DD0-B46F-4420-8F1E-8870F259B53A}" name="Stage"/>
-    <tableColumn id="5" xr3:uid="{56FAA244-28BB-4FA3-BF57-8C08C2EBDE6A}" name="RACI"/>
-    <tableColumn id="6" xr3:uid="{85760AEF-C0C9-476A-BCBE-295A4B0B0866}" name="Note"/>
-    <tableColumn id="7" xr3:uid="{78AD7CF9-2EA3-4A3D-A0FA-9187FB47143C}" name="Conflict"/>
-    <tableColumn id="8" xr3:uid="{C4C8EFC9-FEB1-4E40-8BAF-4D8440704A6B}" name="Conflict Note"/>
+    <tableColumn id="1" xr3:uid="{C2FDC5A5-0AB7-4E88-B1B8-864681491C96}" name="Team"/>
+    <tableColumn id="2" xr3:uid="{5A236A8F-7B46-44C5-B27E-98ADE3D97C0E}" name="Team Group"/>
+    <tableColumn id="3" xr3:uid="{CE4B9929-C91B-4C53-8A1A-E38E0B9E8781}" name="Who"/>
+    <tableColumn id="4" xr3:uid="{584FC3C8-E436-4B27-B926-AD1B432BB987}" name="Stage"/>
+    <tableColumn id="5" xr3:uid="{ED7E12D3-58F3-4962-B3F5-5F25288A7B7A}" name="RACI"/>
+    <tableColumn id="6" xr3:uid="{C9E6ED22-A8BA-4677-B659-70806834915C}" name="Note"/>
+    <tableColumn id="7" xr3:uid="{7202C52B-E4A7-47CC-8ABA-10BC1E3C7E90}" name="Conflict"/>
+    <tableColumn id="8" xr3:uid="{0F6077CF-1D86-4250-AE82-90038E34EA44}" name="Conflict Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4528,8 +4511,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC05E435-C543-472B-BA10-01E2880EEBEB}">
-  <dimension ref="A1:J32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6175A65F-732C-45A3-9206-5B2A45E86CA6}">
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="4" width="22.578125" customWidth="1"/>
@@ -4540,102 +4523,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.3" x14ac:dyDescent="0.85">
-      <c r="A1" s="14" t="s">
-        <v>168</v>
+      <c r="A1" s="25" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="26" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="1.4">
+      <c r="A5" s="27">
+        <v>17</v>
+      </c>
+      <c r="B5" s="29">
+        <v>8</v>
+      </c>
+      <c r="C5" s="31">
+        <v>14</v>
+      </c>
+      <c r="D5" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="D6" s="34" t="s">
         <v>209</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="28" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="1.4">
-      <c r="A5" s="16">
-        <v>17</v>
-      </c>
-      <c r="B5" s="18">
-        <v>8</v>
-      </c>
-      <c r="C5" s="29">
-        <v>14</v>
-      </c>
-      <c r="D5" s="20">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A8" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+    </row>
+    <row r="10" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="11" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-    </row>
-    <row r="10" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="32" t="s">
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="35" t="s">
         <v>213</v>
       </c>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-    </row>
-    <row r="11" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="32" t="s">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="F14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
         <v>214</v>
       </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-    </row>
-    <row r="12" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="32" t="s">
+      <c r="I14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J14" t="s">
         <v>215</v>
-      </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="31" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F15" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" t="s">
-        <v>172</v>
+        <v>49</v>
+      </c>
+      <c r="G15">
+        <v>4</v>
       </c>
       <c r="I15" t="s">
-        <v>62</v>
-      </c>
-      <c r="J15" t="s">
-        <v>173</v>
+        <v>4</v>
+      </c>
+      <c r="J15">
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -4646,10 +4635,10 @@
         <v>3</v>
       </c>
       <c r="I16" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="6:10" x14ac:dyDescent="0.55000000000000004">
@@ -4660,10 +4649,10 @@
         <v>3</v>
       </c>
       <c r="I17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="6:10" x14ac:dyDescent="0.55000000000000004">
@@ -4674,10 +4663,10 @@
         <v>3</v>
       </c>
       <c r="I18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="6:10" x14ac:dyDescent="0.55000000000000004">
@@ -4688,10 +4677,10 @@
         <v>3</v>
       </c>
       <c r="I19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="6:10" x14ac:dyDescent="0.55000000000000004">
@@ -4702,7 +4691,7 @@
         <v>3</v>
       </c>
       <c r="I20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>15</v>
@@ -4716,10 +4705,10 @@
         <v>2</v>
       </c>
       <c r="I21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="6:10" x14ac:dyDescent="0.55000000000000004">
@@ -4730,10 +4719,10 @@
         <v>2</v>
       </c>
       <c r="I22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="6:10" x14ac:dyDescent="0.55000000000000004">
@@ -4743,12 +4732,6 @@
       <c r="G23">
         <v>2</v>
       </c>
-      <c r="I23" t="s">
-        <v>11</v>
-      </c>
-      <c r="J23">
-        <v>13</v>
-      </c>
     </row>
     <row r="24" spans="6:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F24" t="s">
@@ -4776,7 +4759,7 @@
     </row>
     <row r="27" spans="6:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F27" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -4784,15 +4767,15 @@
     </row>
     <row r="28" spans="6:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F28" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="6:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -4800,7 +4783,7 @@
     </row>
     <row r="30" spans="6:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -4808,26 +4791,17 @@
     </row>
     <row r="31" spans="6:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F31" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="6:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="F32" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4835,7 +4809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A099D435-D650-43CE-A7D2-53BDD00EBC1E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3A22337-C3CB-47A1-875E-F83DB399470F}">
   <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -4845,18 +4819,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A1" s="23" t="s">
-        <v>174</v>
+      <c r="A1" s="15" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="15" t="s">
-        <v>175</v>
+      <c r="A2" s="16" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="4" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>4</v>
@@ -4883,482 +4857,482 @@
         <v>11</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>180</v>
+        <v>169</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>184</v>
+        <v>172</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>186</v>
+        <v>173</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>188</v>
+        <v>173</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="J9" s="24" t="s">
-        <v>190</v>
+        <v>173</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E10" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="J10" s="17" t="s">
         <v>182</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>194</v>
+        <v>169</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>196</v>
+        <v>172</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="5" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="J13" s="24" t="s">
-        <v>198</v>
+        <v>172</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>200</v>
+        <v>173</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="5" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>202</v>
+        <v>172</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="J16" s="24" t="s">
-        <v>204</v>
+        <v>169</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="5" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="J17" s="24" t="s">
-        <v>218</v>
+        <v>172</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="5" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="J18" s="24" t="s">
-        <v>220</v>
+        <v>173</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>179</v>
+      <c r="A20" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>169</v>
       </c>
       <c r="C20" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="26" t="s">
-        <v>182</v>
+      <c r="B21" s="19" t="s">
+        <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="27" t="s">
-        <v>183</v>
+      <c r="B22" s="20" t="s">
+        <v>173</v>
       </c>
       <c r="C22" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -5367,8 +5341,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{066AAA2B-C07C-4CB2-AB30-85AA3DD73DAB}">
-  <dimension ref="A1:J32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1332399-AEE2-44C7-9163-AE5445FDA981}">
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="22.578125" customWidth="1"/>
@@ -5419,18 +5393,18 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5" t="s">
@@ -5561,18 +5535,18 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5" t="s">
@@ -5703,18 +5677,18 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="35"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="35"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5" t="s">
@@ -5953,8 +5927,8 @@
       <c r="D23" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>51</v>
+      <c r="E23" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>20</v>
@@ -5968,30 +5942,30 @@
       <c r="I23" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="J23" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="23" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="35"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>17</v>
@@ -6020,69 +5994,54 @@
     </row>
     <row r="28" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A28" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="21" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="32" t="s">
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+    </row>
+    <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-    </row>
-    <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="32" t="s">
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+    </row>
+    <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-    </row>
-    <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-    </row>
-    <row r="32" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A32:J32"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A15:J15"/>
@@ -6096,7 +6055,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98F8F183-0888-4E35-ACCC-4B4021D90D9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9672B321-6ED0-42E0-B5AA-3B170FFAC8FF}">
   <dimension ref="A1:H137"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -6115,25 +6074,25 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6141,22 +6100,22 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6164,22 +6123,22 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6187,25 +6146,25 @@
         <v>13</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="13" t="s">
         <v>74</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6213,22 +6172,22 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6236,25 +6195,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6262,22 +6221,22 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6285,22 +6244,22 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6308,22 +6267,22 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6331,22 +6290,22 @@
         <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6354,19 +6313,19 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6374,25 +6333,25 @@
         <v>18</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6400,22 +6359,22 @@
         <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6423,19 +6382,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6443,19 +6402,19 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
         <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6463,22 +6422,22 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
         <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6486,22 +6445,22 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
         <v>19</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
       </c>
       <c r="F17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6509,22 +6468,22 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
         <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6532,22 +6491,22 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
         <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6555,22 +6514,22 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
         <v>22</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
         <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6578,22 +6537,22 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
         <v>22</v>
       </c>
       <c r="D21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6601,25 +6560,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>22</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6627,22 +6586,22 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6650,19 +6609,19 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
         <v>22</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s">
         <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6670,19 +6629,19 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
         <v>22</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E25" t="s">
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6690,19 +6649,19 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
         <v>24</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E26" t="s">
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6710,19 +6669,19 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
         <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E27" t="s">
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6730,22 +6689,22 @@
         <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
         <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E28" t="s">
         <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6753,19 +6712,19 @@
         <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
         <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E29" t="s">
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6773,19 +6732,19 @@
         <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
         <v>24</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s">
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6793,19 +6752,19 @@
         <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s">
         <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E31" t="s">
         <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6813,22 +6772,22 @@
         <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C32" t="s">
         <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E32" t="s">
         <v>16</v>
       </c>
       <c r="F32" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G32" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6836,22 +6795,22 @@
         <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s">
         <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E33" t="s">
         <v>15</v>
       </c>
       <c r="F33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6859,22 +6818,22 @@
         <v>26</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s">
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E34" t="s">
         <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6882,19 +6841,19 @@
         <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
         <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E35" t="s">
         <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6902,19 +6861,19 @@
         <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
         <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E36" t="s">
         <v>20</v>
       </c>
       <c r="G36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6922,22 +6881,22 @@
         <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
         <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E37" t="s">
         <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6945,25 +6904,25 @@
         <v>26</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>27</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>15</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6971,22 +6930,22 @@
         <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
         <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E39" t="s">
         <v>16</v>
       </c>
       <c r="F39" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G39" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -6994,19 +6953,19 @@
         <v>26</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E40" t="s">
         <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -7014,19 +6973,19 @@
         <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E41" t="s">
         <v>20</v>
       </c>
       <c r="G41" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -7034,22 +6993,22 @@
         <v>28</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C42" t="s">
         <v>29</v>
       </c>
       <c r="D42" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E42" t="s">
         <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G42" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -7057,19 +7016,19 @@
         <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C43" t="s">
         <v>29</v>
       </c>
       <c r="D43" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E43" t="s">
         <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -7077,19 +7036,19 @@
         <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C44" t="s">
         <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E44" t="s">
         <v>20</v>
       </c>
       <c r="G44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -7097,19 +7056,19 @@
         <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
         <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E45" t="s">
         <v>20</v>
       </c>
       <c r="G45" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -7117,22 +7076,22 @@
         <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C46" t="s">
         <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
       </c>
       <c r="F46" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G46" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -7140,22 +7099,22 @@
         <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C47" t="s">
         <v>29</v>
       </c>
       <c r="D47" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E47" t="s">
         <v>16</v>
       </c>
       <c r="F47" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G47" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -7163,19 +7122,19 @@
         <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C48" t="s">
         <v>29</v>
       </c>
       <c r="D48" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E48" t="s">
         <v>20</v>
       </c>
       <c r="G48" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7183,19 +7142,19 @@
         <v>28</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C49" t="s">
         <v>29</v>
       </c>
       <c r="D49" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E49" t="s">
         <v>20</v>
       </c>
       <c r="G49" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7203,19 +7162,19 @@
         <v>30</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C50" t="s">
         <v>31</v>
       </c>
       <c r="D50" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E50" t="s">
         <v>20</v>
       </c>
       <c r="G50" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7223,22 +7182,22 @@
         <v>30</v>
       </c>
       <c r="B51" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C51" t="s">
         <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E51" t="s">
         <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G51" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7246,22 +7205,22 @@
         <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C52" t="s">
         <v>31</v>
       </c>
       <c r="D52" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E52" t="s">
         <v>16</v>
       </c>
       <c r="F52" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7269,22 +7228,22 @@
         <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C53" t="s">
         <v>31</v>
       </c>
       <c r="D53" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E53" t="s">
         <v>20</v>
       </c>
       <c r="F53" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G53" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7292,22 +7251,22 @@
         <v>30</v>
       </c>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C54" t="s">
         <v>31</v>
       </c>
       <c r="D54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E54" t="s">
         <v>15</v>
       </c>
       <c r="F54" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G54" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7315,22 +7274,22 @@
         <v>30</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C55" t="s">
         <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E55" t="s">
         <v>16</v>
       </c>
       <c r="F55" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G55" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7338,19 +7297,19 @@
         <v>30</v>
       </c>
       <c r="B56" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C56" t="s">
         <v>31</v>
       </c>
       <c r="D56" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E56" t="s">
         <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7358,22 +7317,22 @@
         <v>30</v>
       </c>
       <c r="B57" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
         <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E57" t="s">
         <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G57" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7381,19 +7340,19 @@
         <v>32</v>
       </c>
       <c r="B58" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C58" t="s">
         <v>33</v>
       </c>
       <c r="D58" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E58" t="s">
         <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7401,19 +7360,19 @@
         <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
         <v>33</v>
       </c>
       <c r="D59" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E59" t="s">
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7421,22 +7380,22 @@
         <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C60" t="s">
         <v>33</v>
       </c>
       <c r="D60" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E60" t="s">
         <v>16</v>
       </c>
       <c r="F60" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G60" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7444,19 +7403,19 @@
         <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C61" t="s">
         <v>33</v>
       </c>
       <c r="D61" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E61" t="s">
         <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7464,22 +7423,22 @@
         <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C62" t="s">
         <v>33</v>
       </c>
       <c r="D62" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E62" t="s">
         <v>15</v>
       </c>
       <c r="F62" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G62" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7487,22 +7446,22 @@
         <v>32</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C63" t="s">
         <v>33</v>
       </c>
       <c r="D63" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E63" t="s">
         <v>16</v>
       </c>
       <c r="F63" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G63" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7510,22 +7469,22 @@
         <v>32</v>
       </c>
       <c r="B64" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C64" t="s">
         <v>33</v>
       </c>
       <c r="D64" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
       </c>
       <c r="F64" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G64" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7533,22 +7492,22 @@
         <v>32</v>
       </c>
       <c r="B65" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C65" t="s">
         <v>33</v>
       </c>
       <c r="D65" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E65" t="s">
         <v>16</v>
       </c>
       <c r="F65" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G65" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7556,19 +7515,19 @@
         <v>35</v>
       </c>
       <c r="B66" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C66" t="s">
         <v>36</v>
       </c>
       <c r="D66" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E66" t="s">
         <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7576,19 +7535,19 @@
         <v>35</v>
       </c>
       <c r="B67" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C67" t="s">
         <v>36</v>
       </c>
       <c r="D67" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E67" t="s">
         <v>20</v>
       </c>
       <c r="G67" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7596,22 +7555,22 @@
         <v>35</v>
       </c>
       <c r="B68" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C68" t="s">
         <v>36</v>
       </c>
       <c r="D68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E68" t="s">
         <v>16</v>
       </c>
       <c r="F68" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G68" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7619,19 +7578,19 @@
         <v>35</v>
       </c>
       <c r="B69" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C69" t="s">
         <v>36</v>
       </c>
       <c r="D69" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E69" t="s">
         <v>20</v>
       </c>
       <c r="G69" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7639,22 +7598,22 @@
         <v>35</v>
       </c>
       <c r="B70" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C70" t="s">
         <v>36</v>
       </c>
       <c r="D70" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E70" t="s">
         <v>15</v>
       </c>
       <c r="F70" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G70" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7662,19 +7621,19 @@
         <v>35</v>
       </c>
       <c r="B71" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C71" t="s">
         <v>36</v>
       </c>
       <c r="D71" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E71" t="s">
         <v>16</v>
       </c>
       <c r="G71" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7682,22 +7641,22 @@
         <v>35</v>
       </c>
       <c r="B72" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C72" t="s">
         <v>36</v>
       </c>
       <c r="D72" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
       </c>
       <c r="F72" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G72" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7705,22 +7664,22 @@
         <v>35</v>
       </c>
       <c r="B73" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C73" t="s">
         <v>36</v>
       </c>
       <c r="D73" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E73" t="s">
         <v>16</v>
       </c>
       <c r="F73" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G73" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7728,19 +7687,19 @@
         <v>37</v>
       </c>
       <c r="B74" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C74" t="s">
         <v>38</v>
       </c>
       <c r="D74" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E74" t="s">
         <v>20</v>
       </c>
       <c r="G74" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7748,19 +7707,19 @@
         <v>37</v>
       </c>
       <c r="B75" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C75" t="s">
         <v>38</v>
       </c>
       <c r="D75" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E75" t="s">
         <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7768,22 +7727,22 @@
         <v>37</v>
       </c>
       <c r="B76" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C76" t="s">
         <v>38</v>
       </c>
       <c r="D76" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E76" t="s">
         <v>16</v>
       </c>
       <c r="F76" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G76" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7791,19 +7750,19 @@
         <v>37</v>
       </c>
       <c r="B77" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C77" t="s">
         <v>38</v>
       </c>
       <c r="D77" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E77" t="s">
         <v>20</v>
       </c>
       <c r="G77" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7811,22 +7770,22 @@
         <v>37</v>
       </c>
       <c r="B78" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C78" t="s">
         <v>38</v>
       </c>
       <c r="D78" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E78" t="s">
         <v>15</v>
       </c>
       <c r="F78" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G78" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7834,19 +7793,19 @@
         <v>37</v>
       </c>
       <c r="B79" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C79" t="s">
         <v>38</v>
       </c>
       <c r="D79" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E79" t="s">
         <v>16</v>
       </c>
       <c r="G79" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7854,22 +7813,22 @@
         <v>37</v>
       </c>
       <c r="B80" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C80" t="s">
         <v>38</v>
       </c>
       <c r="D80" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E80" t="s">
         <v>15</v>
       </c>
       <c r="F80" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7877,22 +7836,22 @@
         <v>37</v>
       </c>
       <c r="B81" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C81" t="s">
         <v>38</v>
       </c>
       <c r="D81" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E81" t="s">
         <v>16</v>
       </c>
       <c r="F81" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G81" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7900,19 +7859,19 @@
         <v>39</v>
       </c>
       <c r="B82" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C82" t="s">
         <v>40</v>
       </c>
       <c r="D82" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E82" t="s">
         <v>20</v>
       </c>
       <c r="G82" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7920,22 +7879,22 @@
         <v>39</v>
       </c>
       <c r="B83" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C83" t="s">
         <v>40</v>
       </c>
       <c r="D83" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E83" t="s">
         <v>16</v>
       </c>
       <c r="F83" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G83" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7943,22 +7902,22 @@
         <v>39</v>
       </c>
       <c r="B84" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C84" t="s">
         <v>40</v>
       </c>
       <c r="D84" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E84" t="s">
         <v>16</v>
       </c>
       <c r="F84" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G84" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7966,19 +7925,19 @@
         <v>39</v>
       </c>
       <c r="B85" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C85" t="s">
         <v>40</v>
       </c>
       <c r="D85" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E85" t="s">
         <v>20</v>
       </c>
       <c r="G85" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -7986,22 +7945,22 @@
         <v>39</v>
       </c>
       <c r="B86" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C86" t="s">
         <v>40</v>
       </c>
       <c r="D86" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E86" t="s">
         <v>15</v>
       </c>
       <c r="F86" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G86" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8009,22 +7968,22 @@
         <v>39</v>
       </c>
       <c r="B87" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C87" t="s">
         <v>40</v>
       </c>
       <c r="D87" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E87" t="s">
         <v>17</v>
       </c>
       <c r="F87" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G87" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8032,22 +7991,22 @@
         <v>39</v>
       </c>
       <c r="B88" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C88" t="s">
         <v>40</v>
       </c>
       <c r="D88" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
       </c>
       <c r="F88" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G88" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8055,22 +8014,22 @@
         <v>39</v>
       </c>
       <c r="B89" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C89" t="s">
         <v>40</v>
       </c>
       <c r="D89" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E89" t="s">
         <v>16</v>
       </c>
       <c r="F89" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G89" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8078,19 +8037,19 @@
         <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C90" t="s">
         <v>42</v>
       </c>
       <c r="D90" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E90" t="s">
         <v>20</v>
       </c>
       <c r="G90" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8098,19 +8057,19 @@
         <v>41</v>
       </c>
       <c r="B91" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C91" t="s">
         <v>42</v>
       </c>
       <c r="D91" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E91" t="s">
         <v>20</v>
       </c>
       <c r="G91" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8118,22 +8077,22 @@
         <v>41</v>
       </c>
       <c r="B92" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C92" t="s">
         <v>42</v>
       </c>
       <c r="D92" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E92" t="s">
         <v>16</v>
       </c>
       <c r="F92" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G92" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8141,19 +8100,19 @@
         <v>41</v>
       </c>
       <c r="B93" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C93" t="s">
         <v>42</v>
       </c>
       <c r="D93" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E93" t="s">
         <v>20</v>
       </c>
       <c r="G93" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8161,22 +8120,22 @@
         <v>41</v>
       </c>
       <c r="B94" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C94" t="s">
         <v>42</v>
       </c>
       <c r="D94" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E94" t="s">
         <v>15</v>
       </c>
       <c r="F94" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G94" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8184,19 +8143,19 @@
         <v>41</v>
       </c>
       <c r="B95" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C95" t="s">
         <v>42</v>
       </c>
       <c r="D95" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E95" t="s">
         <v>16</v>
       </c>
       <c r="G95" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -8204,22 +8163,22 @@
         <v>41</v>
       </c>
       <c r="B96" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C96" t="s">
         <v>42</v>
       </c>
       <c r="D96" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E96" t="s">
         <v>15</v>
       </c>
       <c r="F96" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G96" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8227,22 +8186,22 @@
         <v>41</v>
       </c>
       <c r="B97" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C97" t="s">
         <v>42</v>
       </c>
       <c r="D97" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E97" t="s">
         <v>16</v>
       </c>
       <c r="F97" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G97" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8250,19 +8209,19 @@
         <v>43</v>
       </c>
       <c r="B98" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C98" t="s">
         <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E98" t="s">
         <v>20</v>
       </c>
       <c r="G98" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8270,19 +8229,19 @@
         <v>43</v>
       </c>
       <c r="B99" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C99" t="s">
         <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E99" t="s">
         <v>20</v>
       </c>
       <c r="G99" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8290,25 +8249,25 @@
         <v>43</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C100" s="13" t="s">
         <v>44</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E100" s="13" t="s">
         <v>16</v>
       </c>
       <c r="F100" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G100" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H100" s="13" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8316,19 +8275,19 @@
         <v>43</v>
       </c>
       <c r="B101" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C101" t="s">
         <v>44</v>
       </c>
       <c r="D101" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E101" t="s">
         <v>20</v>
       </c>
       <c r="G101" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8336,22 +8295,22 @@
         <v>43</v>
       </c>
       <c r="B102" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C102" t="s">
         <v>44</v>
       </c>
       <c r="D102" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E102" t="s">
         <v>15</v>
       </c>
       <c r="F102" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G102" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8359,22 +8318,22 @@
         <v>43</v>
       </c>
       <c r="B103" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C103" t="s">
         <v>44</v>
       </c>
       <c r="D103" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E103" t="s">
         <v>16</v>
       </c>
       <c r="F103" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G103" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8382,22 +8341,22 @@
         <v>43</v>
       </c>
       <c r="B104" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C104" t="s">
         <v>44</v>
       </c>
       <c r="D104" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E104" t="s">
         <v>15</v>
       </c>
       <c r="F104" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G104" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8405,22 +8364,22 @@
         <v>43</v>
       </c>
       <c r="B105" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C105" t="s">
         <v>44</v>
       </c>
       <c r="D105" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E105" t="s">
         <v>15</v>
       </c>
       <c r="F105" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G105" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8428,22 +8387,22 @@
         <v>45</v>
       </c>
       <c r="B106" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C106" t="s">
         <v>46</v>
       </c>
       <c r="D106" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E106" t="s">
         <v>20</v>
       </c>
       <c r="F106" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G106" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8451,19 +8410,19 @@
         <v>45</v>
       </c>
       <c r="B107" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C107" t="s">
         <v>46</v>
       </c>
       <c r="D107" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E107" t="s">
         <v>20</v>
       </c>
       <c r="G107" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8471,22 +8430,22 @@
         <v>45</v>
       </c>
       <c r="B108" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C108" t="s">
         <v>46</v>
       </c>
       <c r="D108" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E108" t="s">
         <v>16</v>
       </c>
       <c r="F108" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G108" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8494,19 +8453,19 @@
         <v>45</v>
       </c>
       <c r="B109" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C109" t="s">
         <v>46</v>
       </c>
       <c r="D109" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E109" t="s">
         <v>20</v>
       </c>
       <c r="G109" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8514,22 +8473,22 @@
         <v>45</v>
       </c>
       <c r="B110" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C110" t="s">
         <v>46</v>
       </c>
       <c r="D110" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E110" t="s">
         <v>15</v>
       </c>
       <c r="F110" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G110" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8537,22 +8496,22 @@
         <v>45</v>
       </c>
       <c r="B111" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C111" t="s">
         <v>46</v>
       </c>
       <c r="D111" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E111" t="s">
         <v>16</v>
       </c>
       <c r="F111" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G111" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
@@ -8560,582 +8519,576 @@
         <v>45</v>
       </c>
       <c r="B112" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C112" t="s">
         <v>46</v>
       </c>
       <c r="D112" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E112" t="s">
         <v>15</v>
       </c>
       <c r="F112" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G112" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>45</v>
       </c>
       <c r="B113" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C113" t="s">
         <v>46</v>
       </c>
       <c r="D113" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E113" t="s">
         <v>15</v>
       </c>
       <c r="F113" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G113" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>47</v>
       </c>
       <c r="B114" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C114" t="s">
         <v>48</v>
       </c>
       <c r="D114" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E114" t="s">
         <v>20</v>
       </c>
       <c r="G114" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>47</v>
       </c>
       <c r="B115" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C115" t="s">
         <v>48</v>
       </c>
       <c r="D115" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E115" t="s">
         <v>20</v>
       </c>
       <c r="G115" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>47</v>
       </c>
       <c r="B116" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C116" t="s">
         <v>48</v>
       </c>
       <c r="D116" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E116" t="s">
         <v>16</v>
       </c>
       <c r="F116" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G116" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>47</v>
       </c>
       <c r="B117" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C117" t="s">
         <v>48</v>
       </c>
       <c r="D117" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E117" t="s">
         <v>20</v>
       </c>
       <c r="G117" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>47</v>
       </c>
       <c r="B118" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C118" t="s">
         <v>48</v>
       </c>
       <c r="D118" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E118" t="s">
         <v>15</v>
       </c>
       <c r="F118" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G118" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>47</v>
       </c>
       <c r="B119" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C119" t="s">
         <v>48</v>
       </c>
       <c r="D119" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E119" t="s">
         <v>16</v>
       </c>
       <c r="F119" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G119" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>47</v>
       </c>
       <c r="B120" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C120" t="s">
         <v>48</v>
       </c>
       <c r="D120" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E120" t="s">
         <v>15</v>
       </c>
       <c r="F120" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G120" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>47</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C121" t="s">
         <v>48</v>
       </c>
       <c r="D121" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E121" t="s">
         <v>15</v>
       </c>
       <c r="F121" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G121" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>49</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C122" t="s">
         <v>50</v>
       </c>
       <c r="D122" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E122" t="s">
         <v>20</v>
       </c>
       <c r="G122" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>49</v>
       </c>
       <c r="B123" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C123" t="s">
         <v>50</v>
       </c>
       <c r="D123" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E123" t="s">
         <v>16</v>
       </c>
       <c r="F123" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G123" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" t="s">
         <v>49</v>
       </c>
-      <c r="B124" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C124" s="13" t="s">
+      <c r="B124" t="s">
+        <v>119</v>
+      </c>
+      <c r="C124" t="s">
         <v>50</v>
       </c>
-      <c r="D124" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E124" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="F124" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="G124" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H124" s="13" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="D124" t="s">
+        <v>71</v>
+      </c>
+      <c r="E124" t="s">
+        <v>15</v>
+      </c>
+      <c r="F124" t="s">
+        <v>153</v>
+      </c>
+      <c r="G124" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>49</v>
       </c>
       <c r="B125" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C125" t="s">
         <v>50</v>
       </c>
       <c r="D125" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E125" t="s">
         <v>20</v>
       </c>
       <c r="G125" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
         <v>49</v>
       </c>
       <c r="B126" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C126" t="s">
         <v>50</v>
       </c>
       <c r="D126" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E126" t="s">
         <v>15</v>
       </c>
       <c r="F126" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G126" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>49</v>
       </c>
       <c r="B127" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C127" t="s">
         <v>50</v>
       </c>
       <c r="D127" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E127" t="s">
         <v>16</v>
       </c>
       <c r="F127" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G127" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
         <v>49</v>
       </c>
       <c r="B128" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C128" t="s">
         <v>50</v>
       </c>
       <c r="D128" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E128" t="s">
         <v>15</v>
       </c>
       <c r="F128" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G128" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A129" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" t="s">
         <v>49</v>
       </c>
-      <c r="B129" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C129" s="13" t="s">
+      <c r="B129" t="s">
+        <v>119</v>
+      </c>
+      <c r="C129" t="s">
         <v>50</v>
       </c>
-      <c r="D129" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E129" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="F129" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="G129" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H129" s="13" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="D129" t="s">
+        <v>84</v>
+      </c>
+      <c r="E129" t="s">
+        <v>15</v>
+      </c>
+      <c r="F129" t="s">
+        <v>156</v>
+      </c>
+      <c r="G129" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
+        <v>52</v>
+      </c>
+      <c r="B130" t="s">
+        <v>157</v>
+      </c>
+      <c r="C130" t="s">
         <v>53</v>
       </c>
-      <c r="B130" t="s">
-        <v>161</v>
-      </c>
-      <c r="C130" t="s">
-        <v>54</v>
-      </c>
       <c r="D130" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E130" t="s">
         <v>17</v>
       </c>
       <c r="F130" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G130" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
+        <v>52</v>
+      </c>
+      <c r="B131" t="s">
+        <v>157</v>
+      </c>
+      <c r="C131" t="s">
         <v>53</v>
       </c>
-      <c r="B131" t="s">
-        <v>161</v>
-      </c>
-      <c r="C131" t="s">
-        <v>54</v>
-      </c>
       <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" t="s">
+        <v>20</v>
+      </c>
+      <c r="G131" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132" t="s">
+        <v>52</v>
+      </c>
+      <c r="B132" t="s">
+        <v>157</v>
+      </c>
+      <c r="C132" t="s">
+        <v>53</v>
+      </c>
+      <c r="D132" t="s">
         <v>71</v>
-      </c>
-      <c r="E131" t="s">
-        <v>20</v>
-      </c>
-      <c r="G131" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A132" t="s">
-        <v>53</v>
-      </c>
-      <c r="B132" t="s">
-        <v>161</v>
-      </c>
-      <c r="C132" t="s">
-        <v>54</v>
-      </c>
-      <c r="D132" t="s">
-        <v>73</v>
       </c>
       <c r="E132" t="s">
         <v>16</v>
       </c>
       <c r="F132" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G132" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
+        <v>52</v>
+      </c>
+      <c r="B133" t="s">
+        <v>157</v>
+      </c>
+      <c r="C133" t="s">
         <v>53</v>
       </c>
-      <c r="B133" t="s">
-        <v>161</v>
-      </c>
-      <c r="C133" t="s">
-        <v>54</v>
-      </c>
       <c r="D133" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E133" t="s">
         <v>15</v>
       </c>
       <c r="F133" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G133" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
+        <v>52</v>
+      </c>
+      <c r="B134" t="s">
+        <v>157</v>
+      </c>
+      <c r="C134" t="s">
         <v>53</v>
       </c>
-      <c r="B134" t="s">
-        <v>161</v>
-      </c>
-      <c r="C134" t="s">
-        <v>54</v>
-      </c>
       <c r="D134" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E134" t="s">
         <v>16</v>
       </c>
       <c r="F134" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G134" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
+        <v>52</v>
+      </c>
+      <c r="B135" t="s">
+        <v>157</v>
+      </c>
+      <c r="C135" t="s">
         <v>53</v>
       </c>
-      <c r="B135" t="s">
-        <v>161</v>
-      </c>
-      <c r="C135" t="s">
-        <v>54</v>
-      </c>
       <c r="D135" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E135" t="s">
         <v>16</v>
       </c>
       <c r="G135" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
+        <v>52</v>
+      </c>
+      <c r="B136" t="s">
+        <v>157</v>
+      </c>
+      <c r="C136" t="s">
         <v>53</v>
       </c>
-      <c r="B136" t="s">
-        <v>161</v>
-      </c>
-      <c r="C136" t="s">
-        <v>54</v>
-      </c>
       <c r="D136" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E136" t="s">
         <v>17</v>
       </c>
       <c r="F136" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G136" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
+        <v>52</v>
+      </c>
+      <c r="B137" t="s">
+        <v>157</v>
+      </c>
+      <c r="C137" t="s">
         <v>53</v>
       </c>
-      <c r="B137" t="s">
-        <v>161</v>
-      </c>
-      <c r="C137" t="s">
-        <v>54</v>
-      </c>
       <c r="D137" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E137" t="s">
         <v>15</v>
       </c>
       <c r="F137" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G137" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/marketing-ownership-map.xlsx
+++ b/marketing-ownership-map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LRUSIN~1\AppData\Local\Temp\claude\c--Users-lrusinova-OneDrive---QuickBase-Documents-Project-Management-MCP\abf0f386-0ae7-411b-800d-e81e7586b212\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://quickbase-my.sharepoint.com/personal/lrusinova_quickbase_com/Documents/Documents/Project Management MCP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B02C43F-0DD0-4BE7-85A2-444C4797CC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{4B02C43F-0DD0-4BE7-85A2-444C4797CC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A2C030C-1D80-431A-B521-74B6ADBE0846}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{D9A43224-3FE6-4782-BEE1-41A45989FA1C}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8904" xr2:uid="{D9A43224-3FE6-4782-BEE1-41A45989FA1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="4" r:id="rId1"/>
@@ -75,7 +75,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{B9D46037-A0AE-42EE-880C-2DEC6612E149}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{2270AA12-66A7-45F5-9643-7E6BD09C19D9}">
       <text>
         <r>
           <rPr>
@@ -83,10 +83,9 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
-          <t>Defines what the launch needs from centralized teams.
-CONFLICT: Demand Gen also shows R here - no agreed Accountable.</t>
+          <t>Defines what the launch needs from centralized teams. Accountable for product/feature Launches - Demand Gen is Accountable instead for non-launch Campaigns (see Project Type Guide). Resolved by Mirissa Kampf, per Aly Reynders' guidance, Aug 2026.</t>
         </r>
       </text>
     </comment>
@@ -104,7 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G6" authorId="0" shapeId="0" xr:uid="{87879CBE-8D30-437D-9BC4-C49F4FED17E1}">
+    <comment ref="G6" authorId="0" shapeId="0" xr:uid="{07F12A58-4A13-4B84-BA5D-BB2D0DFF3EE1}">
       <text>
         <r>
           <rPr>
@@ -112,10 +111,9 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
-          <t>Answers questions, reviews drafts for accuracy.
-CONFLICT: Overlaps with Brand/Positioning and Writer on who owns messaging in the draft.</t>
+          <t>Owns the Launch Story &amp; Messaging Brief (product truth, personas, proof points, guardrails) that Brand and Content execute from; signs off on final copy for accuracy before anything ships. Accountable - resolved by Mirissa Kampf/Aly Reynders, Aug 2026, per the GTM Messaging &amp; Ownership Framework (Heather Pepe).</t>
         </r>
       </text>
     </comment>
@@ -175,7 +173,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{5B00C449-93FE-41FF-9C7E-2CC6BA04DD4B}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{6261401D-3AC1-4D7A-9F30-28C483E5AAA0}">
       <text>
         <r>
           <rPr>
@@ -183,10 +181,9 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
-          <t>Defines channel/activation needs for the launch.
-CONFLICT: PMM also shows R here - no agreed Accountable. Also unclear how this relates to Paid Media's own R at this stage.</t>
+          <t>Defines channel/activation needs for the launch. Accountable instead of PMM when the project is a non-launch Campaign (see Project Type Guide); PMM is Accountable for product/feature Launches. Resolved Aug 2026. Still open: how this relates to Paid Media's own R at this stage - see Open Conflict below.</t>
         </r>
       </text>
     </comment>
@@ -288,7 +285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{35791E69-B3A6-441C-82E9-FD327DE3C6C8}">
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{69730CF1-3485-4EF9-9C8F-B552F263E9EF}">
       <text>
         <r>
           <rPr>
@@ -296,10 +293,9 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
-          <t>Owns messaging accuracy inside produced content.
-CONFLICT: Overlaps with PMM and Writer on who owns messaging in the draft.</t>
+          <t>Executes creative direction and brand copywriting using PMM's Launch Story &amp; Messaging Brief; owns brand voice and portfolio-wide narrative coherence. Responsible - PMM holds final sign-off (Accountable). Resolved Aug 2026.</t>
         </r>
       </text>
     </comment>
@@ -387,7 +383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{8DE5E960-C906-42A9-A525-3FFDF7367203}">
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{D6BC62EB-4CDE-441A-AD36-77EC87E85DCD}">
       <text>
         <r>
           <rPr>
@@ -395,10 +391,9 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
-          <t>Drafts the actual content.
-CONFLICT: How much the PMM brief pins down vs. what's left to the writer's interpretation, and where Brand's messaging ownership ends.</t>
+          <t>Drafts and expands copy from PMM's brief - keeps the required substance, makes it land for the persona/channel. Responsible alongside Brand - PMM holds final sign-off (Accountable). Resolved Aug 2026.</t>
         </r>
       </text>
     </comment>
@@ -1262,7 +1257,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="208">
   <si>
     <t>Marketing Ownership Map - RACI Matrix (Working Draft)</t>
   </si>
@@ -1408,15 +1403,9 @@
     <t>Customer Marketing</t>
   </si>
   <si>
-    <t>Caroline Eglert, Meaghan Nichols</t>
-  </si>
-  <si>
     <t>Partner Marketing</t>
   </si>
   <si>
-    <t>Meaghan Nichols</t>
-  </si>
-  <si>
     <t>ORCHESTRATION</t>
   </si>
   <si>
@@ -1429,15 +1418,6 @@
     <t>OPEN CONFLICTS - NEEDS DISCUSSION</t>
   </si>
   <si>
-    <t>1. Activation Planning - PMM vs. Demand Gen: Both show R (Responsible). No agreed Accountable - unclear who has final say when the two disagree on activation direction.</t>
-  </si>
-  <si>
-    <t>2. Production - PMM vs. Brand/Positioning vs. Content: The single biggest open question. PMM (C), Brand/Positioning (R), and Content/Writers (R) all show ownership at Production. In practice: how much does the PMM brief pin down vs. what's left to the writer's interpretation, and where does Brand's messaging/voice ownership end and Content's drafting begin? Nobody currently owns final say on copy in the draft.</t>
-  </si>
-  <si>
-    <t>3. Paid Media vs. Demand Gen: Unclear whether paid activation is a Demand Gen sub-decision or owned directly by Paid Media. Both show involvement without a clear boundary.</t>
-  </si>
-  <si>
     <t>Team Group</t>
   </si>
   <si>
@@ -1480,15 +1460,9 @@
     <t>Activation Planning</t>
   </si>
   <si>
-    <t>Defines what the launch needs from centralized teams.</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
-    <t>Demand Gen also shows R here - no agreed Accountable.</t>
-  </si>
-  <si>
     <t>Brief to Centralized Teams</t>
   </si>
   <si>
@@ -1498,12 +1472,6 @@
     <t>Production</t>
   </si>
   <si>
-    <t>Answers questions, reviews drafts for accuracy.</t>
-  </si>
-  <si>
-    <t>Overlaps with Brand/Positioning and Writer on who owns messaging in the draft.</t>
-  </si>
-  <si>
     <t>Review &amp; Approval</t>
   </si>
   <si>
@@ -1525,12 +1493,6 @@
     <t>Flags channel/funnel considerations early.</t>
   </si>
   <si>
-    <t>Defines channel/activation needs for the launch.</t>
-  </si>
-  <si>
-    <t>PMM also shows R here - no agreed Accountable. Also unclear how this relates to Paid Media's own R at this stage.</t>
-  </si>
-  <si>
     <t>Co-briefs on funnel and channel requirements.</t>
   </si>
   <si>
@@ -1552,12 +1514,6 @@
     <t>Reviews the brief for narrative consistency.</t>
   </si>
   <si>
-    <t>Owns messaging accuracy inside produced content.</t>
-  </si>
-  <si>
-    <t>Overlaps with PMM and Writer on who owns messaging in the draft.</t>
-  </si>
-  <si>
     <t>Signs off on brand voice and positioning.</t>
   </si>
   <si>
@@ -1576,12 +1532,6 @@
     <t>Receives the brief.</t>
   </si>
   <si>
-    <t>Drafts the actual content.</t>
-  </si>
-  <si>
-    <t>How much the PMM brief pins down vs. what's left to the writer's interpretation, and where Brand's messaging ownership ends.</t>
-  </si>
-  <si>
     <t>Incorporates review feedback.</t>
   </si>
   <si>
@@ -1894,15 +1844,6 @@
     <t>Open conflicts needing discussion</t>
   </si>
   <si>
-    <t>1. Activation Planning: PMM vs. Demand Gen - both show R, no agreed Accountable.</t>
-  </si>
-  <si>
-    <t>2. Production: PMM vs. Brand/Positioning vs. Content - messaging/copy ownership unresolved. The single biggest open question on the board.</t>
-  </si>
-  <si>
-    <t>3. Paid Media vs. Demand Gen - unclear whether paid activation is a Demand Gen sub-decision or owned directly by Paid Media.</t>
-  </si>
-  <si>
     <t>Supporting detail</t>
   </si>
   <si>
@@ -1910,13 +1851,43 @@
   </si>
   <si>
     <t>Active Teams</t>
+  </si>
+  <si>
+    <t>Caroline Eglert, Meaghan Nickols</t>
+  </si>
+  <si>
+    <t>Meaghan Nickols</t>
+  </si>
+  <si>
+    <t>R/A</t>
+  </si>
+  <si>
+    <t>1. Paid Media vs. Demand Gen: Unclear whether paid activation is a Demand Gen sub-decision or owned directly by Paid Media. Both show involvement without a clear boundary.</t>
+  </si>
+  <si>
+    <t>Defines what the launch needs from centralized teams. Accountable for Launches (Demand Gen is Accountable for Campaigns).</t>
+  </si>
+  <si>
+    <t>Owns the Launch Story &amp; Messaging Brief; signs off on final copy for accuracy.</t>
+  </si>
+  <si>
+    <t>Defines channel/activation needs for the launch. Accountable for Campaigns (PMM is Accountable for Launches).</t>
+  </si>
+  <si>
+    <t>Executes creative direction/copywriting from PMM's brief; owns brand voice.</t>
+  </si>
+  <si>
+    <t>Drafts and expands copy from PMM's brief for persona/channel fit.</t>
+  </si>
+  <si>
+    <t>1. Paid Media vs. Demand Gen - unclear whether paid activation is a Demand Gen sub-decision or owned directly by Paid Media.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2077,8 +2048,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2133,6 +2111,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2161,11 +2145,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2187,7 +2170,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2197,14 +2179,6 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2232,11 +2206,67 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="10">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2260,6 +2290,7 @@
           <bgColor rgb="FF082521"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4147,8 +4178,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1356360</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1996440</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>111760</xdr:rowOff>
     </xdr:to>
@@ -4178,18 +4209,22 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2607C8CC-A66C-48FA-AE73-5225724582B4}" name="OwnershipData" displayName="OwnershipData" ref="A1:H137" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2607C8CC-A66C-48FA-AE73-5225724582B4}" name="OwnershipData" displayName="OwnershipData" ref="A1:H137" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:H137" xr:uid="{2607C8CC-A66C-48FA-AE73-5225724582B4}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C2FDC5A5-0AB7-4E88-B1B8-864681491C96}" name="Team"/>
-    <tableColumn id="2" xr3:uid="{5A236A8F-7B46-44C5-B27E-98ADE3D97C0E}" name="Team Group"/>
-    <tableColumn id="3" xr3:uid="{CE4B9929-C91B-4C53-8A1A-E38E0B9E8781}" name="Who"/>
-    <tableColumn id="4" xr3:uid="{584FC3C8-E436-4B27-B926-AD1B432BB987}" name="Stage"/>
-    <tableColumn id="5" xr3:uid="{ED7E12D3-58F3-4962-B3F5-5F25288A7B7A}" name="RACI"/>
-    <tableColumn id="6" xr3:uid="{C9E6ED22-A8BA-4677-B659-70806834915C}" name="Note"/>
-    <tableColumn id="7" xr3:uid="{7202C52B-E4A7-47CC-8ABA-10BC1E3C7E90}" name="Conflict"/>
-    <tableColumn id="8" xr3:uid="{0F6077CF-1D86-4250-AE82-90038E34EA44}" name="Conflict Note"/>
+    <tableColumn id="1" xr3:uid="{C2FDC5A5-0AB7-4E88-B1B8-864681491C96}" name="Team" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{5A236A8F-7B46-44C5-B27E-98ADE3D97C0E}" name="Team Group" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{CE4B9929-C91B-4C53-8A1A-E38E0B9E8781}" name="Who" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{584FC3C8-E436-4B27-B926-AD1B432BB987}" name="Stage" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{ED7E12D3-58F3-4962-B3F5-5F25288A7B7A}" name="RACI" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{C9E6ED22-A8BA-4677-B659-70806834915C}" name="Note" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{7202C52B-E4A7-47CC-8ABA-10BC1E3C7E90}" name="Conflict" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{0F6077CF-1D86-4250-AE82-90038E34EA44}" name="Conflict Note" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4518,85 +4553,82 @@
     <col min="1" max="4" width="22.578125" customWidth="1"/>
     <col min="6" max="6" width="20.578125" customWidth="1"/>
     <col min="7" max="7" width="10.578125" customWidth="1"/>
+    <col min="8" max="8" width="29.3125" customWidth="1"/>
     <col min="9" max="9" width="26.578125" customWidth="1"/>
     <col min="10" max="10" width="12.578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.3" x14ac:dyDescent="0.85">
-      <c r="A1" s="25" t="s">
-        <v>203</v>
+      <c r="A1" s="19" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="16" t="s">
-        <v>204</v>
+      <c r="A2" s="14" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="26" t="s">
-        <v>205</v>
+      <c r="A3" s="20" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="1.4">
-      <c r="A5" s="27">
+      <c r="A5" s="21">
         <v>17</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="23">
         <v>8</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="25">
         <v>14</v>
       </c>
-      <c r="D5" s="33">
-        <v>3</v>
+      <c r="D5" s="27">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="B6" s="30" t="s">
+      <c r="A6" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A8" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A8" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
     </row>
     <row r="10" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
+      <c r="A10" s="39"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
     </row>
     <row r="11" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
+      <c r="A11" s="39"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="35" t="s">
-        <v>213</v>
+      <c r="A13" s="29" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -4604,18 +4636,18 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="I14" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J14" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G15">
         <v>4</v>
@@ -4759,7 +4791,7 @@
     </row>
     <row r="27" spans="6:10" x14ac:dyDescent="0.55000000000000004">
       <c r="F27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -4798,10 +4830,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4819,520 +4849,520 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="14" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="4" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="16" t="s">
+      <c r="B9" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="J9" s="15" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="4" t="s">
+    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="4" t="s">
+      <c r="B10" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J10" s="15" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="5" t="s">
+    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B11" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J11" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="J5" s="17" t="s">
+    </row>
+    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="4" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="5" t="s">
+      <c r="B12" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="J12" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="8" t="s">
+    </row>
+    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="B13" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="J13" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="J6" s="17" t="s">
+    </row>
+    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="4" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="5" t="s">
+      <c r="B14" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="J14" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="J7" s="17" t="s">
+    </row>
+    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="4" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="5" t="s">
+      <c r="B15" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="J15" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="J8" s="17" t="s">
+    </row>
+    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="4" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="5" t="s">
+      <c r="B16" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J16" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="J9" s="17" t="s">
+    </row>
+    <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="4" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="5" t="s">
+      <c r="B17" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="J17" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="J10" s="17" t="s">
+    </row>
+    <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="4" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="5" t="s">
+      <c r="B18" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="J18" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="J11" s="17" t="s">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="12" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="5" t="s">
+      <c r="B20" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" t="s">
         <v>185</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="J12" s="17" t="s">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="5" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C22" t="s">
         <v>187</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="J13" s="17" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="J14" s="17" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="J15" s="17" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="J17" s="17" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="C20" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C21" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="C22" t="s">
-        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -5342,6 +5372,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1332399-AEE2-44C7-9163-AE5445FDA981}">
+  <sheetPr>
+    <tabColor theme="6"/>
+  </sheetPr>
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -5361,693 +5394,687 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="37" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="F7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="G7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="F9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="J9" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="D11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="I11" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="H12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="I13" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="I14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="9" t="s">
+    </row>
+    <row r="15" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="I18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="8" t="s">
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="F19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="H19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="9" t="s">
+      <c r="I19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="J19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="8" t="s">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="7" t="s">
+      <c r="F20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H20" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="I20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="F21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="I21" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="J21" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I13" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" s="8" t="s">
+      <c r="F22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="8" t="s">
+      <c r="I22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="E23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="F23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J23" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="F25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="7" t="s">
+      <c r="H25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="5" t="s">
+    </row>
+    <row r="28" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="A28" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A28" s="12" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
+      <c r="A29" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
     </row>
     <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
+      <c r="A30" s="39"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="40"/>
     </row>
     <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
+      <c r="A31" s="39"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A31:J31"/>
+  <mergeCells count="5">
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A30:J30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6059,3036 +6086,3027 @@
   <dimension ref="A1:H137"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="17.9453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.62890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.3125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.05078125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7890625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.578125" customWidth="1"/>
-    <col min="7" max="7" width="9.26171875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="45.578125" customWidth="1"/>
+    <col min="1" max="1" width="17.9453125" style="31" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.62890625" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.3125" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.05078125" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7890625" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.578125" style="31" customWidth="1"/>
+    <col min="7" max="7" width="9.26171875" style="31" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.578125" style="31" customWidth="1"/>
+    <col min="9" max="16384" width="8.83984375" style="31"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="H1" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="C2" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="E2" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="G2" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="31" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+      <c r="E3" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B4" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D4" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E4" s="32" t="s">
+        <v>200</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="32"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F5" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>203</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="32"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" s="32"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>205</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" s="32"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="G32" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E36" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="G37" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="G38" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H38" s="32"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="G39" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E40" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="G42" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E43" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E44" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E46" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="G46" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="G47" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C49" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D51" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E51" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="G51" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E52" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="G52" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="G53" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E54" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="G54" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B55" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C55" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E55" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G55" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E56" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C57" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D57" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E57" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="G57" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E58" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B59" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C59" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E59" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B60" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E60" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="G60" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B61" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C61" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D61" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D62" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E62" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="G62" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B63" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D63" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E63" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="G63" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B64" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E64" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="G64" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B65" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C65" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E65" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="G65" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C66" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D66" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E66" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C67" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D67" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E67" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B68" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C68" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D68" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E68" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F68" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="G68" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B69" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C69" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D69" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E69" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B70" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C70" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D70" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E70" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F70" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="G70" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B71" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C71" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D71" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E71" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G71" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C72" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D72" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E72" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F72" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="G72" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B73" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C73" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D73" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E73" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F73" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="G73" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C74" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D74" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E74" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G74" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B75" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C75" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D75" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E75" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C76" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D76" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E76" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F76" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="G76" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B77" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C77" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D77" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E77" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G77" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B78" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C78" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D78" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E78" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="G78" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B79" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C79" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D79" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E79" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B80" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C80" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D80" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E80" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F80" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="G80" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B81" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C81" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D81" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E81" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" s="31" t="s">
+        <v>112</v>
+      </c>
+      <c r="G81" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B82" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C82" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D82" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E82" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G82" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C83" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D83" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E83" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="G83" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B84" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C84" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D84" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E84" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F84" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="G84" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B85" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C85" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D85" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E85" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C86" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D86" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E86" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="G86" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B87" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C87" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D87" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E87" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F87" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="G87" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B88" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C88" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D88" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E88" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="G88" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C89" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D89" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E89" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G89" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B90" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C90" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D90" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E90" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G90" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B91" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C91" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D91" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E91" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G91" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B92" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C92" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D92" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E92" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F92" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="G92" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B93" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C93" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D93" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E93" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G93" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C94" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D94" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E94" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="G94" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B95" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C95" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D95" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E95" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G95" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B96" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C96" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D96" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E96" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F96" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="G96" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B97" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C97" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D97" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E97" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F97" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="G97" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B98" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C98" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D98" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E98" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B99" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C99" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D99" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E99" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G99" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B100" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C100" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D100" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E100" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="G100" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H100" s="32" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B101" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C101" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D101" s="31" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="E101" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B102" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C102" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D102" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E102" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F102" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="G102" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B103" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C103" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D103" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E103" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F103" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="G103" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B104" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C104" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D104" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E104" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F104" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G104" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B105" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C105" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D105" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E105" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F105" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="G105" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B106" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C106" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D106" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E106" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="F106" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="G106" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B107" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C107" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D107" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E107" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G107" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B108" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C108" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D108" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E108" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F108" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="G108" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B109" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C109" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D109" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E109" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G109" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B110" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C110" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D110" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="G3" t="s">
+      <c r="E110" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F110" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="G110" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B111" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C111" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D111" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E111" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F111" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="G111" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B112" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C112" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D112" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E112" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F112" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="G112" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="B113" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C113" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D113" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E113" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F113" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="G113" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B114" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C114" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="D114" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E114" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G114" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B115" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C115" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="D115" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E115" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G115" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B116" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C116" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="D116" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E116" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F116" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G116" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B117" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C117" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="D117" s="31" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="13" t="s">
+      <c r="E117" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G117" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B118" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C118" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="D118" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E118" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F118" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="G118" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B119" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C119" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="D119" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E119" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F119" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="G119" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B120" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C120" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="D120" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E120" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="G4" s="13" t="s">
+      <c r="F120" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="G120" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B121" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C121" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="D121" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E121" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="G121" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B122" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C122" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="D122" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E122" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G122" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B123" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C123" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="D123" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E123" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F123" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="G123" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B124" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C124" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="D124" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E124" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F124" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G124" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B125" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C125" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="D125" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E125" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G125" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B126" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C126" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="D126" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E126" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F126" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="G126" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A127" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B127" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C127" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="D127" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E127" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F127" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="G127" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B128" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C128" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="D128" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E128" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="G128" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B129" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="C129" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="D129" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E129" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="F5" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="F129" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="G129" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A130" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B130" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C130" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D130" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E130" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="F130" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="G130" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A131" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B131" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C131" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D131" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="E131" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G131" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B132" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C132" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D132" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E132" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="F132" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="G132" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A133" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B133" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C133" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D133" s="31" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" s="13" t="s">
+      <c r="E133" s="31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F133" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="G133" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A134" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B134" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C134" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D134" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E134" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="F134" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="G134" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A135" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B135" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C135" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D135" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="E135" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="G135" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A136" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B136" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C136" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D136" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="H6" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="E136" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="F7" t="s">
-        <v>81</v>
-      </c>
-      <c r="G7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" t="s">
-        <v>83</v>
-      </c>
-      <c r="G8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" t="s">
-        <v>86</v>
-      </c>
-      <c r="G10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" s="13" t="s">
+      <c r="F136" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="G136" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A137" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B137" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C137" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D137" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="E137" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" t="s">
-        <v>89</v>
-      </c>
-      <c r="G13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" t="s">
-        <v>91</v>
-      </c>
-      <c r="G17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" t="s">
-        <v>65</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" t="s">
-        <v>69</v>
-      </c>
-      <c r="E19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" t="s">
-        <v>93</v>
-      </c>
-      <c r="G19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" t="s">
-        <v>94</v>
-      </c>
-      <c r="G20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" t="s">
-        <v>95</v>
-      </c>
-      <c r="G21" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" t="s">
-        <v>98</v>
-      </c>
-      <c r="G23" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" t="s">
-        <v>20</v>
-      </c>
-      <c r="G26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" t="s">
-        <v>99</v>
-      </c>
-      <c r="G28" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C29" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" t="s">
-        <v>75</v>
-      </c>
-      <c r="E29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" t="s">
-        <v>80</v>
-      </c>
-      <c r="E31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" t="s">
-        <v>82</v>
-      </c>
-      <c r="E32" t="s">
-        <v>16</v>
-      </c>
-      <c r="F32" t="s">
-        <v>100</v>
-      </c>
-      <c r="G32" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" t="s">
-        <v>101</v>
-      </c>
-      <c r="G33" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" t="s">
-        <v>27</v>
-      </c>
-      <c r="D34" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" t="s">
-        <v>16</v>
-      </c>
-      <c r="F34" t="s">
-        <v>102</v>
-      </c>
-      <c r="G34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" t="s">
-        <v>69</v>
-      </c>
-      <c r="E35" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D36" t="s">
-        <v>71</v>
-      </c>
-      <c r="E36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" t="s">
-        <v>77</v>
-      </c>
-      <c r="C37" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E37" t="s">
-        <v>20</v>
-      </c>
-      <c r="F37" t="s">
-        <v>103</v>
-      </c>
-      <c r="G37" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="G38" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="H38" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39" t="s">
-        <v>80</v>
-      </c>
-      <c r="E39" t="s">
-        <v>16</v>
-      </c>
-      <c r="F39" t="s">
-        <v>106</v>
-      </c>
-      <c r="G39" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
-        <v>26</v>
-      </c>
-      <c r="B40" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" t="s">
-        <v>27</v>
-      </c>
-      <c r="D40" t="s">
-        <v>82</v>
-      </c>
-      <c r="E40" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" t="s">
-        <v>26</v>
-      </c>
-      <c r="B41" t="s">
-        <v>77</v>
-      </c>
-      <c r="C41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D41" t="s">
-        <v>84</v>
-      </c>
-      <c r="E41" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" t="s">
-        <v>28</v>
-      </c>
-      <c r="B42" t="s">
-        <v>77</v>
-      </c>
-      <c r="C42" t="s">
-        <v>29</v>
-      </c>
-      <c r="D42" t="s">
-        <v>66</v>
-      </c>
-      <c r="E42" t="s">
-        <v>16</v>
-      </c>
-      <c r="F42" t="s">
-        <v>107</v>
-      </c>
-      <c r="G42" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" t="s">
-        <v>28</v>
-      </c>
-      <c r="B43" t="s">
-        <v>77</v>
-      </c>
-      <c r="C43" t="s">
-        <v>29</v>
-      </c>
-      <c r="D43" t="s">
-        <v>69</v>
-      </c>
-      <c r="E43" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" t="s">
-        <v>28</v>
-      </c>
-      <c r="B44" t="s">
-        <v>77</v>
-      </c>
-      <c r="C44" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44" t="s">
-        <v>71</v>
-      </c>
-      <c r="E44" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" t="s">
-        <v>28</v>
-      </c>
-      <c r="B45" t="s">
-        <v>77</v>
-      </c>
-      <c r="C45" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45" t="s">
-        <v>75</v>
-      </c>
-      <c r="E45" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" t="s">
-        <v>28</v>
-      </c>
-      <c r="B46" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46" t="s">
-        <v>77</v>
-      </c>
-      <c r="E46" t="s">
-        <v>15</v>
-      </c>
-      <c r="F46" t="s">
-        <v>108</v>
-      </c>
-      <c r="G46" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" t="s">
-        <v>77</v>
-      </c>
-      <c r="C47" t="s">
-        <v>29</v>
-      </c>
-      <c r="D47" t="s">
-        <v>80</v>
-      </c>
-      <c r="E47" t="s">
-        <v>16</v>
-      </c>
-      <c r="F47" t="s">
-        <v>106</v>
-      </c>
-      <c r="G47" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" t="s">
-        <v>28</v>
-      </c>
-      <c r="B48" t="s">
-        <v>77</v>
-      </c>
-      <c r="C48" t="s">
-        <v>29</v>
-      </c>
-      <c r="D48" t="s">
-        <v>82</v>
-      </c>
-      <c r="E48" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" t="s">
-        <v>28</v>
-      </c>
-      <c r="B49" t="s">
-        <v>77</v>
-      </c>
-      <c r="C49" t="s">
-        <v>29</v>
-      </c>
-      <c r="D49" t="s">
-        <v>84</v>
-      </c>
-      <c r="E49" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" t="s">
-        <v>30</v>
-      </c>
-      <c r="B50" t="s">
-        <v>77</v>
-      </c>
-      <c r="C50" t="s">
-        <v>31</v>
-      </c>
-      <c r="D50" t="s">
-        <v>66</v>
-      </c>
-      <c r="E50" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" t="s">
-        <v>30</v>
-      </c>
-      <c r="B51" t="s">
-        <v>77</v>
-      </c>
-      <c r="C51" t="s">
-        <v>31</v>
-      </c>
-      <c r="D51" t="s">
-        <v>69</v>
-      </c>
-      <c r="E51" t="s">
-        <v>16</v>
-      </c>
-      <c r="F51" t="s">
-        <v>109</v>
-      </c>
-      <c r="G51" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" t="s">
-        <v>30</v>
-      </c>
-      <c r="B52" t="s">
-        <v>77</v>
-      </c>
-      <c r="C52" t="s">
-        <v>31</v>
-      </c>
-      <c r="D52" t="s">
-        <v>71</v>
-      </c>
-      <c r="E52" t="s">
-        <v>16</v>
-      </c>
-      <c r="F52" t="s">
-        <v>110</v>
-      </c>
-      <c r="G52" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" t="s">
-        <v>30</v>
-      </c>
-      <c r="B53" t="s">
-        <v>77</v>
-      </c>
-      <c r="C53" t="s">
-        <v>31</v>
-      </c>
-      <c r="D53" t="s">
-        <v>75</v>
-      </c>
-      <c r="E53" t="s">
-        <v>20</v>
-      </c>
-      <c r="F53" t="s">
-        <v>111</v>
-      </c>
-      <c r="G53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" t="s">
-        <v>30</v>
-      </c>
-      <c r="B54" t="s">
-        <v>77</v>
-      </c>
-      <c r="C54" t="s">
-        <v>31</v>
-      </c>
-      <c r="D54" t="s">
-        <v>77</v>
-      </c>
-      <c r="E54" t="s">
-        <v>15</v>
-      </c>
-      <c r="F54" t="s">
-        <v>112</v>
-      </c>
-      <c r="G54" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" t="s">
-        <v>30</v>
-      </c>
-      <c r="B55" t="s">
-        <v>77</v>
-      </c>
-      <c r="C55" t="s">
-        <v>31</v>
-      </c>
-      <c r="D55" t="s">
-        <v>80</v>
-      </c>
-      <c r="E55" t="s">
-        <v>16</v>
-      </c>
-      <c r="F55" t="s">
-        <v>113</v>
-      </c>
-      <c r="G55" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" t="s">
-        <v>30</v>
-      </c>
-      <c r="B56" t="s">
-        <v>77</v>
-      </c>
-      <c r="C56" t="s">
-        <v>31</v>
-      </c>
-      <c r="D56" t="s">
-        <v>82</v>
-      </c>
-      <c r="E56" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" t="s">
-        <v>30</v>
-      </c>
-      <c r="B57" t="s">
-        <v>77</v>
-      </c>
-      <c r="C57" t="s">
-        <v>31</v>
-      </c>
-      <c r="D57" t="s">
-        <v>84</v>
-      </c>
-      <c r="E57" t="s">
-        <v>16</v>
-      </c>
-      <c r="F57" t="s">
-        <v>114</v>
-      </c>
-      <c r="G57" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" t="s">
-        <v>32</v>
-      </c>
-      <c r="B58" t="s">
-        <v>77</v>
-      </c>
-      <c r="C58" t="s">
-        <v>33</v>
-      </c>
-      <c r="D58" t="s">
-        <v>66</v>
-      </c>
-      <c r="E58" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" t="s">
-        <v>32</v>
-      </c>
-      <c r="B59" t="s">
-        <v>77</v>
-      </c>
-      <c r="C59" t="s">
-        <v>33</v>
-      </c>
-      <c r="D59" t="s">
-        <v>69</v>
-      </c>
-      <c r="E59" t="s">
-        <v>20</v>
-      </c>
-      <c r="G59" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" t="s">
-        <v>32</v>
-      </c>
-      <c r="B60" t="s">
-        <v>77</v>
-      </c>
-      <c r="C60" t="s">
-        <v>33</v>
-      </c>
-      <c r="D60" t="s">
-        <v>71</v>
-      </c>
-      <c r="E60" t="s">
-        <v>16</v>
-      </c>
-      <c r="F60" t="s">
-        <v>115</v>
-      </c>
-      <c r="G60" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" t="s">
-        <v>32</v>
-      </c>
-      <c r="B61" t="s">
-        <v>77</v>
-      </c>
-      <c r="C61" t="s">
-        <v>33</v>
-      </c>
-      <c r="D61" t="s">
-        <v>75</v>
-      </c>
-      <c r="E61" t="s">
-        <v>20</v>
-      </c>
-      <c r="G61" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" t="s">
-        <v>32</v>
-      </c>
-      <c r="B62" t="s">
-        <v>77</v>
-      </c>
-      <c r="C62" t="s">
-        <v>33</v>
-      </c>
-      <c r="D62" t="s">
-        <v>77</v>
-      </c>
-      <c r="E62" t="s">
-        <v>15</v>
-      </c>
-      <c r="F62" t="s">
-        <v>116</v>
-      </c>
-      <c r="G62" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" t="s">
-        <v>32</v>
-      </c>
-      <c r="B63" t="s">
-        <v>77</v>
-      </c>
-      <c r="C63" t="s">
-        <v>33</v>
-      </c>
-      <c r="D63" t="s">
-        <v>80</v>
-      </c>
-      <c r="E63" t="s">
-        <v>16</v>
-      </c>
-      <c r="F63" t="s">
-        <v>106</v>
-      </c>
-      <c r="G63" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" t="s">
-        <v>32</v>
-      </c>
-      <c r="B64" t="s">
-        <v>77</v>
-      </c>
-      <c r="C64" t="s">
-        <v>33</v>
-      </c>
-      <c r="D64" t="s">
-        <v>82</v>
-      </c>
-      <c r="E64" t="s">
-        <v>15</v>
-      </c>
-      <c r="F64" t="s">
-        <v>117</v>
-      </c>
-      <c r="G64" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" t="s">
-        <v>32</v>
-      </c>
-      <c r="B65" t="s">
-        <v>77</v>
-      </c>
-      <c r="C65" t="s">
-        <v>33</v>
-      </c>
-      <c r="D65" t="s">
-        <v>84</v>
-      </c>
-      <c r="E65" t="s">
-        <v>16</v>
-      </c>
-      <c r="F65" t="s">
-        <v>118</v>
-      </c>
-      <c r="G65" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" t="s">
-        <v>35</v>
-      </c>
-      <c r="B66" t="s">
-        <v>119</v>
-      </c>
-      <c r="C66" t="s">
-        <v>36</v>
-      </c>
-      <c r="D66" t="s">
-        <v>66</v>
-      </c>
-      <c r="E66" t="s">
-        <v>20</v>
-      </c>
-      <c r="G66" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" t="s">
-        <v>35</v>
-      </c>
-      <c r="B67" t="s">
-        <v>119</v>
-      </c>
-      <c r="C67" t="s">
-        <v>36</v>
-      </c>
-      <c r="D67" t="s">
-        <v>69</v>
-      </c>
-      <c r="E67" t="s">
-        <v>20</v>
-      </c>
-      <c r="G67" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" t="s">
-        <v>35</v>
-      </c>
-      <c r="B68" t="s">
-        <v>119</v>
-      </c>
-      <c r="C68" t="s">
-        <v>36</v>
-      </c>
-      <c r="D68" t="s">
-        <v>71</v>
-      </c>
-      <c r="E68" t="s">
-        <v>16</v>
-      </c>
-      <c r="F68" t="s">
-        <v>120</v>
-      </c>
-      <c r="G68" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" t="s">
-        <v>35</v>
-      </c>
-      <c r="B69" t="s">
-        <v>119</v>
-      </c>
-      <c r="C69" t="s">
-        <v>36</v>
-      </c>
-      <c r="D69" t="s">
-        <v>75</v>
-      </c>
-      <c r="E69" t="s">
-        <v>20</v>
-      </c>
-      <c r="G69" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" t="s">
-        <v>35</v>
-      </c>
-      <c r="B70" t="s">
-        <v>119</v>
-      </c>
-      <c r="C70" t="s">
-        <v>36</v>
-      </c>
-      <c r="D70" t="s">
-        <v>77</v>
-      </c>
-      <c r="E70" t="s">
-        <v>15</v>
-      </c>
-      <c r="F70" t="s">
-        <v>121</v>
-      </c>
-      <c r="G70" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" t="s">
-        <v>35</v>
-      </c>
-      <c r="B71" t="s">
-        <v>119</v>
-      </c>
-      <c r="C71" t="s">
-        <v>36</v>
-      </c>
-      <c r="D71" t="s">
-        <v>80</v>
-      </c>
-      <c r="E71" t="s">
-        <v>16</v>
-      </c>
-      <c r="G71" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" t="s">
-        <v>35</v>
-      </c>
-      <c r="B72" t="s">
-        <v>119</v>
-      </c>
-      <c r="C72" t="s">
-        <v>36</v>
-      </c>
-      <c r="D72" t="s">
-        <v>82</v>
-      </c>
-      <c r="E72" t="s">
-        <v>15</v>
-      </c>
-      <c r="F72" t="s">
-        <v>122</v>
-      </c>
-      <c r="G72" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" t="s">
-        <v>35</v>
-      </c>
-      <c r="B73" t="s">
-        <v>119</v>
-      </c>
-      <c r="C73" t="s">
-        <v>36</v>
-      </c>
-      <c r="D73" t="s">
-        <v>84</v>
-      </c>
-      <c r="E73" t="s">
-        <v>16</v>
-      </c>
-      <c r="F73" t="s">
-        <v>123</v>
-      </c>
-      <c r="G73" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" t="s">
-        <v>119</v>
-      </c>
-      <c r="C74" t="s">
-        <v>38</v>
-      </c>
-      <c r="D74" t="s">
-        <v>66</v>
-      </c>
-      <c r="E74" t="s">
-        <v>20</v>
-      </c>
-      <c r="G74" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" t="s">
-        <v>119</v>
-      </c>
-      <c r="C75" t="s">
-        <v>38</v>
-      </c>
-      <c r="D75" t="s">
-        <v>69</v>
-      </c>
-      <c r="E75" t="s">
-        <v>20</v>
-      </c>
-      <c r="G75" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" t="s">
-        <v>119</v>
-      </c>
-      <c r="C76" t="s">
-        <v>38</v>
-      </c>
-      <c r="D76" t="s">
-        <v>71</v>
-      </c>
-      <c r="E76" t="s">
-        <v>16</v>
-      </c>
-      <c r="F76" t="s">
-        <v>124</v>
-      </c>
-      <c r="G76" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" t="s">
-        <v>37</v>
-      </c>
-      <c r="B77" t="s">
-        <v>119</v>
-      </c>
-      <c r="C77" t="s">
-        <v>38</v>
-      </c>
-      <c r="D77" t="s">
-        <v>75</v>
-      </c>
-      <c r="E77" t="s">
-        <v>20</v>
-      </c>
-      <c r="G77" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" t="s">
-        <v>37</v>
-      </c>
-      <c r="B78" t="s">
-        <v>119</v>
-      </c>
-      <c r="C78" t="s">
-        <v>38</v>
-      </c>
-      <c r="D78" t="s">
-        <v>77</v>
-      </c>
-      <c r="E78" t="s">
-        <v>15</v>
-      </c>
-      <c r="F78" t="s">
-        <v>125</v>
-      </c>
-      <c r="G78" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" t="s">
-        <v>37</v>
-      </c>
-      <c r="B79" t="s">
-        <v>119</v>
-      </c>
-      <c r="C79" t="s">
-        <v>38</v>
-      </c>
-      <c r="D79" t="s">
-        <v>80</v>
-      </c>
-      <c r="E79" t="s">
-        <v>16</v>
-      </c>
-      <c r="G79" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" t="s">
-        <v>37</v>
-      </c>
-      <c r="B80" t="s">
-        <v>119</v>
-      </c>
-      <c r="C80" t="s">
-        <v>38</v>
-      </c>
-      <c r="D80" t="s">
-        <v>82</v>
-      </c>
-      <c r="E80" t="s">
-        <v>15</v>
-      </c>
-      <c r="F80" t="s">
-        <v>126</v>
-      </c>
-      <c r="G80" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" t="s">
-        <v>37</v>
-      </c>
-      <c r="B81" t="s">
-        <v>119</v>
-      </c>
-      <c r="C81" t="s">
-        <v>38</v>
-      </c>
-      <c r="D81" t="s">
-        <v>84</v>
-      </c>
-      <c r="E81" t="s">
-        <v>16</v>
-      </c>
-      <c r="F81" t="s">
-        <v>127</v>
-      </c>
-      <c r="G81" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" t="s">
-        <v>39</v>
-      </c>
-      <c r="B82" t="s">
-        <v>119</v>
-      </c>
-      <c r="C82" t="s">
-        <v>40</v>
-      </c>
-      <c r="D82" t="s">
-        <v>66</v>
-      </c>
-      <c r="E82" t="s">
-        <v>20</v>
-      </c>
-      <c r="G82" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" t="s">
-        <v>39</v>
-      </c>
-      <c r="B83" t="s">
-        <v>119</v>
-      </c>
-      <c r="C83" t="s">
-        <v>40</v>
-      </c>
-      <c r="D83" t="s">
-        <v>69</v>
-      </c>
-      <c r="E83" t="s">
-        <v>16</v>
-      </c>
-      <c r="F83" t="s">
-        <v>128</v>
-      </c>
-      <c r="G83" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" t="s">
-        <v>39</v>
-      </c>
-      <c r="B84" t="s">
-        <v>119</v>
-      </c>
-      <c r="C84" t="s">
-        <v>40</v>
-      </c>
-      <c r="D84" t="s">
-        <v>71</v>
-      </c>
-      <c r="E84" t="s">
-        <v>16</v>
-      </c>
-      <c r="F84" t="s">
-        <v>129</v>
-      </c>
-      <c r="G84" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" t="s">
-        <v>39</v>
-      </c>
-      <c r="B85" t="s">
-        <v>119</v>
-      </c>
-      <c r="C85" t="s">
-        <v>40</v>
-      </c>
-      <c r="D85" t="s">
-        <v>75</v>
-      </c>
-      <c r="E85" t="s">
-        <v>20</v>
-      </c>
-      <c r="G85" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" t="s">
-        <v>39</v>
-      </c>
-      <c r="B86" t="s">
-        <v>119</v>
-      </c>
-      <c r="C86" t="s">
-        <v>40</v>
-      </c>
-      <c r="D86" t="s">
-        <v>77</v>
-      </c>
-      <c r="E86" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" t="s">
-        <v>130</v>
-      </c>
-      <c r="G86" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" t="s">
-        <v>39</v>
-      </c>
-      <c r="B87" t="s">
-        <v>119</v>
-      </c>
-      <c r="C87" t="s">
-        <v>40</v>
-      </c>
-      <c r="D87" t="s">
-        <v>80</v>
-      </c>
-      <c r="E87" t="s">
-        <v>17</v>
-      </c>
-      <c r="F87" t="s">
-        <v>131</v>
-      </c>
-      <c r="G87" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" t="s">
-        <v>39</v>
-      </c>
-      <c r="B88" t="s">
-        <v>119</v>
-      </c>
-      <c r="C88" t="s">
-        <v>40</v>
-      </c>
-      <c r="D88" t="s">
-        <v>82</v>
-      </c>
-      <c r="E88" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" t="s">
-        <v>132</v>
-      </c>
-      <c r="G88" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" t="s">
-        <v>39</v>
-      </c>
-      <c r="B89" t="s">
-        <v>119</v>
-      </c>
-      <c r="C89" t="s">
-        <v>40</v>
-      </c>
-      <c r="D89" t="s">
-        <v>84</v>
-      </c>
-      <c r="E89" t="s">
-        <v>16</v>
-      </c>
-      <c r="F89" t="s">
-        <v>133</v>
-      </c>
-      <c r="G89" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" t="s">
-        <v>41</v>
-      </c>
-      <c r="B90" t="s">
-        <v>119</v>
-      </c>
-      <c r="C90" t="s">
-        <v>42</v>
-      </c>
-      <c r="D90" t="s">
-        <v>66</v>
-      </c>
-      <c r="E90" t="s">
-        <v>20</v>
-      </c>
-      <c r="G90" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" t="s">
-        <v>41</v>
-      </c>
-      <c r="B91" t="s">
-        <v>119</v>
-      </c>
-      <c r="C91" t="s">
-        <v>42</v>
-      </c>
-      <c r="D91" t="s">
-        <v>69</v>
-      </c>
-      <c r="E91" t="s">
-        <v>20</v>
-      </c>
-      <c r="G91" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" t="s">
-        <v>41</v>
-      </c>
-      <c r="B92" t="s">
-        <v>119</v>
-      </c>
-      <c r="C92" t="s">
-        <v>42</v>
-      </c>
-      <c r="D92" t="s">
-        <v>71</v>
-      </c>
-      <c r="E92" t="s">
-        <v>16</v>
-      </c>
-      <c r="F92" t="s">
-        <v>134</v>
-      </c>
-      <c r="G92" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" t="s">
-        <v>41</v>
-      </c>
-      <c r="B93" t="s">
-        <v>119</v>
-      </c>
-      <c r="C93" t="s">
-        <v>42</v>
-      </c>
-      <c r="D93" t="s">
-        <v>75</v>
-      </c>
-      <c r="E93" t="s">
-        <v>20</v>
-      </c>
-      <c r="G93" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" t="s">
-        <v>41</v>
-      </c>
-      <c r="B94" t="s">
-        <v>119</v>
-      </c>
-      <c r="C94" t="s">
-        <v>42</v>
-      </c>
-      <c r="D94" t="s">
-        <v>77</v>
-      </c>
-      <c r="E94" t="s">
-        <v>15</v>
-      </c>
-      <c r="F94" t="s">
-        <v>135</v>
-      </c>
-      <c r="G94" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" t="s">
-        <v>41</v>
-      </c>
-      <c r="B95" t="s">
-        <v>119</v>
-      </c>
-      <c r="C95" t="s">
-        <v>42</v>
-      </c>
-      <c r="D95" t="s">
-        <v>80</v>
-      </c>
-      <c r="E95" t="s">
-        <v>16</v>
-      </c>
-      <c r="G95" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" t="s">
-        <v>41</v>
-      </c>
-      <c r="B96" t="s">
-        <v>119</v>
-      </c>
-      <c r="C96" t="s">
-        <v>42</v>
-      </c>
-      <c r="D96" t="s">
-        <v>82</v>
-      </c>
-      <c r="E96" t="s">
-        <v>15</v>
-      </c>
-      <c r="F96" t="s">
-        <v>136</v>
-      </c>
-      <c r="G96" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" t="s">
-        <v>41</v>
-      </c>
-      <c r="B97" t="s">
-        <v>119</v>
-      </c>
-      <c r="C97" t="s">
-        <v>42</v>
-      </c>
-      <c r="D97" t="s">
-        <v>84</v>
-      </c>
-      <c r="E97" t="s">
-        <v>16</v>
-      </c>
-      <c r="F97" t="s">
-        <v>137</v>
-      </c>
-      <c r="G97" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98" t="s">
-        <v>43</v>
-      </c>
-      <c r="B98" t="s">
-        <v>119</v>
-      </c>
-      <c r="C98" t="s">
-        <v>44</v>
-      </c>
-      <c r="D98" t="s">
-        <v>66</v>
-      </c>
-      <c r="E98" t="s">
-        <v>20</v>
-      </c>
-      <c r="G98" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" t="s">
-        <v>43</v>
-      </c>
-      <c r="B99" t="s">
-        <v>119</v>
-      </c>
-      <c r="C99" t="s">
-        <v>44</v>
-      </c>
-      <c r="D99" t="s">
-        <v>69</v>
-      </c>
-      <c r="E99" t="s">
-        <v>20</v>
-      </c>
-      <c r="G99" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B100" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C100" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F100" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G100" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="H100" s="13" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" t="s">
-        <v>43</v>
-      </c>
-      <c r="B101" t="s">
-        <v>119</v>
-      </c>
-      <c r="C101" t="s">
-        <v>44</v>
-      </c>
-      <c r="D101" t="s">
-        <v>75</v>
-      </c>
-      <c r="E101" t="s">
-        <v>20</v>
-      </c>
-      <c r="G101" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102" t="s">
-        <v>43</v>
-      </c>
-      <c r="B102" t="s">
-        <v>119</v>
-      </c>
-      <c r="C102" t="s">
-        <v>44</v>
-      </c>
-      <c r="D102" t="s">
-        <v>77</v>
-      </c>
-      <c r="E102" t="s">
-        <v>15</v>
-      </c>
-      <c r="F102" t="s">
-        <v>140</v>
-      </c>
-      <c r="G102" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" t="s">
-        <v>43</v>
-      </c>
-      <c r="B103" t="s">
-        <v>119</v>
-      </c>
-      <c r="C103" t="s">
-        <v>44</v>
-      </c>
-      <c r="D103" t="s">
-        <v>80</v>
-      </c>
-      <c r="E103" t="s">
-        <v>16</v>
-      </c>
-      <c r="F103" t="s">
-        <v>106</v>
-      </c>
-      <c r="G103" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" t="s">
-        <v>43</v>
-      </c>
-      <c r="B104" t="s">
-        <v>119</v>
-      </c>
-      <c r="C104" t="s">
-        <v>44</v>
-      </c>
-      <c r="D104" t="s">
-        <v>82</v>
-      </c>
-      <c r="E104" t="s">
-        <v>15</v>
-      </c>
-      <c r="F104" t="s">
-        <v>141</v>
-      </c>
-      <c r="G104" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105" t="s">
-        <v>43</v>
-      </c>
-      <c r="B105" t="s">
-        <v>119</v>
-      </c>
-      <c r="C105" t="s">
-        <v>44</v>
-      </c>
-      <c r="D105" t="s">
-        <v>84</v>
-      </c>
-      <c r="E105" t="s">
-        <v>15</v>
-      </c>
-      <c r="F105" t="s">
-        <v>142</v>
-      </c>
-      <c r="G105" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106" t="s">
-        <v>45</v>
-      </c>
-      <c r="B106" t="s">
-        <v>119</v>
-      </c>
-      <c r="C106" t="s">
-        <v>46</v>
-      </c>
-      <c r="D106" t="s">
-        <v>66</v>
-      </c>
-      <c r="E106" t="s">
-        <v>20</v>
-      </c>
-      <c r="F106" t="s">
-        <v>143</v>
-      </c>
-      <c r="G106" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107" t="s">
-        <v>45</v>
-      </c>
-      <c r="B107" t="s">
-        <v>119</v>
-      </c>
-      <c r="C107" t="s">
-        <v>46</v>
-      </c>
-      <c r="D107" t="s">
-        <v>69</v>
-      </c>
-      <c r="E107" t="s">
-        <v>20</v>
-      </c>
-      <c r="G107" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A108" t="s">
-        <v>45</v>
-      </c>
-      <c r="B108" t="s">
-        <v>119</v>
-      </c>
-      <c r="C108" t="s">
-        <v>46</v>
-      </c>
-      <c r="D108" t="s">
-        <v>71</v>
-      </c>
-      <c r="E108" t="s">
-        <v>16</v>
-      </c>
-      <c r="F108" t="s">
-        <v>144</v>
-      </c>
-      <c r="G108" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A109" t="s">
-        <v>45</v>
-      </c>
-      <c r="B109" t="s">
-        <v>119</v>
-      </c>
-      <c r="C109" t="s">
-        <v>46</v>
-      </c>
-      <c r="D109" t="s">
-        <v>75</v>
-      </c>
-      <c r="E109" t="s">
-        <v>20</v>
-      </c>
-      <c r="G109" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A110" t="s">
-        <v>45</v>
-      </c>
-      <c r="B110" t="s">
-        <v>119</v>
-      </c>
-      <c r="C110" t="s">
-        <v>46</v>
-      </c>
-      <c r="D110" t="s">
-        <v>77</v>
-      </c>
-      <c r="E110" t="s">
-        <v>15</v>
-      </c>
-      <c r="F110" t="s">
-        <v>145</v>
-      </c>
-      <c r="G110" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A111" t="s">
-        <v>45</v>
-      </c>
-      <c r="B111" t="s">
-        <v>119</v>
-      </c>
-      <c r="C111" t="s">
-        <v>46</v>
-      </c>
-      <c r="D111" t="s">
-        <v>80</v>
-      </c>
-      <c r="E111" t="s">
-        <v>16</v>
-      </c>
-      <c r="F111" t="s">
-        <v>106</v>
-      </c>
-      <c r="G111" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112" t="s">
-        <v>45</v>
-      </c>
-      <c r="B112" t="s">
-        <v>119</v>
-      </c>
-      <c r="C112" t="s">
-        <v>46</v>
-      </c>
-      <c r="D112" t="s">
-        <v>82</v>
-      </c>
-      <c r="E112" t="s">
-        <v>15</v>
-      </c>
-      <c r="F112" t="s">
-        <v>146</v>
-      </c>
-      <c r="G112" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113" t="s">
-        <v>45</v>
-      </c>
-      <c r="B113" t="s">
-        <v>119</v>
-      </c>
-      <c r="C113" t="s">
-        <v>46</v>
-      </c>
-      <c r="D113" t="s">
-        <v>84</v>
-      </c>
-      <c r="E113" t="s">
-        <v>15</v>
-      </c>
-      <c r="F113" t="s">
-        <v>147</v>
-      </c>
-      <c r="G113" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A114" t="s">
-        <v>47</v>
-      </c>
-      <c r="B114" t="s">
-        <v>119</v>
-      </c>
-      <c r="C114" t="s">
-        <v>48</v>
-      </c>
-      <c r="D114" t="s">
-        <v>66</v>
-      </c>
-      <c r="E114" t="s">
-        <v>20</v>
-      </c>
-      <c r="G114" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115" t="s">
-        <v>47</v>
-      </c>
-      <c r="B115" t="s">
-        <v>119</v>
-      </c>
-      <c r="C115" t="s">
-        <v>48</v>
-      </c>
-      <c r="D115" t="s">
-        <v>69</v>
-      </c>
-      <c r="E115" t="s">
-        <v>20</v>
-      </c>
-      <c r="G115" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A116" t="s">
-        <v>47</v>
-      </c>
-      <c r="B116" t="s">
-        <v>119</v>
-      </c>
-      <c r="C116" t="s">
-        <v>48</v>
-      </c>
-      <c r="D116" t="s">
-        <v>71</v>
-      </c>
-      <c r="E116" t="s">
-        <v>16</v>
-      </c>
-      <c r="F116" t="s">
+      <c r="F137" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="G116" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A117" t="s">
-        <v>47</v>
-      </c>
-      <c r="B117" t="s">
-        <v>119</v>
-      </c>
-      <c r="C117" t="s">
-        <v>48</v>
-      </c>
-      <c r="D117" t="s">
-        <v>75</v>
-      </c>
-      <c r="E117" t="s">
-        <v>20</v>
-      </c>
-      <c r="G117" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A118" t="s">
-        <v>47</v>
-      </c>
-      <c r="B118" t="s">
-        <v>119</v>
-      </c>
-      <c r="C118" t="s">
-        <v>48</v>
-      </c>
-      <c r="D118" t="s">
-        <v>77</v>
-      </c>
-      <c r="E118" t="s">
-        <v>15</v>
-      </c>
-      <c r="F118" t="s">
-        <v>149</v>
-      </c>
-      <c r="G118" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A119" t="s">
-        <v>47</v>
-      </c>
-      <c r="B119" t="s">
-        <v>119</v>
-      </c>
-      <c r="C119" t="s">
-        <v>48</v>
-      </c>
-      <c r="D119" t="s">
-        <v>80</v>
-      </c>
-      <c r="E119" t="s">
-        <v>16</v>
-      </c>
-      <c r="F119" t="s">
-        <v>106</v>
-      </c>
-      <c r="G119" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A120" t="s">
-        <v>47</v>
-      </c>
-      <c r="B120" t="s">
-        <v>119</v>
-      </c>
-      <c r="C120" t="s">
-        <v>48</v>
-      </c>
-      <c r="D120" t="s">
-        <v>82</v>
-      </c>
-      <c r="E120" t="s">
-        <v>15</v>
-      </c>
-      <c r="F120" t="s">
-        <v>150</v>
-      </c>
-      <c r="G120" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A121" t="s">
-        <v>47</v>
-      </c>
-      <c r="B121" t="s">
-        <v>119</v>
-      </c>
-      <c r="C121" t="s">
-        <v>48</v>
-      </c>
-      <c r="D121" t="s">
-        <v>84</v>
-      </c>
-      <c r="E121" t="s">
-        <v>15</v>
-      </c>
-      <c r="F121" t="s">
-        <v>151</v>
-      </c>
-      <c r="G121" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A122" t="s">
-        <v>49</v>
-      </c>
-      <c r="B122" t="s">
-        <v>119</v>
-      </c>
-      <c r="C122" t="s">
-        <v>50</v>
-      </c>
-      <c r="D122" t="s">
-        <v>66</v>
-      </c>
-      <c r="E122" t="s">
-        <v>20</v>
-      </c>
-      <c r="G122" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A123" t="s">
-        <v>49</v>
-      </c>
-      <c r="B123" t="s">
-        <v>119</v>
-      </c>
-      <c r="C123" t="s">
-        <v>50</v>
-      </c>
-      <c r="D123" t="s">
-        <v>69</v>
-      </c>
-      <c r="E123" t="s">
-        <v>16</v>
-      </c>
-      <c r="F123" t="s">
-        <v>152</v>
-      </c>
-      <c r="G123" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" t="s">
-        <v>49</v>
-      </c>
-      <c r="B124" t="s">
-        <v>119</v>
-      </c>
-      <c r="C124" t="s">
-        <v>50</v>
-      </c>
-      <c r="D124" t="s">
-        <v>71</v>
-      </c>
-      <c r="E124" t="s">
-        <v>15</v>
-      </c>
-      <c r="F124" t="s">
-        <v>153</v>
-      </c>
-      <c r="G124" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A125" t="s">
-        <v>49</v>
-      </c>
-      <c r="B125" t="s">
-        <v>119</v>
-      </c>
-      <c r="C125" t="s">
-        <v>50</v>
-      </c>
-      <c r="D125" t="s">
-        <v>75</v>
-      </c>
-      <c r="E125" t="s">
-        <v>20</v>
-      </c>
-      <c r="G125" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A126" t="s">
-        <v>49</v>
-      </c>
-      <c r="B126" t="s">
-        <v>119</v>
-      </c>
-      <c r="C126" t="s">
-        <v>50</v>
-      </c>
-      <c r="D126" t="s">
-        <v>77</v>
-      </c>
-      <c r="E126" t="s">
-        <v>15</v>
-      </c>
-      <c r="F126" t="s">
-        <v>154</v>
-      </c>
-      <c r="G126" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A127" t="s">
-        <v>49</v>
-      </c>
-      <c r="B127" t="s">
-        <v>119</v>
-      </c>
-      <c r="C127" t="s">
-        <v>50</v>
-      </c>
-      <c r="D127" t="s">
-        <v>80</v>
-      </c>
-      <c r="E127" t="s">
-        <v>16</v>
-      </c>
-      <c r="F127" t="s">
-        <v>106</v>
-      </c>
-      <c r="G127" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A128" t="s">
-        <v>49</v>
-      </c>
-      <c r="B128" t="s">
-        <v>119</v>
-      </c>
-      <c r="C128" t="s">
-        <v>50</v>
-      </c>
-      <c r="D128" t="s">
-        <v>82</v>
-      </c>
-      <c r="E128" t="s">
-        <v>15</v>
-      </c>
-      <c r="F128" t="s">
-        <v>155</v>
-      </c>
-      <c r="G128" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A129" t="s">
-        <v>49</v>
-      </c>
-      <c r="B129" t="s">
-        <v>119</v>
-      </c>
-      <c r="C129" t="s">
-        <v>50</v>
-      </c>
-      <c r="D129" t="s">
-        <v>84</v>
-      </c>
-      <c r="E129" t="s">
-        <v>15</v>
-      </c>
-      <c r="F129" t="s">
-        <v>156</v>
-      </c>
-      <c r="G129" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A130" t="s">
-        <v>52</v>
-      </c>
-      <c r="B130" t="s">
-        <v>157</v>
-      </c>
-      <c r="C130" t="s">
-        <v>53</v>
-      </c>
-      <c r="D130" t="s">
-        <v>66</v>
-      </c>
-      <c r="E130" t="s">
-        <v>17</v>
-      </c>
-      <c r="F130" t="s">
-        <v>158</v>
-      </c>
-      <c r="G130" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A131" t="s">
-        <v>52</v>
-      </c>
-      <c r="B131" t="s">
-        <v>157</v>
-      </c>
-      <c r="C131" t="s">
-        <v>53</v>
-      </c>
-      <c r="D131" t="s">
-        <v>69</v>
-      </c>
-      <c r="E131" t="s">
-        <v>20</v>
-      </c>
-      <c r="G131" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A132" t="s">
-        <v>52</v>
-      </c>
-      <c r="B132" t="s">
-        <v>157</v>
-      </c>
-      <c r="C132" t="s">
-        <v>53</v>
-      </c>
-      <c r="D132" t="s">
-        <v>71</v>
-      </c>
-      <c r="E132" t="s">
-        <v>16</v>
-      </c>
-      <c r="F132" t="s">
-        <v>159</v>
-      </c>
-      <c r="G132" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A133" t="s">
-        <v>52</v>
-      </c>
-      <c r="B133" t="s">
-        <v>157</v>
-      </c>
-      <c r="C133" t="s">
-        <v>53</v>
-      </c>
-      <c r="D133" t="s">
-        <v>75</v>
-      </c>
-      <c r="E133" t="s">
-        <v>15</v>
-      </c>
-      <c r="F133" t="s">
-        <v>160</v>
-      </c>
-      <c r="G133" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A134" t="s">
-        <v>52</v>
-      </c>
-      <c r="B134" t="s">
-        <v>157</v>
-      </c>
-      <c r="C134" t="s">
-        <v>53</v>
-      </c>
-      <c r="D134" t="s">
-        <v>77</v>
-      </c>
-      <c r="E134" t="s">
-        <v>16</v>
-      </c>
-      <c r="F134" t="s">
-        <v>161</v>
-      </c>
-      <c r="G134" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A135" t="s">
-        <v>52</v>
-      </c>
-      <c r="B135" t="s">
-        <v>157</v>
-      </c>
-      <c r="C135" t="s">
-        <v>53</v>
-      </c>
-      <c r="D135" t="s">
-        <v>80</v>
-      </c>
-      <c r="E135" t="s">
-        <v>16</v>
-      </c>
-      <c r="G135" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A136" t="s">
-        <v>52</v>
-      </c>
-      <c r="B136" t="s">
-        <v>157</v>
-      </c>
-      <c r="C136" t="s">
-        <v>53</v>
-      </c>
-      <c r="D136" t="s">
-        <v>82</v>
-      </c>
-      <c r="E136" t="s">
-        <v>17</v>
-      </c>
-      <c r="F136" t="s">
-        <v>162</v>
-      </c>
-      <c r="G136" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A137" t="s">
-        <v>52</v>
-      </c>
-      <c r="B137" t="s">
-        <v>157</v>
-      </c>
-      <c r="C137" t="s">
-        <v>53</v>
-      </c>
-      <c r="D137" t="s">
-        <v>84</v>
-      </c>
-      <c r="E137" t="s">
-        <v>15</v>
-      </c>
-      <c r="F137" t="s">
-        <v>163</v>
-      </c>
-      <c r="G137" t="s">
-        <v>68</v>
+      <c r="G137" s="31" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/marketing-ownership-map.xlsx
+++ b/marketing-ownership-map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://quickbase-my.sharepoint.com/personal/lrusinova_quickbase_com/Documents/Documents/Project Management MCP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{4B02C43F-0DD0-4BE7-85A2-444C4797CC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A2C030C-1D80-431A-B521-74B6ADBE0846}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="13_ncr:1_{4B02C43F-0DD0-4BE7-85A2-444C4797CC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B20F4D6-FE02-49B6-93C6-4D1457E44F70}"/>
   <bookViews>
     <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8904" xr2:uid="{D9A43224-3FE6-4782-BEE1-41A45989FA1C}"/>
   </bookViews>
@@ -173,7 +173,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{6261401D-3AC1-4D7A-9F30-28C483E5AAA0}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{DEA2D4DF-FD84-4A72-87D2-1EC0D884F158}">
       <text>
         <r>
           <rPr>
@@ -183,7 +183,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>Defines channel/activation needs for the launch. Accountable instead of PMM when the project is a non-launch Campaign (see Project Type Guide); PMM is Accountable for product/feature Launches. Resolved Aug 2026. Still open: how this relates to Paid Media's own R at this stage - see Open Conflict below.</t>
+          <t>Defines channel/activation needs for the launch, including the paid approach as part of the overall campaign brief (what needs to happen). Accountable instead of PMM when the project is a non-launch Campaign (see Project Type Guide); PMM is Accountable for product/feature Launches. Paid Media weighs in on feasibility; ad-spend budget itself sits with Digital, outside this RACI. Fully resolved Aug 2026.</t>
         </r>
       </text>
     </comment>
@@ -201,7 +201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{50BC8400-2346-4431-8350-F3ABB5FAB396}">
+    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{205C4F0A-0C76-44E3-A83C-35B0403C6948}">
       <text>
         <r>
           <rPr>
@@ -209,9 +209,9 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
-          <t>Executes paid, email, and channel activation.</t>
+          <t>Directs the campaign and executes email/lifecycle activation directly; paid tactical execution is Paid Media's lane per the Activation Planning boundary (resolved Aug 2026).</t>
         </r>
       </text>
     </comment>
@@ -859,7 +859,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{E7C06D9E-5457-4CB7-97C1-BE95537FA8C7}">
+    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{FE908144-C95C-4F7C-A645-05054DBC1C23}">
       <text>
         <r>
           <rPr>
@@ -867,10 +867,9 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
-          <t>Weighs in on paid feasibility and budget.
-CONFLICT: Potential overlap with Demand Gen's R here - confirm whether paid activation is a Demand Gen sub-decision or owned directly by Paid Media.</t>
+          <t>Weighs in on paid feasibility; Demand Gen decides the paid/channel approach as part of the overall campaign definition. Ad-spend budget is owned by Digital, not Demand Gen or Paid Media. Resolved Aug 2026.</t>
         </r>
       </text>
     </comment>
@@ -902,7 +901,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{DC324683-05A9-4B88-B540-4DF6198C356E}">
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{FB44F423-2EFB-4836-89C8-7B914862C4CE}">
       <text>
         <r>
           <rPr>
@@ -910,9 +909,9 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
-          <t>Runs paid campaigns at launch.</t>
+          <t>Runs paid campaigns at launch, per Demand Gen's campaign direction set at Activation Planning. Ad-spend budget owned by Digital.</t>
         </r>
       </text>
     </comment>
@@ -1257,7 +1256,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="206">
   <si>
     <t>Marketing Ownership Map - RACI Matrix (Working Draft)</t>
   </si>
@@ -1415,9 +1414,6 @@
     <t>Luiza Rusinova, Soumya Ghosh</t>
   </si>
   <si>
-    <t>OPEN CONFLICTS - NEEDS DISCUSSION</t>
-  </si>
-  <si>
     <t>Team Group</t>
   </si>
   <si>
@@ -1460,9 +1456,6 @@
     <t>Activation Planning</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>Brief to Centralized Teams</t>
   </si>
   <si>
@@ -1496,9 +1489,6 @@
     <t>Co-briefs on funnel and channel requirements.</t>
   </si>
   <si>
-    <t>Executes paid, email, and channel activation.</t>
-  </si>
-  <si>
     <t>Reports channel performance against targets.</t>
   </si>
   <si>
@@ -1628,18 +1618,9 @@
     <t>Reports email performance.</t>
   </si>
   <si>
-    <t>Weighs in on paid feasibility and budget.</t>
-  </si>
-  <si>
-    <t>Potential overlap with Demand Gen's R here - confirm whether paid activation is a Demand Gen sub-decision or owned directly by Paid Media.</t>
-  </si>
-  <si>
     <t>Builds paid landing pages and ad creative/campaign setup.</t>
   </si>
   <si>
-    <t>Runs paid campaigns at launch.</t>
-  </si>
-  <si>
     <t>Reports paid performance and ROI.</t>
   </si>
   <si>
@@ -1862,25 +1843,37 @@
     <t>R/A</t>
   </si>
   <si>
-    <t>1. Paid Media vs. Demand Gen: Unclear whether paid activation is a Demand Gen sub-decision or owned directly by Paid Media. Both show involvement without a clear boundary.</t>
-  </si>
-  <si>
     <t>Defines what the launch needs from centralized teams. Accountable for Launches (Demand Gen is Accountable for Campaigns).</t>
   </si>
   <si>
     <t>Owns the Launch Story &amp; Messaging Brief; signs off on final copy for accuracy.</t>
   </si>
   <si>
-    <t>Defines channel/activation needs for the launch. Accountable for Campaigns (PMM is Accountable for Launches).</t>
-  </si>
-  <si>
     <t>Executes creative direction/copywriting from PMM's brief; owns brand voice.</t>
   </si>
   <si>
     <t>Drafts and expands copy from PMM's brief for persona/channel fit.</t>
   </si>
   <si>
-    <t>1. Paid Media vs. Demand Gen - unclear whether paid activation is a Demand Gen sub-decision or owned directly by Paid Media.</t>
+    <t>CONFLICT LOG - ALL RESOLVED</t>
+  </si>
+  <si>
+    <t>All flagged conflicts resolved as of Aug 2026: (1) Partner Marketing routing/attribution - Meaghan Nickols named Channel Leader. (2) Activation Planning (PMM vs. Demand Gen) - PMM Accountable for Launches, Demand Gen Accountable for Campaigns. (3) Production (PMM vs. Brand/Positioning vs. Content) - PMM Accountable (owns the Launch Story &amp; Messaging Brief and final sign-off), Brand and Content Responsible for execution. (4) Paid Media vs. Demand Gen - Demand Gen owns the campaign definition and paid approach; Paid Media executes tactically; ad-spend budget sits with Digital.</t>
+  </si>
+  <si>
+    <t>Defines channel/activation needs for the launch, including the paid approach as part of the overall campaign brief. Accountable for Campaigns (PMM is Accountable for Launches). Paid Media weighs in on feasibility; budget sits with Digital. Resolved Aug 2026.</t>
+  </si>
+  <si>
+    <t>Directs the campaign and executes email/lifecycle activation directly; paid tactical execution is Paid Media's lane.</t>
+  </si>
+  <si>
+    <t>Weighs in on paid feasibility; Demand Gen decides the paid/channel approach. Ad-spend budget owned by Digital. Resolved Aug 2026.</t>
+  </si>
+  <si>
+    <t>Runs paid campaigns at launch, per Demand Gen's campaign direction. Ad-spend budget owned by Digital.</t>
+  </si>
+  <si>
+    <t>All open conflicts resolved as of Aug 2026 - Partner Marketing (Channel Leader named), Activation Planning, Production, and Paid Media vs. Demand Gen. See Ownership Matrix for full resolution notes.</t>
   </si>
 </sst>
 </file>
@@ -2056,7 +2049,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2107,12 +2100,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF23E30"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2145,7 +2132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2158,9 +2145,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2199,12 +2183,6 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2215,7 +2193,16 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2223,16 +2210,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4559,76 +4537,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.3" x14ac:dyDescent="0.85">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="13" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="19" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="1.4">
+      <c r="A5" s="20">
+        <v>17</v>
+      </c>
+      <c r="B5" s="22">
+        <v>8</v>
+      </c>
+      <c r="C5" s="24">
+        <v>14</v>
+      </c>
+      <c r="D5" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="23" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="14" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="20" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="40" customHeight="1" x14ac:dyDescent="1.4">
-      <c r="A5" s="21">
-        <v>17</v>
-      </c>
-      <c r="B5" s="23">
-        <v>8</v>
-      </c>
-      <c r="C5" s="25">
-        <v>14</v>
-      </c>
-      <c r="D5" s="27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>194</v>
-      </c>
-    </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A8" s="11" t="s">
-        <v>52</v>
+      <c r="A8" s="10" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="33" t="s">
-        <v>207</v>
+      <c r="A9" s="37" t="s">
+        <v>205</v>
       </c>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
       <c r="D9" s="34"/>
     </row>
     <row r="10" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="39"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
     </row>
     <row r="11" spans="1:10" ht="28" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="39"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="29" t="s">
-        <v>195</v>
+      <c r="A13" s="26" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -4636,13 +4614,13 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="I14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J14" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
@@ -4849,18 +4827,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.3" x14ac:dyDescent="0.7">
-      <c r="A1" s="13" t="s">
-        <v>149</v>
+      <c r="A1" s="12" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="14" t="s">
-        <v>150</v>
+      <c r="A2" s="13" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>4</v>
@@ -4887,482 +4865,482 @@
         <v>11</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>155</v>
+        <v>148</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>159</v>
+        <v>151</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>161</v>
+        <v>151</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J8" s="14" t="s">
         <v>157</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>165</v>
+        <v>151</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="4" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>158</v>
+        <v>148</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J10" s="15" t="s">
-        <v>167</v>
+        <v>148</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>158</v>
+        <v>148</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>169</v>
+        <v>148</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>158</v>
+        <v>148</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="J12" s="15" t="s">
-        <v>171</v>
+        <v>151</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>158</v>
+        <v>148</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>158</v>
+        <v>148</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="J13" s="15" t="s">
-        <v>173</v>
+        <v>151</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>158</v>
+        <v>148</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>158</v>
+        <v>148</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>175</v>
+        <v>151</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>158</v>
+        <v>148</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="J15" s="15" t="s">
-        <v>177</v>
+        <v>151</v>
+      </c>
+      <c r="J15" s="14" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>158</v>
+        <v>148</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J16" s="15" t="s">
-        <v>179</v>
+        <v>148</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="J17" s="15" t="s">
-        <v>181</v>
+        <v>151</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="J18" s="15" t="s">
-        <v>183</v>
+        <v>151</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>154</v>
+      <c r="A20" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>148</v>
       </c>
       <c r="C20" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="17" t="s">
-        <v>157</v>
+      <c r="B21" s="16" t="s">
+        <v>151</v>
       </c>
       <c r="C21" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="18" t="s">
-        <v>158</v>
+      <c r="B22" s="17" t="s">
+        <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -5452,16 +5430,16 @@
       <c r="D6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="37" t="s">
-        <v>200</v>
+      <c r="E6" s="30" t="s">
+        <v>194</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="8" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="7" t="s">
@@ -5481,19 +5459,19 @@
       <c r="C7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="38" t="s">
+      <c r="D7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="31" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="G7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="6" t="s">
@@ -5522,16 +5500,16 @@
       <c r="F8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="10" t="s">
+      <c r="I8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -5542,22 +5520,22 @@
       <c r="B9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="10" t="s">
+      <c r="C9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="10" t="s">
+      <c r="F9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I9" s="7" t="s">
@@ -5591,25 +5569,25 @@
       <c r="C11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="38" t="s">
+      <c r="D11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="31" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="10" t="s">
+      <c r="I11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -5623,13 +5601,13 @@
       <c r="C12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="10" t="s">
+      <c r="D12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G12" s="6" t="s">
@@ -5638,10 +5616,10 @@
       <c r="H12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="10" t="s">
+      <c r="I12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -5652,7 +5630,7 @@
       <c r="B13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="7" t="s">
@@ -5661,7 +5639,7 @@
       <c r="E13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G13" s="6" t="s">
@@ -5670,7 +5648,7 @@
       <c r="H13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="9" t="s">
         <v>20</v>
       </c>
       <c r="J13" s="7" t="s">
@@ -5684,16 +5662,16 @@
       <c r="B14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="10" t="s">
+      <c r="C14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="6" t="s">
@@ -5730,16 +5708,16 @@
       <c r="B16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="6" t="s">
@@ -5762,16 +5740,16 @@
       <c r="B17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="C17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G17" s="6" t="s">
@@ -5794,7 +5772,7 @@
       <c r="B18" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D18" s="7" t="s">
@@ -5803,13 +5781,13 @@
       <c r="E18" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="8" t="s">
         <v>17</v>
       </c>
       <c r="I18" s="6" t="s">
@@ -5826,16 +5804,16 @@
       <c r="B19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="C19" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -5858,16 +5836,16 @@
       <c r="B20" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="8" t="s">
+      <c r="C20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -5890,16 +5868,16 @@
       <c r="B21" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="10" t="s">
+      <c r="C21" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G21" s="6" t="s">
@@ -5920,18 +5898,18 @@
         <v>47</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="6" t="s">
@@ -5952,9 +5930,9 @@
         <v>48</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C23" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="7" t="s">
@@ -5963,7 +5941,7 @@
       <c r="E23" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="9" t="s">
         <v>20</v>
       </c>
       <c r="G23" s="6" t="s">
@@ -6000,10 +5978,10 @@
       <c r="B25" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="9" t="s">
         <v>20</v>
       </c>
       <c r="E25" s="7" t="s">
@@ -6018,7 +5996,7 @@
       <c r="H25" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="I25" s="8" t="s">
         <v>17</v>
       </c>
       <c r="J25" s="6" t="s">
@@ -6026,13 +6004,13 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.6" x14ac:dyDescent="0.6">
-      <c r="A28" s="11" t="s">
-        <v>52</v>
+      <c r="A28" s="10" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="33" t="s">
-        <v>201</v>
+      <c r="A29" s="37" t="s">
+        <v>200</v>
       </c>
       <c r="B29" s="34"/>
       <c r="C29" s="34"/>
@@ -6045,28 +6023,28 @@
       <c r="J29" s="34"/>
     </row>
     <row r="30" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="39"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="40"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
     </row>
     <row r="31" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="39"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="40"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6086,3027 +6064,3025 @@
   <dimension ref="A1:H137"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="17.9453125" style="31" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.62890625" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.3125" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.05078125" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7890625" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.578125" style="31" customWidth="1"/>
-    <col min="7" max="7" width="9.26171875" style="31" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="45.578125" style="31" customWidth="1"/>
-    <col min="9" max="16384" width="8.83984375" style="31"/>
+    <col min="1" max="1" width="17.9453125" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.62890625" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.3125" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.05078125" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7890625" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.578125" style="28" customWidth="1"/>
+    <col min="7" max="7" width="9.26171875" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.578125" style="28" customWidth="1"/>
+    <col min="9" max="16384" width="8.83984375" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="D1" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="E1" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="F1" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="G1" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="H1" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="30" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="28" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="31" t="s">
+      <c r="C2" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B3" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>194</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="29"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="29"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="31" t="s">
+      <c r="E10" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2" s="31" t="s">
+      <c r="F12" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="29"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="28" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="31" t="s">
+      <c r="E19" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="29"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="31" t="s">
+      <c r="E26" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F28" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="G32" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="E36" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="G37" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B38" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="G38" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="H38" s="29"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G39" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="G42" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" s="28" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="32" t="s">
+      <c r="E43" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="G46" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G47" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="32" t="s">
+      <c r="E50" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="G51" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E52" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="G52" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="32" t="s">
-        <v>200</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="G4" s="32" t="s">
+      <c r="E53" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="G53" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="G54" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B55" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="G55" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B57" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="G57" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B58" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E58" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B59" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="32"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="31" t="s">
+      <c r="E59" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B60" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E60" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="G60" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B61" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E61" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B62" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D62" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E62" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="G62" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B63" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C63" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G63" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B64" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E64" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="G64" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B65" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E65" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="G65" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C66" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D66" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="31" t="s">
+      <c r="E66" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C67" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D67" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E67" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B68" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C68" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D68" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E68" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F68" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="G68" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B69" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C69" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D69" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E69" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B70" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C70" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D70" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E70" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F70" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="G70" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B71" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C71" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D71" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="E71" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G71" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C72" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D72" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E72" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F72" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="G72" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B73" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C73" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D73" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E73" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F73" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="G73" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C74" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D74" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E74" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G74" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B75" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C75" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D75" s="28" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="32" t="s">
+      <c r="E75" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C76" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D76" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E76" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F76" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="G76" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B77" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C77" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D77" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E77" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G77" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B78" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C78" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D78" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E78" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="G78" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B79" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C79" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D79" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B80" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C80" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D80" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E80" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F80" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="G80" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B81" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C81" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D81" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E81" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="G81" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B82" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D82" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="32" t="s">
+      <c r="E82" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G82" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C83" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D83" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E83" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="G83" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B84" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C84" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D84" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E84" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F84" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="G84" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B85" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C85" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D85" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E85" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C86" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D86" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E86" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="G86" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B87" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C87" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D87" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E87" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F87" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="G87" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B88" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C88" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D88" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E88" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="G88" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C89" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="D89" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E89" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="G89" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B90" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C90" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D90" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E90" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G90" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B91" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C91" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D91" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E91" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G91" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B92" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C92" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D92" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E92" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F92" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="G92" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B93" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C93" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D93" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E93" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G93" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C94" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D94" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E94" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="G94" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B95" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C95" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D95" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G95" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B96" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C96" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D96" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E96" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F96" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="G96" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B97" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C97" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D97" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E97" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F97" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="G97" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B98" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C98" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D98" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E98" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B99" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C99" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D99" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E99" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G99" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B100" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C100" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D100" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="E100" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="F100" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G100" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="H100" s="29"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B101" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C101" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D101" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E101" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B102" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C102" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D102" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E102" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F102" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="G102" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B103" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C103" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D103" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E103" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F103" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G103" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B104" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C104" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D104" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E104" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F104" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="G104" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B105" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C105" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="D105" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E105" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F105" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="G105" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B106" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C106" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D106" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E106" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="F106" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="G106" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B107" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C107" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D107" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="32"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="31" t="s">
+      <c r="E107" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G107" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B108" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C108" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D108" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E108" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F108" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="G108" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B109" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C109" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D109" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E109" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G109" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B110" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C110" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D110" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E110" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F110" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="G110" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B111" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C111" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D111" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E111" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F111" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G111" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B112" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C112" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D112" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E112" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F112" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="G112" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B113" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C113" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D113" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E113" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F113" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="G113" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B114" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C114" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D114" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="31" t="s">
+      <c r="E114" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G114" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B115" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C115" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D115" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E115" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G115" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B116" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C116" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D116" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E116" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F116" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="G116" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B117" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C117" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D117" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E117" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G117" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B118" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C118" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D118" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E118" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F118" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="G118" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B119" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C119" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D119" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F119" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G119" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B120" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C120" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D120" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E120" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F120" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="G120" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B121" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C121" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D121" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E121" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="G121" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B122" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C122" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D122" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E122" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G122" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B123" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C123" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D123" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="E123" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F123" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="G123" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B124" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C124" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D124" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E124" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F124" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="G124" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B125" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C125" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D125" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E125" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G125" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B126" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C126" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D126" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E126" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F126" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G126" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A127" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B127" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C127" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D127" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E127" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F127" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="G127" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B128" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C128" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D128" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E128" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="G128" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B129" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C129" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="D129" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E129" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F129" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="G129" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A130" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B130" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C130" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D130" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E130" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="31" t="s">
+      <c r="F130" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="G130" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A131" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B131" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C131" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D131" s="28" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="31" t="s">
+      <c r="E131" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G131" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B132" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C132" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D132" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="E132" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F132" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="G132" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A133" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B133" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C133" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D133" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E133" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F133" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="G133" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A134" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B134" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C134" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D134" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="E134" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="F134" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="G134" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A135" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B135" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C135" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D135" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G135" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A136" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B136" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C136" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D136" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E136" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F136" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="G136" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A137" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="B137" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C137" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D137" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="32" t="s">
+      <c r="E137" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="H12" s="32"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="G18" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>205</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="H22" s="32"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G26" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="G28" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E30" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E31" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E32" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F32" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="G32" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E33" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="G33" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D34" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E34" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F34" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="G34" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E35" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D36" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E36" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D37" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E37" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F37" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="G37" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="D38" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="E38" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="G38" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="H38" s="32"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D39" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E39" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F39" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="G39" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B40" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D40" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E40" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="B41" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C41" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D41" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E41" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B42" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C42" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D42" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E42" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F42" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="G42" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B43" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D43" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E43" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B44" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E44" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B45" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E45" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B46" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E46" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F46" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="G46" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C47" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D47" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E47" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F47" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="G47" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B48" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C48" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D48" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E48" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B49" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C49" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D49" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E49" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B50" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D50" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E50" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B51" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D51" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E51" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F51" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="G51" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B52" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D52" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E52" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F52" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="G52" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B53" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C53" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D53" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E53" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F53" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="G53" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B54" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C54" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D54" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E54" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F54" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="G54" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B55" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C55" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D55" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E55" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F55" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="G55" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B56" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C56" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D56" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E56" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B57" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C57" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="D57" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E57" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F57" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="G57" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B58" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D58" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E58" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B59" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C59" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D59" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E59" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G59" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B60" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C60" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D60" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E60" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F60" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="G60" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B61" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D61" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E61" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G61" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B62" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C62" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D62" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E62" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F62" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="G62" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B63" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C63" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D63" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E63" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F63" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="G63" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B64" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C64" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D64" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E64" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F64" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="G64" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B65" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="C65" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D65" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E65" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F65" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="G65" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B66" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C66" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D66" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E66" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G66" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B67" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C67" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D67" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E67" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G67" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B68" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C68" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D68" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E68" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F68" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="G68" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B69" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C69" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D69" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E69" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G69" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B70" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C70" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D70" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E70" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F70" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="G70" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B71" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C71" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D71" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E71" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="G71" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B72" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C72" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D72" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E72" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F72" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="G72" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B73" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C73" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D73" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E73" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F73" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="G73" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C74" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D74" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E74" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G74" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C75" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D75" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E75" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G75" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C76" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D76" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E76" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F76" s="31" t="s">
-        <v>109</v>
-      </c>
-      <c r="G76" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B77" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C77" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D77" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E77" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G77" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B78" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C78" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D78" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E78" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F78" s="31" t="s">
-        <v>110</v>
-      </c>
-      <c r="G78" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B79" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C79" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D79" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E79" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="G79" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B80" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C80" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D80" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E80" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F80" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="G80" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="B81" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C81" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D81" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E81" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F81" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="G81" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="B82" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C82" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D82" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E82" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G82" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="B83" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C83" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D83" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E83" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F83" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="G83" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="B84" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C84" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D84" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E84" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F84" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="G84" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="B85" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C85" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D85" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E85" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G85" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="B86" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C86" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D86" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E86" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="G86" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="B87" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C87" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D87" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E87" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="F87" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="G87" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="B88" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C88" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D88" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E88" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="G88" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="B89" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C89" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D89" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E89" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F89" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G89" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="B90" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C90" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D90" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E90" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G90" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="B91" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C91" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D91" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E91" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G91" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="B92" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C92" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D92" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E92" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F92" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="G92" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A93" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="B93" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C93" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D93" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E93" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G93" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="B94" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C94" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D94" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E94" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F94" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G94" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="B95" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C95" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D95" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E95" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="G95" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A96" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="B96" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C96" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D96" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E96" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F96" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="G96" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="B97" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C97" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="D97" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E97" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F97" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="G97" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A98" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B98" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C98" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D98" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E98" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G98" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B99" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C99" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D99" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E99" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G99" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A100" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B100" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="C100" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D100" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="E100" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="F100" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="G100" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="H100" s="32" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B101" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C101" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D101" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E101" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G101" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B102" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C102" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D102" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E102" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F102" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="G102" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A103" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B103" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C103" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D103" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E103" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F103" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="G103" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A104" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B104" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C104" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D104" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E104" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F104" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="G104" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A105" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="B105" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C105" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D105" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E105" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F105" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="G105" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A106" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B106" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C106" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D106" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E106" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F106" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="G106" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A107" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B107" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C107" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D107" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E107" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G107" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A108" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B108" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C108" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D108" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E108" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F108" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="G108" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A109" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B109" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C109" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D109" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E109" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G109" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A110" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B110" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C110" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D110" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E110" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F110" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="G110" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A111" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B111" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C111" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D111" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E111" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F111" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="G111" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A112" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B112" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C112" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D112" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E112" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F112" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="G112" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="B113" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C113" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D113" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E113" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F113" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="G113" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A114" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B114" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C114" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="D114" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E114" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G114" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A115" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B115" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C115" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="D115" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E115" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G115" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A116" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B116" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C116" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="D116" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E116" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F116" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="G116" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A117" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B117" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C117" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="D117" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E117" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G117" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A118" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B118" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C118" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="D118" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E118" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F118" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="G118" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A119" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B119" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C119" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="D119" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E119" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F119" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="G119" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A120" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B120" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C120" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="D120" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E120" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F120" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="G120" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A121" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="B121" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C121" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="D121" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E121" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F121" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="G121" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A122" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B122" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C122" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="D122" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E122" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G122" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A123" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B123" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C123" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="D123" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E123" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F123" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="G123" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A124" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B124" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C124" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="D124" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E124" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F124" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="G124" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A125" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B125" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C125" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="D125" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E125" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G125" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A126" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B126" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C126" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="D126" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E126" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F126" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="G126" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A127" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B127" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C127" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="D127" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E127" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F127" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="G127" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A128" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B128" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C128" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="D128" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E128" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F128" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G128" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A129" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="B129" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="C129" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="D129" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E129" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F129" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="G129" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A130" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B130" s="31" t="s">
+      <c r="F137" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="C130" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D130" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E130" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="F130" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="G130" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A131" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B131" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C131" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D131" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="E131" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G131" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A132" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B132" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C132" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D132" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="E132" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F132" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="G132" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A133" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B133" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C133" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D133" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="E133" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F133" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G133" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A134" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B134" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C134" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D134" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E134" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F134" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="G134" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A135" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B135" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C135" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D135" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="E135" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="G135" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A136" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B136" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C136" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D136" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="E136" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="F136" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="G136" s="31" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A137" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B137" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C137" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D137" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E137" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F137" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="G137" s="31" t="s">
-        <v>63</v>
+      <c r="G137" s="28" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
